--- a/kiwoom_cli_commands.xlsx
+++ b/kiwoom_cli_commands.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 명령어" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="전체 명령어" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체 명령어'!$A$1:$H$220</definedName>
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H220"/>
+  <dimension ref="A1:H221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8578,90 +8578,87 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="12" t="inlineStr">
+      <c r="A191" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B191" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C191" s="12" t="inlineStr">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>kiwoom stock list</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>KRX 전체 상장종목 리스트 (pykrx)</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>--market [all, kospi, kosdaq, konex] 기본:all (시장구분)
+--search (종목명/코드 검색 키워드)
+--refresh (캐시 무시하고 새로 조회)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B192" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C192" s="12" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D191" s="12" t="inlineStr">
+      <c r="D192" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock short</t>
         </is>
       </c>
-      <c r="E191" s="12" t="inlineStr">
+      <c r="E192" s="12" t="inlineStr">
         <is>
           <t>공매도 추이 조회</t>
         </is>
       </c>
-      <c r="F191" s="13" t="inlineStr">
+      <c r="F192" s="13" t="inlineStr">
         <is>
           <t>ka10014</t>
         </is>
       </c>
-      <c r="G191" s="12" t="inlineStr">
+      <c r="G192" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H191" s="12" t="inlineStr">
+      <c r="H192" s="12" t="inlineStr">
         <is>
           <t>--from (시작일자 (YYYYMMDD, 기본=30일전))
 --to (종료일자 (YYYYMMDD, 기본=오늘))</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B192" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C192" s="12" t="inlineStr">
-        <is>
-          <t>tick-strength</t>
-        </is>
-      </c>
-      <c r="D192" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock tick-strength</t>
-        </is>
-      </c>
-      <c r="E192" s="12" t="inlineStr">
-        <is>
-          <t>체결강도추이 시간별</t>
-        </is>
-      </c>
-      <c r="F192" s="13" t="inlineStr">
-        <is>
-          <t>ka10046</t>
-        </is>
-      </c>
-      <c r="G192" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H192" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="193">
       <c r="A193" s="12" t="inlineStr">
         <is>
@@ -8675,22 +8672,22 @@
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>timeprice</t>
+          <t>tick-strength</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock timeprice</t>
+          <t>kiwoom stock tick-strength</t>
         </is>
       </c>
       <c r="E193" s="12" t="inlineStr">
         <is>
-          <t>시분 시세 조회</t>
+          <t>체결강도추이 시간별</t>
         </is>
       </c>
       <c r="F193" s="13" t="inlineStr">
         <is>
-          <t>ka10006</t>
+          <t>ka10046</t>
         </is>
       </c>
       <c r="G193" s="12" t="inlineStr">
@@ -8717,30 +8714,72 @@
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
+          <t>timeprice</t>
+        </is>
+      </c>
+      <c r="D194" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock timeprice</t>
+        </is>
+      </c>
+      <c r="E194" s="12" t="inlineStr">
+        <is>
+          <t>시분 시세 조회</t>
+        </is>
+      </c>
+      <c r="F194" s="13" t="inlineStr">
+        <is>
+          <t>ka10006</t>
+        </is>
+      </c>
+      <c r="G194" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H194" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B195" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C195" s="12" t="inlineStr">
+        <is>
           <t>today-exec</t>
         </is>
       </c>
-      <c r="D194" s="12" t="inlineStr">
+      <c r="D195" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock today-exec</t>
         </is>
       </c>
-      <c r="E194" s="12" t="inlineStr">
+      <c r="E195" s="12" t="inlineStr">
         <is>
           <t>당일/전일 체결 조회</t>
         </is>
       </c>
-      <c r="F194" s="13" t="inlineStr">
+      <c r="F195" s="13" t="inlineStr">
         <is>
           <t>ka10084</t>
         </is>
       </c>
-      <c r="G194" s="12" t="inlineStr">
+      <c r="G195" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H194" s="12" t="inlineStr">
+      <c r="H195" s="12" t="inlineStr">
         <is>
           <t>--when [1, 2] 기본:1 (당일전일 (1=당일, 2=전일))
 --mode [0, 1] (틱/분 (0=틱, 1=분))
@@ -8748,48 +8787,6 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B195" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C195" s="12" t="inlineStr">
-        <is>
-          <t>today-volume</t>
-        </is>
-      </c>
-      <c r="D195" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock today-volume</t>
-        </is>
-      </c>
-      <c r="E195" s="12" t="inlineStr">
-        <is>
-          <t>당일/전일 체결량 조회</t>
-        </is>
-      </c>
-      <c r="F195" s="13" t="inlineStr">
-        <is>
-          <t>ka10055</t>
-        </is>
-      </c>
-      <c r="G195" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H195" s="12" t="inlineStr">
-        <is>
-          <t>--when [1, 2] 기본:1 (당일전일 (1=당일, 2=전일))</t>
-        </is>
-      </c>
-    </row>
     <row r="196">
       <c r="A196" s="12" t="inlineStr">
         <is>
@@ -8803,22 +8800,22 @@
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>trader</t>
+          <t>today-volume</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock trader</t>
+          <t>kiwoom stock today-volume</t>
         </is>
       </c>
       <c r="E196" s="12" t="inlineStr">
         <is>
-          <t>거래원 조회</t>
+          <t>당일/전일 체결량 조회</t>
         </is>
       </c>
       <c r="F196" s="13" t="inlineStr">
         <is>
-          <t>ka10002</t>
+          <t>ka10055</t>
         </is>
       </c>
       <c r="G196" s="12" t="inlineStr">
@@ -8828,7 +8825,7 @@
       </c>
       <c r="H196" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>--when [1, 2] 기본:1 (당일전일 (1=당일, 2=전일))</t>
         </is>
       </c>
     </row>
@@ -8845,70 +8842,74 @@
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
+          <t>trader</t>
+        </is>
+      </c>
+      <c r="D197" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock trader</t>
+        </is>
+      </c>
+      <c r="E197" s="12" t="inlineStr">
+        <is>
+          <t>거래원 조회</t>
+        </is>
+      </c>
+      <c r="F197" s="13" t="inlineStr">
+        <is>
+          <t>ka10002</t>
+        </is>
+      </c>
+      <c r="G197" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H197" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B198" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C198" s="12" t="inlineStr">
+        <is>
           <t>watchlist</t>
         </is>
       </c>
-      <c r="D197" s="12" t="inlineStr">
+      <c r="D198" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock watchlist</t>
         </is>
       </c>
-      <c r="E197" s="12" t="inlineStr">
+      <c r="E198" s="12" t="inlineStr">
         <is>
           <t>관심종목정보 조회 (코드를 |로 구분, 예: 005930|000660)</t>
         </is>
       </c>
-      <c r="F197" s="13" t="inlineStr">
+      <c r="F198" s="13" t="inlineStr">
         <is>
           <t>ka10095</t>
         </is>
       </c>
-      <c r="G197" s="12" t="inlineStr">
+      <c r="G198" s="12" t="inlineStr">
         <is>
           <t>CODES (필수)</t>
         </is>
       </c>
-      <c r="H197" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="14" t="inlineStr">
-        <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="B198" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C198" s="14" t="inlineStr">
-        <is>
-          <t>after-hours</t>
-        </is>
-      </c>
-      <c r="D198" s="14" t="inlineStr">
-        <is>
-          <t>kiwoom stream after-hours</t>
-        </is>
-      </c>
-      <c r="E198" s="14" t="inlineStr">
-        <is>
-          <t>주식시간외호가 실시간 (0E)</t>
-        </is>
-      </c>
-      <c r="F198" s="15" t="inlineStr"/>
-      <c r="G198" s="14" t="inlineStr">
-        <is>
-          <t>CODES (복수) (필수)</t>
-        </is>
-      </c>
-      <c r="H198" s="14" t="inlineStr">
-        <is>
-          <t>--raw (JSON 원본 출력)</t>
+      <c r="H198" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8925,23 +8926,23 @@
       </c>
       <c r="C199" s="14" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>after-hours</t>
         </is>
       </c>
       <c r="D199" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream balance</t>
+          <t>kiwoom stream after-hours</t>
         </is>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>잔고 실시간 (04)</t>
+          <t>주식시간외호가 실시간 (0E)</t>
         </is>
       </c>
       <c r="F199" s="15" t="inlineStr"/>
       <c r="G199" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H199" s="14" t="inlineStr">
@@ -8963,23 +8964,23 @@
       </c>
       <c r="C200" s="14" t="inlineStr">
         <is>
-          <t>best-bid</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="D200" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream best-bid</t>
+          <t>kiwoom stream balance</t>
         </is>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>주식우선호가 실시간 (0C)</t>
+          <t>잔고 실시간 (04)</t>
         </is>
       </c>
       <c r="F200" s="15" t="inlineStr"/>
       <c r="G200" s="14" t="inlineStr">
         <is>
-          <t>CODES (복수) (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H200" s="14" t="inlineStr">
@@ -9001,64 +9002,64 @@
       </c>
       <c r="C201" s="14" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>best-bid</t>
         </is>
       </c>
       <c r="D201" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream custom</t>
+          <t>kiwoom stream best-bid</t>
         </is>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>커스텀 실시간 타입으로 스트리밍</t>
+          <t>주식우선호가 실시간 (0C)</t>
         </is>
       </c>
       <c r="F201" s="15" t="inlineStr"/>
       <c r="G201" s="14" t="inlineStr">
         <is>
+          <t>CODES (복수) (필수)</t>
+        </is>
+      </c>
+      <c r="H201" s="14" t="inlineStr">
+        <is>
+          <t>--raw (JSON 원본 출력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="14" t="inlineStr">
+        <is>
+          <t>stream</t>
+        </is>
+      </c>
+      <c r="B202" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C202" s="14" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D202" s="14" t="inlineStr">
+        <is>
+          <t>kiwoom stream custom</t>
+        </is>
+      </c>
+      <c r="E202" s="14" t="inlineStr">
+        <is>
+          <t>커스텀 실시간 타입으로 스트리밍</t>
+        </is>
+      </c>
+      <c r="F202" s="15" t="inlineStr"/>
+      <c r="G202" s="14" t="inlineStr">
+        <is>
           <t>TYPE_CODES (필수)
 CODES (복수) (선택)</t>
         </is>
       </c>
-      <c r="H201" s="14" t="inlineStr">
-        <is>
-          <t>--raw (JSON 원본 출력)</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="14" t="inlineStr">
-        <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="B202" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C202" s="14" t="inlineStr">
-        <is>
-          <t>elw-indicator</t>
-        </is>
-      </c>
-      <c r="D202" s="14" t="inlineStr">
-        <is>
-          <t>kiwoom stream elw-indicator</t>
-        </is>
-      </c>
-      <c r="E202" s="14" t="inlineStr">
-        <is>
-          <t>ELW 지표 실시간 (0u)</t>
-        </is>
-      </c>
-      <c r="F202" s="15" t="inlineStr"/>
-      <c r="G202" s="14" t="inlineStr">
-        <is>
-          <t>CODES (복수) (필수)</t>
-        </is>
-      </c>
       <c r="H202" s="14" t="inlineStr">
         <is>
           <t>--raw (JSON 원본 출력)</t>
@@ -9078,17 +9079,17 @@
       </c>
       <c r="C203" s="14" t="inlineStr">
         <is>
-          <t>elw-theory</t>
+          <t>elw-indicator</t>
         </is>
       </c>
       <c r="D203" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream elw-theory</t>
+          <t>kiwoom stream elw-indicator</t>
         </is>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>ELW 이론가 실시간 (0m)</t>
+          <t>ELW 지표 실시간 (0u)</t>
         </is>
       </c>
       <c r="F203" s="15" t="inlineStr"/>
@@ -9116,17 +9117,17 @@
       </c>
       <c r="C204" s="14" t="inlineStr">
         <is>
-          <t>etf-nav</t>
+          <t>elw-theory</t>
         </is>
       </c>
       <c r="D204" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream etf-nav</t>
+          <t>kiwoom stream elw-theory</t>
         </is>
       </c>
       <c r="E204" s="14" t="inlineStr">
         <is>
-          <t>ETF NAV 실시간 (0G)</t>
+          <t>ELW 이론가 실시간 (0m)</t>
         </is>
       </c>
       <c r="F204" s="15" t="inlineStr"/>
@@ -9154,17 +9155,17 @@
       </c>
       <c r="C205" s="14" t="inlineStr">
         <is>
-          <t>expected</t>
+          <t>etf-nav</t>
         </is>
       </c>
       <c r="D205" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream expected</t>
+          <t>kiwoom stream etf-nav</t>
         </is>
       </c>
       <c r="E205" s="14" t="inlineStr">
         <is>
-          <t>주식예상체결 실시간 (0H)</t>
+          <t>ETF NAV 실시간 (0G)</t>
         </is>
       </c>
       <c r="F205" s="15" t="inlineStr"/>
@@ -9192,17 +9193,17 @@
       </c>
       <c r="C206" s="14" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>expected</t>
         </is>
       </c>
       <c r="D206" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream gold</t>
+          <t>kiwoom stream expected</t>
         </is>
       </c>
       <c r="E206" s="14" t="inlineStr">
         <is>
-          <t>국제금환산가격 실시간 (0I)</t>
+          <t>주식예상체결 실시간 (0H)</t>
         </is>
       </c>
       <c r="F206" s="15" t="inlineStr"/>
@@ -9230,23 +9231,23 @@
       </c>
       <c r="C207" s="14" t="inlineStr">
         <is>
-          <t>market-time</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="D207" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream market-time</t>
+          <t>kiwoom stream gold</t>
         </is>
       </c>
       <c r="E207" s="14" t="inlineStr">
         <is>
-          <t>장시작시간 실시간 (0s)</t>
+          <t>국제금환산가격 실시간 (0I)</t>
         </is>
       </c>
       <c r="F207" s="15" t="inlineStr"/>
       <c r="G207" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H207" s="14" t="inlineStr">
@@ -9268,23 +9269,23 @@
       </c>
       <c r="C208" s="14" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>market-time</t>
         </is>
       </c>
       <c r="D208" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream multi</t>
+          <t>kiwoom stream market-time</t>
         </is>
       </c>
       <c r="E208" s="14" t="inlineStr">
         <is>
-          <t>주식체결+호가잔량 동시 스트리밍 (0B+0D)</t>
+          <t>장시작시간 실시간 (0s)</t>
         </is>
       </c>
       <c r="F208" s="15" t="inlineStr"/>
       <c r="G208" s="14" t="inlineStr">
         <is>
-          <t>CODES (복수) (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H208" s="14" t="inlineStr">
@@ -9306,23 +9307,23 @@
       </c>
       <c r="C209" s="14" t="inlineStr">
         <is>
-          <t>order</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="D209" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream order</t>
+          <t>kiwoom stream multi</t>
         </is>
       </c>
       <c r="E209" s="14" t="inlineStr">
         <is>
-          <t>주문체결 실시간 (00)</t>
+          <t>주식체결+호가잔량 동시 스트리밍 (0B+0D)</t>
         </is>
       </c>
       <c r="F209" s="15" t="inlineStr"/>
       <c r="G209" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H209" s="14" t="inlineStr">
@@ -9344,23 +9345,23 @@
       </c>
       <c r="C210" s="14" t="inlineStr">
         <is>
-          <t>orderbook</t>
+          <t>order</t>
         </is>
       </c>
       <c r="D210" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream orderbook</t>
+          <t>kiwoom stream order</t>
         </is>
       </c>
       <c r="E210" s="14" t="inlineStr">
         <is>
-          <t>주식호가잔량 실시간 (0D)</t>
+          <t>주문체결 실시간 (00)</t>
         </is>
       </c>
       <c r="F210" s="15" t="inlineStr"/>
       <c r="G210" s="14" t="inlineStr">
         <is>
-          <t>CODES (복수) (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H210" s="14" t="inlineStr">
@@ -9382,17 +9383,17 @@
       </c>
       <c r="C211" s="14" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>orderbook</t>
         </is>
       </c>
       <c r="D211" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream price</t>
+          <t>kiwoom stream orderbook</t>
         </is>
       </c>
       <c r="E211" s="14" t="inlineStr">
         <is>
-          <t>주식기세 실시간 (0A)</t>
+          <t>주식호가잔량 실시간 (0D)</t>
         </is>
       </c>
       <c r="F211" s="15" t="inlineStr"/>
@@ -9420,17 +9421,17 @@
       </c>
       <c r="C212" s="14" t="inlineStr">
         <is>
-          <t>program</t>
+          <t>price</t>
         </is>
       </c>
       <c r="D212" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream program</t>
+          <t>kiwoom stream price</t>
         </is>
       </c>
       <c r="E212" s="14" t="inlineStr">
         <is>
-          <t>종목프로그램매매 실시간 (0w)</t>
+          <t>주식기세 실시간 (0A)</t>
         </is>
       </c>
       <c r="F212" s="15" t="inlineStr"/>
@@ -9458,17 +9459,17 @@
       </c>
       <c r="C213" s="14" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>program</t>
         </is>
       </c>
       <c r="D213" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream quote</t>
+          <t>kiwoom stream program</t>
         </is>
       </c>
       <c r="E213" s="14" t="inlineStr">
         <is>
-          <t>주식체결 실시간 (0B)</t>
+          <t>종목프로그램매매 실시간 (0w)</t>
         </is>
       </c>
       <c r="F213" s="15" t="inlineStr"/>
@@ -9496,17 +9497,17 @@
       </c>
       <c r="C214" s="14" t="inlineStr">
         <is>
-          <t>sector-change</t>
+          <t>quote</t>
         </is>
       </c>
       <c r="D214" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream sector-change</t>
+          <t>kiwoom stream quote</t>
         </is>
       </c>
       <c r="E214" s="14" t="inlineStr">
         <is>
-          <t>업종등락 실시간 (0U)</t>
+          <t>주식체결 실시간 (0B)</t>
         </is>
       </c>
       <c r="F214" s="15" t="inlineStr"/>
@@ -9534,17 +9535,17 @@
       </c>
       <c r="C215" s="14" t="inlineStr">
         <is>
-          <t>sector-index</t>
+          <t>sector-change</t>
         </is>
       </c>
       <c r="D215" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream sector-index</t>
+          <t>kiwoom stream sector-change</t>
         </is>
       </c>
       <c r="E215" s="14" t="inlineStr">
         <is>
-          <t>업종지수 실시간 (0J)</t>
+          <t>업종등락 실시간 (0U)</t>
         </is>
       </c>
       <c r="F215" s="15" t="inlineStr"/>
@@ -9572,17 +9573,17 @@
       </c>
       <c r="C216" s="14" t="inlineStr">
         <is>
-          <t>stock-info</t>
+          <t>sector-index</t>
         </is>
       </c>
       <c r="D216" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream stock-info</t>
+          <t>kiwoom stream sector-index</t>
         </is>
       </c>
       <c r="E216" s="14" t="inlineStr">
         <is>
-          <t>주식종목정보 실시간 (0g)</t>
+          <t>업종지수 실시간 (0J)</t>
         </is>
       </c>
       <c r="F216" s="15" t="inlineStr"/>
@@ -9610,17 +9611,17 @@
       </c>
       <c r="C217" s="14" t="inlineStr">
         <is>
-          <t>trader</t>
+          <t>stock-info</t>
         </is>
       </c>
       <c r="D217" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream trader</t>
+          <t>kiwoom stream stock-info</t>
         </is>
       </c>
       <c r="E217" s="14" t="inlineStr">
         <is>
-          <t>주식당일거래원 실시간 (0F)</t>
+          <t>주식종목정보 실시간 (0g)</t>
         </is>
       </c>
       <c r="F217" s="15" t="inlineStr"/>
@@ -9648,28 +9649,28 @@
       </c>
       <c r="C218" s="14" t="inlineStr">
         <is>
-          <t>types</t>
+          <t>trader</t>
         </is>
       </c>
       <c r="D218" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream types</t>
+          <t>kiwoom stream trader</t>
         </is>
       </c>
       <c r="E218" s="14" t="inlineStr">
         <is>
-          <t>사용 가능한 실시간 타입 코드 목록</t>
+          <t>주식당일거래원 실시간 (0F)</t>
         </is>
       </c>
       <c r="F218" s="15" t="inlineStr"/>
       <c r="G218" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H218" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>--raw (JSON 원본 출력)</t>
         </is>
       </c>
     </row>
@@ -9686,64 +9687,102 @@
       </c>
       <c r="C219" s="14" t="inlineStr">
         <is>
-          <t>vi</t>
+          <t>types</t>
         </is>
       </c>
       <c r="D219" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream vi</t>
+          <t>kiwoom stream types</t>
         </is>
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>VI발동/해제 실시간 (1h)</t>
+          <t>사용 가능한 실시간 타입 코드 목록</t>
         </is>
       </c>
       <c r="F219" s="15" t="inlineStr"/>
       <c r="G219" s="14" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H219" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="14" t="inlineStr">
+        <is>
+          <t>stream</t>
+        </is>
+      </c>
+      <c r="B220" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C220" s="14" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="D220" s="14" t="inlineStr">
+        <is>
+          <t>kiwoom stream vi</t>
+        </is>
+      </c>
+      <c r="E220" s="14" t="inlineStr">
+        <is>
+          <t>VI발동/해제 실시간 (1h)</t>
+        </is>
+      </c>
+      <c r="F220" s="15" t="inlineStr"/>
+      <c r="G220" s="14" t="inlineStr">
+        <is>
           <t>CODES (복수) (필수)</t>
         </is>
       </c>
-      <c r="H219" s="14" t="inlineStr">
+      <c r="H220" s="14" t="inlineStr">
         <is>
           <t>--raw (JSON 원본 출력)</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="6" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="6" t="inlineStr">
         <is>
           <t>watch</t>
         </is>
       </c>
-      <c r="B220" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C220" s="6" t="inlineStr">
+      <c r="B221" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C221" s="6" t="inlineStr">
         <is>
           <t>watch</t>
         </is>
       </c>
-      <c r="D220" s="6" t="inlineStr">
+      <c r="D221" s="6" t="inlineStr">
         <is>
           <t>kiwoom watch</t>
         </is>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="E221" s="6" t="inlineStr">
         <is>
           <t>실시간 종목 모니터링 (TUI 대시보드)</t>
         </is>
       </c>
-      <c r="F220" s="7" t="inlineStr"/>
-      <c r="G220" s="6" t="inlineStr">
+      <c r="F221" s="7" t="inlineStr"/>
+      <c r="G221" s="6" t="inlineStr">
         <is>
           <t>CODES (복수) (필수)</t>
         </is>
       </c>
-      <c r="H220" s="6" t="inlineStr">
+      <c r="H221" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9776,6 +9815,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
@@ -9845,7 +9885,7 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
@@ -9950,7 +9990,7 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/kiwoom_cli_commands.xlsx
+++ b/kiwoom_cli_commands.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="전체 명령어" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 명령어" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체 명령어'!$A$1:$H$220</definedName>
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H221"/>
+  <dimension ref="A1:H220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8573,46 +8573,50 @@
       </c>
       <c r="H190" s="12" t="inlineStr">
         <is>
-          <t>--market [kospi, kosdaq, k-otc, konex, etf, elw] 기본:kospi (시장구분 (kospi/kosdaq/k-otc/konex/etf/elw))</t>
+          <t>--market [all, kospi, kosdaq, k-otc, konex, etf, elw] 기본:all (시장구분 (all/kospi/kosdaq/k-otc/konex/etf/elw))</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>kiwoom stock list</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>KRX 전체 상장종목 리스트 (pykrx)</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>--market [all, kospi, kosdaq, konex] 기본:all (시장구분)
---search (종목명/코드 검색 키워드)
---refresh (캐시 무시하고 새로 조회)</t>
+      <c r="B191" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C191" s="12" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D191" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock short</t>
+        </is>
+      </c>
+      <c r="E191" s="12" t="inlineStr">
+        <is>
+          <t>공매도 추이 조회</t>
+        </is>
+      </c>
+      <c r="F191" s="13" t="inlineStr">
+        <is>
+          <t>ka10014</t>
+        </is>
+      </c>
+      <c r="G191" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H191" s="12" t="inlineStr">
+        <is>
+          <t>--from (시작일자 (YYYYMMDD, 기본=30일전))
+--to (종료일자 (YYYYMMDD, 기본=오늘))</t>
         </is>
       </c>
     </row>
@@ -8629,22 +8633,22 @@
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>tick-strength</t>
         </is>
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock short</t>
+          <t>kiwoom stock tick-strength</t>
         </is>
       </c>
       <c r="E192" s="12" t="inlineStr">
         <is>
-          <t>공매도 추이 조회</t>
+          <t>체결강도추이 시간별</t>
         </is>
       </c>
       <c r="F192" s="13" t="inlineStr">
         <is>
-          <t>ka10014</t>
+          <t>ka10046</t>
         </is>
       </c>
       <c r="G192" s="12" t="inlineStr">
@@ -8654,8 +8658,7 @@
       </c>
       <c r="H192" s="12" t="inlineStr">
         <is>
-          <t>--from (시작일자 (YYYYMMDD, 기본=30일전))
---to (종료일자 (YYYYMMDD, 기본=오늘))</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8672,22 +8675,22 @@
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>tick-strength</t>
+          <t>timeprice</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock tick-strength</t>
+          <t>kiwoom stock timeprice</t>
         </is>
       </c>
       <c r="E193" s="12" t="inlineStr">
         <is>
-          <t>체결강도추이 시간별</t>
+          <t>시분 시세 조회</t>
         </is>
       </c>
       <c r="F193" s="13" t="inlineStr">
         <is>
-          <t>ka10046</t>
+          <t>ka10006</t>
         </is>
       </c>
       <c r="G193" s="12" t="inlineStr">
@@ -8714,22 +8717,22 @@
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>timeprice</t>
+          <t>today-exec</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock timeprice</t>
+          <t>kiwoom stock today-exec</t>
         </is>
       </c>
       <c r="E194" s="12" t="inlineStr">
         <is>
-          <t>시분 시세 조회</t>
+          <t>당일/전일 체결 조회</t>
         </is>
       </c>
       <c r="F194" s="13" t="inlineStr">
         <is>
-          <t>ka10006</t>
+          <t>ka10084</t>
         </is>
       </c>
       <c r="G194" s="12" t="inlineStr">
@@ -8738,48 +8741,6 @@
         </is>
       </c>
       <c r="H194" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B195" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C195" s="12" t="inlineStr">
-        <is>
-          <t>today-exec</t>
-        </is>
-      </c>
-      <c r="D195" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock today-exec</t>
-        </is>
-      </c>
-      <c r="E195" s="12" t="inlineStr">
-        <is>
-          <t>당일/전일 체결 조회</t>
-        </is>
-      </c>
-      <c r="F195" s="13" t="inlineStr">
-        <is>
-          <t>ka10084</t>
-        </is>
-      </c>
-      <c r="G195" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H195" s="12" t="inlineStr">
         <is>
           <t>--when [1, 2] 기본:1 (당일전일 (1=당일, 2=전일))
 --mode [0, 1] (틱/분 (0=틱, 1=분))
@@ -8787,6 +8748,48 @@
         </is>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B195" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C195" s="12" t="inlineStr">
+        <is>
+          <t>today-volume</t>
+        </is>
+      </c>
+      <c r="D195" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock today-volume</t>
+        </is>
+      </c>
+      <c r="E195" s="12" t="inlineStr">
+        <is>
+          <t>당일/전일 체결량 조회</t>
+        </is>
+      </c>
+      <c r="F195" s="13" t="inlineStr">
+        <is>
+          <t>ka10055</t>
+        </is>
+      </c>
+      <c r="G195" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H195" s="12" t="inlineStr">
+        <is>
+          <t>--when [1, 2] 기본:1 (당일전일 (1=당일, 2=전일))</t>
+        </is>
+      </c>
+    </row>
     <row r="196">
       <c r="A196" s="12" t="inlineStr">
         <is>
@@ -8800,22 +8803,22 @@
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>today-volume</t>
+          <t>trader</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock today-volume</t>
+          <t>kiwoom stock trader</t>
         </is>
       </c>
       <c r="E196" s="12" t="inlineStr">
         <is>
-          <t>당일/전일 체결량 조회</t>
+          <t>거래원 조회</t>
         </is>
       </c>
       <c r="F196" s="13" t="inlineStr">
         <is>
-          <t>ka10055</t>
+          <t>ka10002</t>
         </is>
       </c>
       <c r="G196" s="12" t="inlineStr">
@@ -8825,7 +8828,7 @@
       </c>
       <c r="H196" s="12" t="inlineStr">
         <is>
-          <t>--when [1, 2] 기본:1 (당일전일 (1=당일, 2=전일))</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8842,27 +8845,27 @@
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>trader</t>
+          <t>watchlist</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock trader</t>
+          <t>kiwoom stock watchlist</t>
         </is>
       </c>
       <c r="E197" s="12" t="inlineStr">
         <is>
-          <t>거래원 조회</t>
+          <t>관심종목정보 조회 (코드를 |로 구분, 예: 005930|000660)</t>
         </is>
       </c>
       <c r="F197" s="13" t="inlineStr">
         <is>
-          <t>ka10002</t>
+          <t>ka10095</t>
         </is>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
-          <t>CODE (필수)</t>
+          <t>CODES (필수)</t>
         </is>
       </c>
       <c r="H197" s="12" t="inlineStr">
@@ -8872,44 +8875,40 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B198" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C198" s="12" t="inlineStr">
-        <is>
-          <t>watchlist</t>
-        </is>
-      </c>
-      <c r="D198" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock watchlist</t>
-        </is>
-      </c>
-      <c r="E198" s="12" t="inlineStr">
-        <is>
-          <t>관심종목정보 조회 (코드를 |로 구분, 예: 005930|000660)</t>
-        </is>
-      </c>
-      <c r="F198" s="13" t="inlineStr">
-        <is>
-          <t>ka10095</t>
-        </is>
-      </c>
-      <c r="G198" s="12" t="inlineStr">
-        <is>
-          <t>CODES (필수)</t>
-        </is>
-      </c>
-      <c r="H198" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A198" s="14" t="inlineStr">
+        <is>
+          <t>stream</t>
+        </is>
+      </c>
+      <c r="B198" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C198" s="14" t="inlineStr">
+        <is>
+          <t>after-hours</t>
+        </is>
+      </c>
+      <c r="D198" s="14" t="inlineStr">
+        <is>
+          <t>kiwoom stream after-hours</t>
+        </is>
+      </c>
+      <c r="E198" s="14" t="inlineStr">
+        <is>
+          <t>주식시간외호가 실시간 (0E)</t>
+        </is>
+      </c>
+      <c r="F198" s="15" t="inlineStr"/>
+      <c r="G198" s="14" t="inlineStr">
+        <is>
+          <t>CODES (복수) (필수)</t>
+        </is>
+      </c>
+      <c r="H198" s="14" t="inlineStr">
+        <is>
+          <t>--raw (JSON 원본 출력)</t>
         </is>
       </c>
     </row>
@@ -8926,23 +8925,23 @@
       </c>
       <c r="C199" s="14" t="inlineStr">
         <is>
-          <t>after-hours</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="D199" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream after-hours</t>
+          <t>kiwoom stream balance</t>
         </is>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>주식시간외호가 실시간 (0E)</t>
+          <t>잔고 실시간 (04)</t>
         </is>
       </c>
       <c r="F199" s="15" t="inlineStr"/>
       <c r="G199" s="14" t="inlineStr">
         <is>
-          <t>CODES (복수) (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H199" s="14" t="inlineStr">
@@ -8964,23 +8963,23 @@
       </c>
       <c r="C200" s="14" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>best-bid</t>
         </is>
       </c>
       <c r="D200" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream balance</t>
+          <t>kiwoom stream best-bid</t>
         </is>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>잔고 실시간 (04)</t>
+          <t>주식우선호가 실시간 (0C)</t>
         </is>
       </c>
       <c r="F200" s="15" t="inlineStr"/>
       <c r="G200" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H200" s="14" t="inlineStr">
@@ -9002,23 +9001,24 @@
       </c>
       <c r="C201" s="14" t="inlineStr">
         <is>
-          <t>best-bid</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="D201" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream best-bid</t>
+          <t>kiwoom stream custom</t>
         </is>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>주식우선호가 실시간 (0C)</t>
+          <t>커스텀 실시간 타입으로 스트리밍</t>
         </is>
       </c>
       <c r="F201" s="15" t="inlineStr"/>
       <c r="G201" s="14" t="inlineStr">
         <is>
-          <t>CODES (복수) (필수)</t>
+          <t>TYPE_CODES (필수)
+CODES (복수) (선택)</t>
         </is>
       </c>
       <c r="H201" s="14" t="inlineStr">
@@ -9040,24 +9040,23 @@
       </c>
       <c r="C202" s="14" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>elw-indicator</t>
         </is>
       </c>
       <c r="D202" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream custom</t>
+          <t>kiwoom stream elw-indicator</t>
         </is>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>커스텀 실시간 타입으로 스트리밍</t>
+          <t>ELW 지표 실시간 (0u)</t>
         </is>
       </c>
       <c r="F202" s="15" t="inlineStr"/>
       <c r="G202" s="14" t="inlineStr">
         <is>
-          <t>TYPE_CODES (필수)
-CODES (복수) (선택)</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H202" s="14" t="inlineStr">
@@ -9079,17 +9078,17 @@
       </c>
       <c r="C203" s="14" t="inlineStr">
         <is>
-          <t>elw-indicator</t>
+          <t>elw-theory</t>
         </is>
       </c>
       <c r="D203" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream elw-indicator</t>
+          <t>kiwoom stream elw-theory</t>
         </is>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>ELW 지표 실시간 (0u)</t>
+          <t>ELW 이론가 실시간 (0m)</t>
         </is>
       </c>
       <c r="F203" s="15" t="inlineStr"/>
@@ -9117,17 +9116,17 @@
       </c>
       <c r="C204" s="14" t="inlineStr">
         <is>
-          <t>elw-theory</t>
+          <t>etf-nav</t>
         </is>
       </c>
       <c r="D204" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream elw-theory</t>
+          <t>kiwoom stream etf-nav</t>
         </is>
       </c>
       <c r="E204" s="14" t="inlineStr">
         <is>
-          <t>ELW 이론가 실시간 (0m)</t>
+          <t>ETF NAV 실시간 (0G)</t>
         </is>
       </c>
       <c r="F204" s="15" t="inlineStr"/>
@@ -9155,17 +9154,17 @@
       </c>
       <c r="C205" s="14" t="inlineStr">
         <is>
-          <t>etf-nav</t>
+          <t>expected</t>
         </is>
       </c>
       <c r="D205" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream etf-nav</t>
+          <t>kiwoom stream expected</t>
         </is>
       </c>
       <c r="E205" s="14" t="inlineStr">
         <is>
-          <t>ETF NAV 실시간 (0G)</t>
+          <t>주식예상체결 실시간 (0H)</t>
         </is>
       </c>
       <c r="F205" s="15" t="inlineStr"/>
@@ -9193,17 +9192,17 @@
       </c>
       <c r="C206" s="14" t="inlineStr">
         <is>
-          <t>expected</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="D206" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream expected</t>
+          <t>kiwoom stream gold</t>
         </is>
       </c>
       <c r="E206" s="14" t="inlineStr">
         <is>
-          <t>주식예상체결 실시간 (0H)</t>
+          <t>국제금환산가격 실시간 (0I)</t>
         </is>
       </c>
       <c r="F206" s="15" t="inlineStr"/>
@@ -9231,23 +9230,23 @@
       </c>
       <c r="C207" s="14" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>market-time</t>
         </is>
       </c>
       <c r="D207" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream gold</t>
+          <t>kiwoom stream market-time</t>
         </is>
       </c>
       <c r="E207" s="14" t="inlineStr">
         <is>
-          <t>국제금환산가격 실시간 (0I)</t>
+          <t>장시작시간 실시간 (0s)</t>
         </is>
       </c>
       <c r="F207" s="15" t="inlineStr"/>
       <c r="G207" s="14" t="inlineStr">
         <is>
-          <t>CODES (복수) (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H207" s="14" t="inlineStr">
@@ -9269,23 +9268,23 @@
       </c>
       <c r="C208" s="14" t="inlineStr">
         <is>
-          <t>market-time</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="D208" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream market-time</t>
+          <t>kiwoom stream multi</t>
         </is>
       </c>
       <c r="E208" s="14" t="inlineStr">
         <is>
-          <t>장시작시간 실시간 (0s)</t>
+          <t>주식체결+호가잔량 동시 스트리밍 (0B+0D)</t>
         </is>
       </c>
       <c r="F208" s="15" t="inlineStr"/>
       <c r="G208" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H208" s="14" t="inlineStr">
@@ -9307,23 +9306,23 @@
       </c>
       <c r="C209" s="14" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>order</t>
         </is>
       </c>
       <c r="D209" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream multi</t>
+          <t>kiwoom stream order</t>
         </is>
       </c>
       <c r="E209" s="14" t="inlineStr">
         <is>
-          <t>주식체결+호가잔량 동시 스트리밍 (0B+0D)</t>
+          <t>주문체결 실시간 (00)</t>
         </is>
       </c>
       <c r="F209" s="15" t="inlineStr"/>
       <c r="G209" s="14" t="inlineStr">
         <is>
-          <t>CODES (복수) (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H209" s="14" t="inlineStr">
@@ -9345,23 +9344,23 @@
       </c>
       <c r="C210" s="14" t="inlineStr">
         <is>
-          <t>order</t>
+          <t>orderbook</t>
         </is>
       </c>
       <c r="D210" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream order</t>
+          <t>kiwoom stream orderbook</t>
         </is>
       </c>
       <c r="E210" s="14" t="inlineStr">
         <is>
-          <t>주문체결 실시간 (00)</t>
+          <t>주식호가잔량 실시간 (0D)</t>
         </is>
       </c>
       <c r="F210" s="15" t="inlineStr"/>
       <c r="G210" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H210" s="14" t="inlineStr">
@@ -9383,17 +9382,17 @@
       </c>
       <c r="C211" s="14" t="inlineStr">
         <is>
-          <t>orderbook</t>
+          <t>price</t>
         </is>
       </c>
       <c r="D211" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream orderbook</t>
+          <t>kiwoom stream price</t>
         </is>
       </c>
       <c r="E211" s="14" t="inlineStr">
         <is>
-          <t>주식호가잔량 실시간 (0D)</t>
+          <t>주식기세 실시간 (0A)</t>
         </is>
       </c>
       <c r="F211" s="15" t="inlineStr"/>
@@ -9421,17 +9420,17 @@
       </c>
       <c r="C212" s="14" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>program</t>
         </is>
       </c>
       <c r="D212" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream price</t>
+          <t>kiwoom stream program</t>
         </is>
       </c>
       <c r="E212" s="14" t="inlineStr">
         <is>
-          <t>주식기세 실시간 (0A)</t>
+          <t>종목프로그램매매 실시간 (0w)</t>
         </is>
       </c>
       <c r="F212" s="15" t="inlineStr"/>
@@ -9459,17 +9458,17 @@
       </c>
       <c r="C213" s="14" t="inlineStr">
         <is>
-          <t>program</t>
+          <t>quote</t>
         </is>
       </c>
       <c r="D213" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream program</t>
+          <t>kiwoom stream quote</t>
         </is>
       </c>
       <c r="E213" s="14" t="inlineStr">
         <is>
-          <t>종목프로그램매매 실시간 (0w)</t>
+          <t>주식체결 실시간 (0B)</t>
         </is>
       </c>
       <c r="F213" s="15" t="inlineStr"/>
@@ -9497,17 +9496,17 @@
       </c>
       <c r="C214" s="14" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>sector-change</t>
         </is>
       </c>
       <c r="D214" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream quote</t>
+          <t>kiwoom stream sector-change</t>
         </is>
       </c>
       <c r="E214" s="14" t="inlineStr">
         <is>
-          <t>주식체결 실시간 (0B)</t>
+          <t>업종등락 실시간 (0U)</t>
         </is>
       </c>
       <c r="F214" s="15" t="inlineStr"/>
@@ -9535,17 +9534,17 @@
       </c>
       <c r="C215" s="14" t="inlineStr">
         <is>
-          <t>sector-change</t>
+          <t>sector-index</t>
         </is>
       </c>
       <c r="D215" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream sector-change</t>
+          <t>kiwoom stream sector-index</t>
         </is>
       </c>
       <c r="E215" s="14" t="inlineStr">
         <is>
-          <t>업종등락 실시간 (0U)</t>
+          <t>업종지수 실시간 (0J)</t>
         </is>
       </c>
       <c r="F215" s="15" t="inlineStr"/>
@@ -9573,17 +9572,17 @@
       </c>
       <c r="C216" s="14" t="inlineStr">
         <is>
-          <t>sector-index</t>
+          <t>stock-info</t>
         </is>
       </c>
       <c r="D216" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream sector-index</t>
+          <t>kiwoom stream stock-info</t>
         </is>
       </c>
       <c r="E216" s="14" t="inlineStr">
         <is>
-          <t>업종지수 실시간 (0J)</t>
+          <t>주식종목정보 실시간 (0g)</t>
         </is>
       </c>
       <c r="F216" s="15" t="inlineStr"/>
@@ -9611,17 +9610,17 @@
       </c>
       <c r="C217" s="14" t="inlineStr">
         <is>
-          <t>stock-info</t>
+          <t>trader</t>
         </is>
       </c>
       <c r="D217" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream stock-info</t>
+          <t>kiwoom stream trader</t>
         </is>
       </c>
       <c r="E217" s="14" t="inlineStr">
         <is>
-          <t>주식종목정보 실시간 (0g)</t>
+          <t>주식당일거래원 실시간 (0F)</t>
         </is>
       </c>
       <c r="F217" s="15" t="inlineStr"/>
@@ -9649,28 +9648,28 @@
       </c>
       <c r="C218" s="14" t="inlineStr">
         <is>
-          <t>trader</t>
+          <t>types</t>
         </is>
       </c>
       <c r="D218" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream trader</t>
+          <t>kiwoom stream types</t>
         </is>
       </c>
       <c r="E218" s="14" t="inlineStr">
         <is>
-          <t>주식당일거래원 실시간 (0F)</t>
+          <t>사용 가능한 실시간 타입 코드 목록</t>
         </is>
       </c>
       <c r="F218" s="15" t="inlineStr"/>
       <c r="G218" s="14" t="inlineStr">
         <is>
-          <t>CODES (복수) (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H218" s="14" t="inlineStr">
         <is>
-          <t>--raw (JSON 원본 출력)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9687,102 +9686,64 @@
       </c>
       <c r="C219" s="14" t="inlineStr">
         <is>
-          <t>types</t>
+          <t>vi</t>
         </is>
       </c>
       <c r="D219" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream types</t>
+          <t>kiwoom stream vi</t>
         </is>
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>사용 가능한 실시간 타입 코드 목록</t>
+          <t>VI발동/해제 실시간 (1h)</t>
         </is>
       </c>
       <c r="F219" s="15" t="inlineStr"/>
       <c r="G219" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H219" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>--raw (JSON 원본 출력)</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="14" t="inlineStr">
-        <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="B220" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C220" s="14" t="inlineStr">
-        <is>
-          <t>vi</t>
-        </is>
-      </c>
-      <c r="D220" s="14" t="inlineStr">
-        <is>
-          <t>kiwoom stream vi</t>
-        </is>
-      </c>
-      <c r="E220" s="14" t="inlineStr">
-        <is>
-          <t>VI발동/해제 실시간 (1h)</t>
-        </is>
-      </c>
-      <c r="F220" s="15" t="inlineStr"/>
-      <c r="G220" s="14" t="inlineStr">
+      <c r="A220" s="6" t="inlineStr">
+        <is>
+          <t>watch</t>
+        </is>
+      </c>
+      <c r="B220" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t>watch</t>
+        </is>
+      </c>
+      <c r="D220" s="6" t="inlineStr">
+        <is>
+          <t>kiwoom watch</t>
+        </is>
+      </c>
+      <c r="E220" s="6" t="inlineStr">
+        <is>
+          <t>실시간 종목 모니터링 (TUI 대시보드)</t>
+        </is>
+      </c>
+      <c r="F220" s="7" t="inlineStr"/>
+      <c r="G220" s="6" t="inlineStr">
         <is>
           <t>CODES (복수) (필수)</t>
         </is>
       </c>
-      <c r="H220" s="14" t="inlineStr">
-        <is>
-          <t>--raw (JSON 원본 출력)</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="6" t="inlineStr">
-        <is>
-          <t>watch</t>
-        </is>
-      </c>
-      <c r="B221" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C221" s="6" t="inlineStr">
-        <is>
-          <t>watch</t>
-        </is>
-      </c>
-      <c r="D221" s="6" t="inlineStr">
-        <is>
-          <t>kiwoom watch</t>
-        </is>
-      </c>
-      <c r="E221" s="6" t="inlineStr">
-        <is>
-          <t>실시간 종목 모니터링 (TUI 대시보드)</t>
-        </is>
-      </c>
-      <c r="F221" s="7" t="inlineStr"/>
-      <c r="G221" s="6" t="inlineStr">
-        <is>
-          <t>CODES (복수) (필수)</t>
-        </is>
-      </c>
-      <c r="H221" s="6" t="inlineStr">
+      <c r="H220" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9815,7 +9776,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
@@ -9885,7 +9845,7 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
@@ -9990,7 +9950,7 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/kiwoom_cli_commands.xlsx
+++ b/kiwoom_cli_commands.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체 명령어'!$A$1:$H$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체 명령어'!$A$1:$H$223</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H220"/>
+  <dimension ref="A1:H223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>접근토큰 발급</t>
+          <t>접근토큰 발급 (비밀번호 확인 후 암호화된 인증정보 사용)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>접근토큰 폐기</t>
+          <t>접근토큰 폐기 (비밀번호 확인 필요)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr"/>
@@ -1978,17 +1978,17 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>profiles</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>kiwoom config setup</t>
+          <t>kiwoom config profiles</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>초기 설정 (App Key, Secret Key, 도메인)</t>
+          <t>등록된 프로필 목록</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
@@ -1999,126 +1999,203 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>--appkey (키움 API App Key)
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>kiwoom config setup</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>초기 설정 (App Key, Secret Key, 도메인)</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>--profile 기본:default (프로필 이름)
+--appkey (키움 API App Key)
 --secretkey (키움 API Secret Key)
 --domain [prod, mock] 기본:mock (도메인 (prod: 실거래, mock: 모의투자))
 --account (기본 계좌번호)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>show</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>kiwoom config show</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>현재 설정 확인</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>kiwoom config use</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>기본 프로필 변경</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>PROFILE_NAME (필수)</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>dashboard</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>dashboard</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>kiwoom dashboard</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>대시보드: 계좌 요약 + 거래량 상위 종목</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>kt00004</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>elw</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>balance-rank</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>kiwoom market elw balance-rank</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>ELW 잔량 순위</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr"/>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr"/>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>--sort 기본:1 (정렬 (1=순매수잔량상위, 2=순매도잔량상위))
 --right-type 기본:000 (권리구분 (000=전체))
@@ -2126,39 +2203,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>elw</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>broker-top</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>kiwoom market elw broker-top</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>거래원별 ELW 순매매 상위</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr"/>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="F40" s="9" t="inlineStr"/>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>--issuer 기본:000000000000 (발행사코드)
 --vol-type (거래량구분)
@@ -2168,39 +2245,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>elw</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>change-rank</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>kiwoom market elw change-rank</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>ELW 등락율 순위</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr"/>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr"/>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>--sort 기본:1 (정렬 (1=상승률,2=상승폭,3=하락률,4=하락폭))
 --right-type 기본:000 (권리구분 (000=전체))
@@ -2208,77 +2285,77 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>elw</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>kiwoom market elw detail</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>ELW 종목 상세정보</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr"/>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr"/>
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>elw</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>disparity</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>kiwoom market elw disparity</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>ELW 괴리율</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr"/>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr"/>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>--issuer 기본:000000000000 (발행사코드)
 --underlying 기본:000000000000 (기초자산코드)
@@ -2288,82 +2365,6 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>elw</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>lp-daily</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>kiwoom market elw lp-daily</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>ELW LP 보유 일별 추이</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr"/>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>UNDERLYING_CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>--date *필수 (기준일자 (YYYYMMDD))</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>elw</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>proximity</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>kiwoom market elw proximity</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>ELW 근접율</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr"/>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
@@ -2377,26 +2378,102 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>lp-daily</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market elw search</t>
+          <t>kiwoom market elw lp-daily</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>ELW 조건 검색</t>
+          <t>ELW LP 보유 일별 추이</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr"/>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UNDERLYING_CODE (필수)</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>--date *필수 (기준일자 (YYYYMMDD))</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>elw</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>proximity</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>kiwoom market elw proximity</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>ELW 근접율</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr"/>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>elw</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>search</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>kiwoom market elw search</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>ELW 조건 검색</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr"/>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>--issuer 기본:000000000000 (발행사코드)
 --underlying 기본:000000000000 (기초자산코드)
@@ -2406,82 +2483,6 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>elw</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>sensitivity</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>kiwoom market elw sensitivity</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>ELW 민감도 지표</t>
-        </is>
-      </c>
-      <c r="F45" s="9" t="inlineStr"/>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H45" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>elw</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>sensitivity-daily</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>kiwoom market elw sensitivity-daily</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>ELW 일별 민감도 지표</t>
-        </is>
-      </c>
-      <c r="F46" s="9" t="inlineStr"/>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
@@ -2495,26 +2496,102 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>surge</t>
+          <t>sensitivity</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market elw surge</t>
+          <t>kiwoom market elw sensitivity</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>ELW 가격 급등락</t>
+          <t>ELW 민감도 지표</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr"/>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODE (필수)</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>elw</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>sensitivity-daily</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>kiwoom market elw sensitivity-daily</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>ELW 일별 민감도 지표</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr"/>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>elw</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>surge</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>kiwoom market elw surge</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>ELW 가격 급등락</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr"/>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>--type 기본:1 (등락구분 (1=급등, 2=급락))
 --time-type 기본:1 (시간구분 (1=분전, 2=일전))
@@ -2528,39 +2605,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>etf</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>kiwoom market etf all</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>ETF 전체 시세</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr"/>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="F50" s="9" t="inlineStr"/>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>--tax-type (과세유형 (0=전체))
 --nav (NAV대비 (0=전체))
@@ -2571,82 +2648,6 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>etf</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>kiwoom market etf daily</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>ETF 일별추이</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr"/>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>etf</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>daily-exec</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>kiwoom market etf daily-exec</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>ETF 일자별 체결</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="inlineStr"/>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H50" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
@@ -2660,17 +2661,17 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market etf info</t>
+          <t>kiwoom market etf daily</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>ETF 종목정보</t>
+          <t>ETF 일별추이</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr"/>
@@ -2698,17 +2699,17 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>returns</t>
+          <t>daily-exec</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market etf returns</t>
+          <t>kiwoom market etf daily-exec</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>ETF 수익율 조회</t>
+          <t>ETF 일자별 체결</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr"/>
@@ -2719,87 +2720,87 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>etf</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>kiwoom market etf info</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>ETF 종목정보</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr"/>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>etf</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>returns</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>kiwoom market etf returns</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>ETF 수익율 조회</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr"/>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
           <t>--index (ETF대상지수코드)
 --period (기간 (0=1주,1=1달,2=6개월,3=1년))</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>etf</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>time-exec</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>kiwoom market etf time-exec</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>ETF 시간대별 체결</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="inlineStr"/>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H53" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>etf</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>time-exec2</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>kiwoom market etf time-exec2</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>ETF 시간대별 체결 (상세)</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="inlineStr"/>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
@@ -2813,17 +2814,17 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>time-trend</t>
+          <t>time-exec</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market etf time-trend</t>
+          <t>kiwoom market etf time-exec</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>ETF 시간대별 추이</t>
+          <t>ETF 시간대별 체결</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr"/>
@@ -2851,17 +2852,17 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>time-trend2</t>
+          <t>time-exec2</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market etf time-trend2</t>
+          <t>kiwoom market etf time-exec2</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>ETF 시간대별 추이 (상세)</t>
+          <t>ETF 시간대별 체결 (상세)</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr"/>
@@ -2884,31 +2885,107 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>etf</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>chart-day</t>
+          <t>time-trend</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market gold chart-day</t>
+          <t>kiwoom market etf time-trend</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>금현물 일봉 차트</t>
+          <t>ETF 시간대별 추이</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODE (필수)</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>etf</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>time-trend2</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>kiwoom market etf time-trend2</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>ETF 시간대별 추이 (상세)</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr"/>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>chart-day</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>kiwoom market gold chart-day</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>금현물 일봉 차트</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr"/>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>--code 기본:M04020000 (종목코드)
 --date *필수 (기준일자 (YYYYMMDD))
@@ -2916,39 +2993,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>chart-minute</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>kiwoom market gold chart-minute</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>금현물 분봉 차트</t>
         </is>
       </c>
-      <c r="F58" s="9" t="inlineStr"/>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="8" t="inlineStr">
+      <c r="F60" s="9" t="inlineStr"/>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>--code 기본:M04020000 (종목코드)
 --scope 기본:1 (틱범위 (1,3,5,10,15,30,45,60))
@@ -2956,39 +3033,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>chart-month</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>kiwoom market gold chart-month</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>금현물 월봉 차트</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr"/>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="8" t="inlineStr">
+      <c r="F61" s="9" t="inlineStr"/>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
         <is>
           <t>--code 기본:M04020000 (종목코드)
 --date *필수 (기준일자 (YYYYMMDD))
@@ -2996,39 +3073,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>chart-tick</t>
         </is>
       </c>
-      <c r="D60" s="8" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>kiwoom market gold chart-tick</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>금현물 틱차트</t>
         </is>
       </c>
-      <c r="F60" s="9" t="inlineStr"/>
-      <c r="G60" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="8" t="inlineStr">
+      <c r="F62" s="9" t="inlineStr"/>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>--code 기본:M04020000 (종목코드)
 --scope 기본:1 (틱범위 (1,3,5,10,30))
@@ -3036,39 +3113,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>chart-week</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>kiwoom market gold chart-week</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>금현물 주봉 차트</t>
         </is>
       </c>
-      <c r="F61" s="9" t="inlineStr"/>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="8" t="inlineStr">
+      <c r="F63" s="9" t="inlineStr"/>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>--code 기본:M04020000 (종목코드)
 --date *필수 (기준일자 (YYYYMMDD))
@@ -3076,121 +3153,45 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="D62" s="8" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>kiwoom market gold daily</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>금현물 일별 추이</t>
         </is>
       </c>
-      <c r="F62" s="9" t="inlineStr"/>
-      <c r="G62" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="8" t="inlineStr">
+      <c r="F64" s="9" t="inlineStr"/>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>--code 기본:M04020000 (종목코드)
 --date *필수 (기준일자 (YYYYMMDD))</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>gold</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>executions</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>kiwoom market gold executions</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>금현물 체결 추이</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="inlineStr"/>
-      <c r="G63" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="8" t="inlineStr">
-        <is>
-          <t>--code 기본:M04020000 (종목코드 (M04020000=금99.99_1kg, M04020100=미니금99.99_100g))</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>gold</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>expected</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>kiwoom market gold expected</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>금현물 예상 체결</t>
-        </is>
-      </c>
-      <c r="F64" s="9" t="inlineStr"/>
-      <c r="G64" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="8" t="inlineStr">
-        <is>
-          <t>--code 기본:M04020000 (종목코드)</t>
-        </is>
-      </c>
-    </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
@@ -3204,17 +3205,17 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>investors</t>
+          <t>executions</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market gold investors</t>
+          <t>kiwoom market gold executions</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>금현물 투자자 현황</t>
+          <t>금현물 체결 추이</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr"/>
@@ -3225,7 +3226,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>--code 기본:M04020000 (종목코드 (M04020000=금99.99_1kg, M04020100=미니금99.99_100g))</t>
         </is>
       </c>
     </row>
@@ -3242,17 +3243,17 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>orderbook</t>
+          <t>expected</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market gold orderbook</t>
+          <t>kiwoom market gold expected</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>금현물 호가</t>
+          <t>금현물 예상 체결</t>
         </is>
       </c>
       <c r="F66" s="9" t="inlineStr"/>
@@ -3263,199 +3264,275 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
+          <t>--code 기본:M04020000 (종목코드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>investors</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>kiwoom market gold investors</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>금현물 투자자 현황</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr"/>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>orderbook</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>kiwoom market gold orderbook</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>금현물 호가</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr"/>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
           <t>--code 기본:M04020000 (종목코드)
 --scope 기본:1 (틱범위)</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>kiwoom market gold price</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr">
+      <c r="E69" s="8" t="inlineStr">
         <is>
           <t>금현물 시세정보</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr"/>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="inlineStr">
+      <c r="F69" s="9" t="inlineStr"/>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
         <is>
           <t>--code 기본:M04020000 (종목코드)</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>today-minute</t>
         </is>
       </c>
-      <c r="D68" s="8" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>kiwoom market gold today-minute</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>금현물 당일 분봉 차트</t>
         </is>
       </c>
-      <c r="F68" s="9" t="inlineStr"/>
-      <c r="G68" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="8" t="inlineStr">
+      <c r="F70" s="9" t="inlineStr"/>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
         <is>
           <t>--code 기본:M04020000 (종목코드)
 --scope 기본:1 (틱범위)</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>today-tick</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>kiwoom market gold today-tick</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="E71" s="8" t="inlineStr">
         <is>
           <t>금현물 당일 틱차트</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr"/>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="8" t="inlineStr">
+      <c r="F71" s="9" t="inlineStr"/>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
         <is>
           <t>--code 기본:M04020000 (종목코드)
 --scope 기본:1 (틱범위 (1,3,5,10,30))</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>program</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>arbitrage-balance</t>
         </is>
       </c>
-      <c r="D70" s="8" t="inlineStr">
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>kiwoom market program arbitrage-balance</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>프로그램매매 차익잔고 추이</t>
         </is>
       </c>
-      <c r="F70" s="9" t="inlineStr"/>
-      <c r="G70" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="8" t="inlineStr">
+      <c r="F72" s="9" t="inlineStr"/>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
         <is>
           <t>--date *필수 (날짜 (YYYYMMDD))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>program</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>cumulative</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>kiwoom market program cumulative</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
+      <c r="E73" s="8" t="inlineStr">
         <is>
           <t>프로그램매매 누적 추이</t>
         </is>
       </c>
-      <c r="F71" s="9" t="inlineStr"/>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" s="8" t="inlineStr">
+      <c r="F73" s="9" t="inlineStr"/>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
         <is>
           <t>--date *필수 (날짜 (YYYYMMDD))
 --unit 기본:1 (금액/수량)
@@ -3464,39 +3541,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>program</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>daily-trend</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>kiwoom market program daily-trend</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
+      <c r="E74" s="8" t="inlineStr">
         <is>
           <t>프로그램매매 추이 (일자별)</t>
         </is>
       </c>
-      <c r="F72" s="9" t="inlineStr"/>
-      <c r="G72" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" s="8" t="inlineStr">
+      <c r="F74" s="9" t="inlineStr"/>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
         <is>
           <t>--date *필수 (날짜 (YYYYMMDD))
 --unit 기본:1 (금액/수량)
@@ -3506,117 +3583,117 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>program</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>stock-daily</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>kiwoom market program stock-daily</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>종목 일별 프로그램매매 추이</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr"/>
-      <c r="G73" s="8" t="inlineStr">
+      <c r="F75" s="9" t="inlineStr"/>
+      <c r="G75" s="8" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H73" s="8" t="inlineStr">
+      <c r="H75" s="8" t="inlineStr">
         <is>
           <t>--unit (금액/수량 (선택))
 --date (날짜 (YYYYMMDD, 선택))</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>program</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>stock-time</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>kiwoom market program stock-time</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>종목 시간별 프로그램매매 추이</t>
         </is>
       </c>
-      <c r="F74" s="9" t="inlineStr"/>
-      <c r="G74" s="8" t="inlineStr">
+      <c r="F76" s="9" t="inlineStr"/>
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H74" s="8" t="inlineStr">
+      <c r="H76" s="8" t="inlineStr">
         <is>
           <t>--unit 기본:1 (금액/수량)
 --date (날짜 (YYYYMMDD))</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>program</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>time-trend</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>kiwoom market program time-trend</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>프로그램매매 추이 (시간대별)</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr"/>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="inlineStr">
+      <c r="F77" s="9" t="inlineStr"/>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>--date *필수 (날짜 (YYYYMMDD))
 --unit 기본:1 (금액/수량 (1=금액백만원, 2=수량천주))
@@ -3626,39 +3703,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>afterhours-change</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank afterhours-change</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>시간외 단일가 등락율 순위</t>
         </is>
       </c>
-      <c r="F76" s="9" t="inlineStr"/>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="8" t="inlineStr">
+      <c r="F78" s="9" t="inlineStr"/>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --sort 기본:1 (정렬 (1=상승률,2=상승폭,3=하락률,4=하락폭,5=보합))
@@ -3669,39 +3746,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank amount</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>거래대금 상위</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr"/>
-      <c r="G77" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="inlineStr">
+      <c r="F79" s="9" t="inlineStr"/>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --include-managed (관리종목포함 (0=미포함, 1=포함))
@@ -3709,39 +3786,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="8" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>balance-rate-surge</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank balance-rate-surge</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="E80" s="8" t="inlineStr">
         <is>
           <t>잔량율 급증</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr"/>
-      <c r="G78" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="8" t="inlineStr">
+      <c r="F80" s="9" t="inlineStr"/>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
         <is>
           <t>--market [kospi, kosdaq] 기본:kospi (시장구분)
 --type 기본:1 (비율구분 (1=매수/매도비율, 2=매도/매수비율))
@@ -3752,39 +3829,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>broker-by-stock</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank broker-by-stock</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t>종목별 증권사 순위</t>
         </is>
       </c>
-      <c r="F79" s="9" t="inlineStr"/>
-      <c r="G79" s="8" t="inlineStr">
+      <c r="F81" s="9" t="inlineStr"/>
+      <c r="G81" s="8" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H79" s="8" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr">
         <is>
           <t>--type 기본:1 (조회구분 (1=순매도순위, 2=순매수순위))
 --from (시작일자 (YYYYMMDD))
@@ -3793,39 +3870,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>broker-top</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank broker-top</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr">
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>증권사별 매매 상위</t>
         </is>
       </c>
-      <c r="F80" s="9" t="inlineStr"/>
-      <c r="G80" s="8" t="inlineStr">
+      <c r="F82" s="9" t="inlineStr"/>
+      <c r="G82" s="8" t="inlineStr">
         <is>
           <t>BROKER_CODE (필수)</t>
         </is>
       </c>
-      <c r="H80" s="8" t="inlineStr">
+      <c r="H82" s="8" t="inlineStr">
         <is>
           <t>--vol-type (거래량구분)
 --type 기본:1 (매매구분 (1=순매수, 2=순매도))
@@ -3834,39 +3911,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank change</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
+      <c r="E83" s="8" t="inlineStr">
         <is>
           <t>전일대비 등락률 상위</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr"/>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="8" t="inlineStr">
+      <c r="F83" s="9" t="inlineStr"/>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --sort 기본:1 (정렬 (1=상승률,2=상승폭,3=하락률,4=하락폭,5=보합))
@@ -3880,39 +3957,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="8" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>credit-ratio</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank credit-ratio</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>신용비율 상위</t>
         </is>
       </c>
-      <c r="F82" s="9" t="inlineStr"/>
-      <c r="G82" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="8" t="inlineStr">
+      <c r="F84" s="9" t="inlineStr"/>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --vol-type (거래량구분)
@@ -3923,39 +4000,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>expected-change</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank expected-change</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>예상체결 등락률 상위</t>
         </is>
       </c>
-      <c r="F83" s="9" t="inlineStr"/>
-      <c r="G83" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="8" t="inlineStr">
+      <c r="F85" s="9" t="inlineStr"/>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --sort 기본:1 (정렬 (1=상승률,2=상승폭,3=보합,4=하락률,5=하락폭,6=체결량,7=상한,8=하한))
@@ -3967,39 +4044,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>foreign-broker</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank foreign-broker</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>외국계 창구 매매 상위</t>
         </is>
       </c>
-      <c r="F84" s="9" t="inlineStr"/>
-      <c r="G84" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="8" t="inlineStr">
+      <c r="F86" s="9" t="inlineStr"/>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --period (기간)
@@ -4009,39 +4086,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="8" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>foreign-consecutive</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank foreign-consecutive</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>외인 연속 순매매 상위</t>
         </is>
       </c>
-      <c r="F85" s="9" t="inlineStr"/>
-      <c r="G85" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="8" t="inlineStr">
+      <c r="F87" s="9" t="inlineStr"/>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --type 기본:2 (구분 (1=연속순매도, 2=연속순매수))
@@ -4050,39 +4127,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>foreign-exhaust</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank foreign-exhaust</t>
         </is>
       </c>
-      <c r="E86" s="8" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>외인 한도소진율 증가 상위</t>
         </is>
       </c>
-      <c r="F86" s="9" t="inlineStr"/>
-      <c r="G86" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" s="8" t="inlineStr">
+      <c r="F88" s="9" t="inlineStr"/>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --period (기간 (0=당일,1=전일,5=5일,10,20,60))
@@ -4090,39 +4167,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="8" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C87" s="8" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>foreign-inst</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank foreign-inst</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>외국인/기관 매매 상위</t>
         </is>
       </c>
-      <c r="F87" s="9" t="inlineStr"/>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" s="8" t="inlineStr">
+      <c r="F89" s="9" t="inlineStr"/>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --unit 기본:1 (금액/수량 (1=금액, 2=수량))
@@ -4132,39 +4209,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>foreign-period</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank foreign-period</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>외인 기간별 매매 상위</t>
         </is>
       </c>
-      <c r="F88" s="9" t="inlineStr"/>
-      <c r="G88" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" s="8" t="inlineStr">
+      <c r="F90" s="9" t="inlineStr"/>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --type 기본:2 (매매구분 (1=순매도, 2=순매수, 3=순매매))
@@ -4173,77 +4250,77 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="D91" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank hot</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>실시간 종목 조회 순위</t>
         </is>
       </c>
-      <c r="F89" s="9" t="inlineStr"/>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" s="8" t="inlineStr">
+      <c r="F91" s="9" t="inlineStr"/>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
         <is>
           <t>--period [1, 2, 3, 4, 5] 기본:4 (구분 (1=1분, 2=10분, 3=1시간, 4=당일누적, 5=30초))</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
         <is>
           <t>investor-top</t>
         </is>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="D92" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank investor-top</t>
         </is>
       </c>
-      <c r="E90" s="8" t="inlineStr">
+      <c r="E92" s="8" t="inlineStr">
         <is>
           <t>장중 투자자별 매매 상위</t>
         </is>
       </c>
-      <c r="F90" s="9" t="inlineStr"/>
-      <c r="G90" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" s="8" t="inlineStr">
+      <c r="F92" s="9" t="inlineStr"/>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
         <is>
           <t>--type 기본:1 (매매구분 (1=순매수, 2=순매도))
 --market [all, kospi, kosdaq] 기본:all (시장구분)
@@ -4252,39 +4329,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="8" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C91" s="8" t="inlineStr">
+      <c r="C93" s="8" t="inlineStr">
         <is>
           <t>limit</t>
         </is>
       </c>
-      <c r="D91" s="8" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank limit</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
+      <c r="E93" s="8" t="inlineStr">
         <is>
           <t>상하한가 순위</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr"/>
-      <c r="G91" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="8" t="inlineStr">
+      <c r="F93" s="9" t="inlineStr"/>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --type 기본:1 (상하한구분 (1=상한,2=상승,3=보합,4=하한,5=하락,6=전일상한,7=전일하한))
@@ -4297,77 +4374,77 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C92" s="8" t="inlineStr">
+      <c r="C94" s="8" t="inlineStr">
         <is>
           <t>major-trader</t>
         </is>
       </c>
-      <c r="D92" s="8" t="inlineStr">
+      <c r="D94" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank major-trader</t>
         </is>
       </c>
-      <c r="E92" s="8" t="inlineStr">
+      <c r="E94" s="8" t="inlineStr">
         <is>
           <t>당일 주요 거래원</t>
         </is>
       </c>
-      <c r="F92" s="9" t="inlineStr"/>
-      <c r="G92" s="8" t="inlineStr">
+      <c r="F94" s="9" t="inlineStr"/>
+      <c r="G94" s="8" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H92" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C93" s="8" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>near-highlow</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank near-highlow</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr">
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t>고저가근접 순위</t>
         </is>
       </c>
-      <c r="F93" s="9" t="inlineStr"/>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="inlineStr">
+      <c r="F95" s="9" t="inlineStr"/>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr">
         <is>
           <t>--type 기본:1 (구분 (1=고가, 2=저가))
 --rate 기본:05 (근접율 (05,10,15,20,25,30))
@@ -4379,39 +4456,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="8" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C94" s="8" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
         <is>
           <t>net-buyer</t>
         </is>
       </c>
-      <c r="D94" s="8" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank net-buyer</t>
         </is>
       </c>
-      <c r="E94" s="8" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>순매수 거래원 순위</t>
         </is>
       </c>
-      <c r="F94" s="9" t="inlineStr"/>
-      <c r="G94" s="8" t="inlineStr">
+      <c r="F96" s="9" t="inlineStr"/>
+      <c r="G96" s="8" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H94" s="8" t="inlineStr">
+      <c r="H96" s="8" t="inlineStr">
         <is>
           <t>--from (시작일자 (YYYYMMDD))
 --to (종료일자 (YYYYMMDD))
@@ -4422,39 +4499,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="8" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C95" s="8" t="inlineStr">
+      <c r="C97" s="8" t="inlineStr">
         <is>
           <t>new-highlow</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank new-highlow</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
+      <c r="E97" s="8" t="inlineStr">
         <is>
           <t>신고저가 순위</t>
         </is>
       </c>
-      <c r="F95" s="9" t="inlineStr"/>
-      <c r="G95" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" s="8" t="inlineStr">
+      <c r="F97" s="9" t="inlineStr"/>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --type 기본:1 (신고저구분 (1=신고가, 2=신저가))
@@ -4468,39 +4545,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="8" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr">
+      <c r="C98" s="8" t="inlineStr">
         <is>
           <t>orderbook-surge</t>
         </is>
       </c>
-      <c r="D96" s="8" t="inlineStr">
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank orderbook-surge</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr">
+      <c r="E98" s="8" t="inlineStr">
         <is>
           <t>호가잔량 급증</t>
         </is>
       </c>
-      <c r="F96" s="9" t="inlineStr"/>
-      <c r="G96" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H96" s="8" t="inlineStr">
+      <c r="F98" s="9" t="inlineStr"/>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="inlineStr">
         <is>
           <t>--market [kospi, kosdaq] 기본:kospi (시장구분)
 --type 기본:1 (매매구분 (1=매수잔량, 2=매도잔량))
@@ -4512,39 +4589,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="8" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C97" s="8" t="inlineStr">
+      <c r="C99" s="8" t="inlineStr">
         <is>
           <t>orderbook-top</t>
         </is>
       </c>
-      <c r="D97" s="8" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank orderbook-top</t>
         </is>
       </c>
-      <c r="E97" s="8" t="inlineStr">
+      <c r="E99" s="8" t="inlineStr">
         <is>
           <t>호가잔량 상위</t>
         </is>
       </c>
-      <c r="F97" s="9" t="inlineStr"/>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="8" t="inlineStr">
+      <c r="F99" s="9" t="inlineStr"/>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr">
         <is>
           <t>--market [kospi, kosdaq] 기본:kospi (시장구분)
 --sort 기본:1 (정렬 (1=순매수잔량순,2=순매도잔량순,3=매수비율순,4=매도비율순))
@@ -4555,39 +4632,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="8" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C98" s="8" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>prev-volume</t>
         </is>
       </c>
-      <c r="D98" s="8" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank prev-volume</t>
         </is>
       </c>
-      <c r="E98" s="8" t="inlineStr">
+      <c r="E100" s="8" t="inlineStr">
         <is>
           <t>전일 거래량 상위</t>
         </is>
       </c>
-      <c r="F98" s="9" t="inlineStr"/>
-      <c r="G98" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H98" s="8" t="inlineStr">
+      <c r="F100" s="9" t="inlineStr"/>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --type 기본:1 (조회구분 (1=전일거래량, 2=전일거래대금))
@@ -4597,39 +4674,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="8" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C99" s="8" t="inlineStr">
+      <c r="C101" s="8" t="inlineStr">
         <is>
           <t>same-net-trade</t>
         </is>
       </c>
-      <c r="D99" s="8" t="inlineStr">
+      <c r="D101" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank same-net-trade</t>
         </is>
       </c>
-      <c r="E99" s="8" t="inlineStr">
+      <c r="E101" s="8" t="inlineStr">
         <is>
           <t>동일 순매매 순위</t>
         </is>
       </c>
-      <c r="F99" s="9" t="inlineStr"/>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="8" t="inlineStr">
+      <c r="F101" s="9" t="inlineStr"/>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to (종료일자 (YYYYMMDD))
@@ -4641,39 +4718,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="8" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C100" s="8" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr">
         <is>
           <t>surge</t>
         </is>
       </c>
-      <c r="D100" s="8" t="inlineStr">
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank surge</t>
         </is>
       </c>
-      <c r="E100" s="8" t="inlineStr">
+      <c r="E102" s="8" t="inlineStr">
         <is>
           <t>가격급등락 순위</t>
         </is>
       </c>
-      <c r="F100" s="9" t="inlineStr"/>
-      <c r="G100" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" s="8" t="inlineStr">
+      <c r="F102" s="9" t="inlineStr"/>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --type 기본:1 (등락구분 (1=급등, 2=급락))
@@ -4688,77 +4765,77 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C101" s="8" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>top-exit</t>
         </is>
       </c>
-      <c r="D101" s="8" t="inlineStr">
+      <c r="D103" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank top-exit</t>
         </is>
       </c>
-      <c r="E101" s="8" t="inlineStr">
+      <c r="E103" s="8" t="inlineStr">
         <is>
           <t>당일 상위 이탈원</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr"/>
-      <c r="G101" s="8" t="inlineStr">
+      <c r="F103" s="9" t="inlineStr"/>
+      <c r="G103" s="8" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H101" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="8" t="inlineStr">
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C102" s="8" t="inlineStr">
+      <c r="C104" s="8" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="D102" s="8" t="inlineStr">
+      <c r="D104" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank volume</t>
         </is>
       </c>
-      <c r="E102" s="8" t="inlineStr">
+      <c r="E104" s="8" t="inlineStr">
         <is>
           <t>당일 거래량 상위</t>
         </is>
       </c>
-      <c r="F102" s="9" t="inlineStr"/>
-      <c r="G102" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" s="8" t="inlineStr">
+      <c r="F104" s="9" t="inlineStr"/>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --sort 기본:1 (정렬 (1=거래량,2=거래회전율,3=거래대금))
@@ -4772,39 +4849,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="8" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="C103" s="8" t="inlineStr">
+      <c r="C105" s="8" t="inlineStr">
         <is>
           <t>volume-surge</t>
         </is>
       </c>
-      <c r="D103" s="8" t="inlineStr">
+      <c r="D105" s="8" t="inlineStr">
         <is>
           <t>kiwoom market rank volume-surge</t>
         </is>
       </c>
-      <c r="E103" s="8" t="inlineStr">
+      <c r="E105" s="8" t="inlineStr">
         <is>
           <t>거래량 급증</t>
         </is>
       </c>
-      <c r="F103" s="9" t="inlineStr"/>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="8" t="inlineStr">
+      <c r="F105" s="9" t="inlineStr"/>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
 --sort 기본:1 (정렬 (1=급증량,2=급증률,3=급감량,4=급감률))
@@ -4817,159 +4894,83 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="8" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>sector chart</t>
         </is>
       </c>
-      <c r="C104" s="8" t="inlineStr">
+      <c r="C106" s="8" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="D104" s="8" t="inlineStr">
+      <c r="D106" s="8" t="inlineStr">
         <is>
           <t>kiwoom market sector chart day</t>
         </is>
       </c>
-      <c r="E104" s="8" t="inlineStr">
+      <c r="E106" s="8" t="inlineStr">
         <is>
           <t>업종 일봉 차트</t>
         </is>
       </c>
-      <c r="F104" s="9" t="inlineStr"/>
-      <c r="G104" s="8" t="inlineStr">
+      <c r="F106" s="9" t="inlineStr"/>
+      <c r="G106" s="8" t="inlineStr">
         <is>
           <t>INDS_CD (필수)</t>
         </is>
       </c>
-      <c r="H104" s="8" t="inlineStr">
+      <c r="H106" s="8" t="inlineStr">
         <is>
           <t>--date *필수 (기준일자 (YYYYMMDD))</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="8" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>sector chart</t>
         </is>
       </c>
-      <c r="C105" s="8" t="inlineStr">
+      <c r="C107" s="8" t="inlineStr">
         <is>
           <t>minute</t>
         </is>
       </c>
-      <c r="D105" s="8" t="inlineStr">
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>kiwoom market sector chart minute</t>
         </is>
       </c>
-      <c r="E105" s="8" t="inlineStr">
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>업종 분봉 차트</t>
         </is>
       </c>
-      <c r="F105" s="9" t="inlineStr"/>
-      <c r="G105" s="8" t="inlineStr">
+      <c r="F107" s="9" t="inlineStr"/>
+      <c r="G107" s="8" t="inlineStr">
         <is>
           <t>INDS_CD (필수)</t>
         </is>
       </c>
-      <c r="H105" s="8" t="inlineStr">
+      <c r="H107" s="8" t="inlineStr">
         <is>
           <t>--scope 기본:1 (틱범위 (1,3,5,10,30))
 --date (기준일자 (YYYYMMDD))</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>sector chart</t>
-        </is>
-      </c>
-      <c r="C106" s="8" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="inlineStr">
-        <is>
-          <t>kiwoom market sector chart month</t>
-        </is>
-      </c>
-      <c r="E106" s="8" t="inlineStr">
-        <is>
-          <t>업종 월봉 차트</t>
-        </is>
-      </c>
-      <c r="F106" s="9" t="inlineStr"/>
-      <c r="G106" s="8" t="inlineStr">
-        <is>
-          <t>INDS_CD (필수)</t>
-        </is>
-      </c>
-      <c r="H106" s="8" t="inlineStr">
-        <is>
-          <t>--date *필수 (기준일자 (YYYYMMDD))</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="8" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>sector chart</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="inlineStr">
-        <is>
-          <t>tick</t>
-        </is>
-      </c>
-      <c r="D107" s="8" t="inlineStr">
-        <is>
-          <t>kiwoom market sector chart tick</t>
-        </is>
-      </c>
-      <c r="E107" s="8" t="inlineStr">
-        <is>
-          <t>업종 틱차트</t>
-        </is>
-      </c>
-      <c r="F107" s="9" t="inlineStr"/>
-      <c r="G107" s="8" t="inlineStr">
-        <is>
-          <t>INDS_CD (필수)</t>
-        </is>
-      </c>
-      <c r="H107" s="8" t="inlineStr">
-        <is>
-          <t>--scope 기본:1 (틱범위 (1,3,5,10,30))</t>
-        </is>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
@@ -4983,17 +4984,17 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>week</t>
+          <t>month</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market sector chart week</t>
+          <t>kiwoom market sector chart month</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>업종 주봉 차트</t>
+          <t>업종 월봉 차트</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr"/>
@@ -5021,17 +5022,17 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>tick</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market sector chart year</t>
+          <t>kiwoom market sector chart tick</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>업종 년봉 차트</t>
+          <t>업종 틱차트</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr"/>
@@ -5042,7 +5043,7 @@
       </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
-          <t>--date *필수 (기준일자 (YYYYMMDD))</t>
+          <t>--scope 기본:1 (틱범위 (1,3,5,10,30))</t>
         </is>
       </c>
     </row>
@@ -5054,33 +5055,33 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>sector</t>
+          <t>sector chart</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>codes</t>
+          <t>week</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market sector codes</t>
+          <t>kiwoom market sector chart week</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>업종코드 리스트</t>
+          <t>업종 주봉 차트</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr"/>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INDS_CD (필수)</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>--market (시장구분 (0=코스피,1=코스닥,2=KOSPI200,4=KOSPI100,7=KRX100))</t>
+          <t>--date *필수 (기준일자 (YYYYMMDD))</t>
         </is>
       </c>
     </row>
@@ -5092,22 +5093,22 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>sector</t>
+          <t>sector chart</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>year</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market sector current</t>
+          <t>kiwoom market sector chart year</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>업종 현재가 조회</t>
+          <t>업종 년봉 차트</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr"/>
@@ -5118,7 +5119,7 @@
       </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>--market (시장구분 (0=코스피, 1=코스닥, 2=코스피200))</t>
+          <t>--date *필수 (기준일자 (YYYYMMDD))</t>
         </is>
       </c>
     </row>
@@ -5135,28 +5136,28 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>codes</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market sector daily</t>
+          <t>kiwoom market sector codes</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>업종 현재가 일별</t>
+          <t>업종코드 리스트</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr"/>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>INDS_CD (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
-          <t>--market (시장구분)</t>
+          <t>--market (시장구분 (0=코스피,1=코스닥,2=KOSPI200,4=KOSPI100,7=KRX100))</t>
         </is>
       </c>
     </row>
@@ -5173,28 +5174,28 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>current</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market sector index</t>
+          <t>kiwoom market sector current</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>전업종 지수</t>
+          <t>업종 현재가 조회</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr"/>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INDS_CD (필수)</t>
         </is>
       </c>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>--inds-cd 기본:001 (업종코드 (001=KOSPI종합, 101=KOSDAQ종합))</t>
+          <t>--market (시장구분 (0=코스피, 1=코스닥, 2=코스피200))</t>
         </is>
       </c>
     </row>
@@ -5211,26 +5212,102 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>investor</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>kiwoom market sector investor</t>
+          <t>kiwoom market sector daily</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>업종별 투자자 순매수</t>
+          <t>업종 현재가 일별</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr"/>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INDS_CD (필수)</t>
         </is>
       </c>
       <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>--market (시장구분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>kiwoom market sector index</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>전업종 지수</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr"/>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>--inds-cd 기본:001 (업종코드 (001=KOSPI종합, 101=KOSDAQ종합))</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>investor</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>kiwoom market sector investor</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>업종별 투자자 순매수</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr"/>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" s="8" t="inlineStr">
         <is>
           <t>--market [kospi, kosdaq] 기본:kospi (시장구분)
 --unit (금액/수량 (0=금액, 1=수량))
@@ -5239,116 +5316,116 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="8" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C115" s="8" t="inlineStr">
+      <c r="C117" s="8" t="inlineStr">
         <is>
           <t>program</t>
         </is>
       </c>
-      <c r="D115" s="8" t="inlineStr">
+      <c r="D117" s="8" t="inlineStr">
         <is>
           <t>kiwoom market sector program</t>
         </is>
       </c>
-      <c r="E115" s="8" t="inlineStr">
+      <c r="E117" s="8" t="inlineStr">
         <is>
           <t>업종 프로그램매매</t>
         </is>
       </c>
-      <c r="F115" s="9" t="inlineStr"/>
-      <c r="G115" s="8" t="inlineStr">
+      <c r="F117" s="9" t="inlineStr"/>
+      <c r="G117" s="8" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H115" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="8" t="inlineStr">
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B118" s="8" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C116" s="8" t="inlineStr">
+      <c r="C118" s="8" t="inlineStr">
         <is>
           <t>stocks</t>
         </is>
       </c>
-      <c r="D116" s="8" t="inlineStr">
+      <c r="D118" s="8" t="inlineStr">
         <is>
           <t>kiwoom market sector stocks</t>
         </is>
       </c>
-      <c r="E116" s="8" t="inlineStr">
+      <c r="E118" s="8" t="inlineStr">
         <is>
           <t>업종별 주가</t>
         </is>
       </c>
-      <c r="F116" s="9" t="inlineStr"/>
-      <c r="G116" s="8" t="inlineStr">
+      <c r="F118" s="9" t="inlineStr"/>
+      <c r="G118" s="8" t="inlineStr">
         <is>
           <t>INDS_CD (필수)</t>
         </is>
       </c>
-      <c r="H116" s="8" t="inlineStr">
+      <c r="H118" s="8" t="inlineStr">
         <is>
           <t>--market (시장구분)
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="8" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>theme</t>
         </is>
       </c>
-      <c r="C117" s="8" t="inlineStr">
+      <c r="C119" s="8" t="inlineStr">
         <is>
           <t>groups</t>
         </is>
       </c>
-      <c r="D117" s="8" t="inlineStr">
+      <c r="D119" s="8" t="inlineStr">
         <is>
           <t>kiwoom market theme groups</t>
         </is>
       </c>
-      <c r="E117" s="8" t="inlineStr">
+      <c r="E119" s="8" t="inlineStr">
         <is>
           <t>테마 그룹별 조회</t>
         </is>
       </c>
-      <c r="F117" s="9" t="inlineStr"/>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H117" s="8" t="inlineStr">
+      <c r="F119" s="9" t="inlineStr"/>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr">
         <is>
           <t>--type (검색구분 (0=전체, 1=테마검색, 2=종목검색))
 --code (종목코드 (종목검색시))
@@ -5359,83 +5436,83 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="8" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="8" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B120" s="8" t="inlineStr">
         <is>
           <t>theme</t>
         </is>
       </c>
-      <c r="C118" s="8" t="inlineStr">
+      <c r="C120" s="8" t="inlineStr">
         <is>
           <t>stocks</t>
         </is>
       </c>
-      <c r="D118" s="8" t="inlineStr">
+      <c r="D120" s="8" t="inlineStr">
         <is>
           <t>kiwoom market theme stocks</t>
         </is>
       </c>
-      <c r="E118" s="8" t="inlineStr">
+      <c r="E120" s="8" t="inlineStr">
         <is>
           <t>테마 구성종목 조회</t>
         </is>
       </c>
-      <c r="F118" s="9" t="inlineStr"/>
-      <c r="G118" s="8" t="inlineStr">
+      <c r="F120" s="9" t="inlineStr"/>
+      <c r="G120" s="8" t="inlineStr">
         <is>
           <t>THEME_CODE (필수)</t>
         </is>
       </c>
-      <c r="H118" s="8" t="inlineStr">
+      <c r="H120" s="8" t="inlineStr">
         <is>
           <t>--date-type 기본:1 (날짜구분 (1~99일))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="10" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B119" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="10" t="inlineStr">
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
         <is>
           <t>buy</t>
         </is>
       </c>
-      <c r="D119" s="10" t="inlineStr">
+      <c r="D121" s="10" t="inlineStr">
         <is>
           <t>kiwoom order buy</t>
         </is>
       </c>
-      <c r="E119" s="10" t="inlineStr">
+      <c r="E121" s="10" t="inlineStr">
         <is>
           <t>주식 매수주문 (kt10000)</t>
         </is>
       </c>
-      <c r="F119" s="11" t="inlineStr">
+      <c r="F121" s="11" t="inlineStr">
         <is>
           <t>kt10000</t>
         </is>
       </c>
-      <c r="G119" s="10" t="inlineStr">
+      <c r="G121" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)
 QTY (필수)</t>
         </is>
       </c>
-      <c r="H119" s="10" t="inlineStr">
+      <c r="H121" s="10" t="inlineStr">
         <is>
           <t>--price (주문가격 (시장가 주문시 생략))
 --type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
@@ -5445,44 +5522,44 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="10" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B120" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="10" t="inlineStr">
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
         <is>
           <t>cancel</t>
         </is>
       </c>
-      <c r="D120" s="10" t="inlineStr">
+      <c r="D122" s="10" t="inlineStr">
         <is>
           <t>kiwoom order cancel</t>
         </is>
       </c>
-      <c r="E120" s="10" t="inlineStr">
+      <c r="E122" s="10" t="inlineStr">
         <is>
           <t>주식 취소주문 (kt10003)</t>
         </is>
       </c>
-      <c r="F120" s="11" t="inlineStr">
+      <c r="F122" s="11" t="inlineStr">
         <is>
           <t>kt10003</t>
         </is>
       </c>
-      <c r="G120" s="10" t="inlineStr">
+      <c r="G122" s="10" t="inlineStr">
         <is>
           <t>ORIG_ORDER_NO (필수)
 CODE (필수)</t>
         </is>
       </c>
-      <c r="H120" s="10" t="inlineStr">
+      <c r="H122" s="10" t="inlineStr">
         <is>
           <t>--qty (취소수량 (0=전량취소))
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
@@ -5490,128 +5567,128 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="10" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B121" s="10" t="inlineStr">
+      <c r="B123" s="10" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="C121" s="10" t="inlineStr">
+      <c r="C123" s="10" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="D121" s="10" t="inlineStr">
+      <c r="D123" s="10" t="inlineStr">
         <is>
           <t>kiwoom order condition list</t>
         </is>
       </c>
-      <c r="E121" s="10" t="inlineStr">
+      <c r="E123" s="10" t="inlineStr">
         <is>
           <t>조건검색 목록조회 (ka10171)</t>
         </is>
       </c>
-      <c r="F121" s="11" t="inlineStr">
+      <c r="F123" s="11" t="inlineStr">
         <is>
           <t>ka10171</t>
         </is>
       </c>
-      <c r="G121" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H121" s="10" t="inlineStr">
+      <c r="G123" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" s="10" t="inlineStr">
         <is>
           <t>--confirm *필수 (조회 확인 (필수))</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="10" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B122" s="10" t="inlineStr">
+      <c r="B124" s="10" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="C122" s="10" t="inlineStr">
+      <c r="C124" s="10" t="inlineStr">
         <is>
           <t>realtime</t>
         </is>
       </c>
-      <c r="D122" s="10" t="inlineStr">
+      <c r="D124" s="10" t="inlineStr">
         <is>
           <t>kiwoom order condition realtime</t>
         </is>
       </c>
-      <c r="E122" s="10" t="inlineStr">
+      <c r="E124" s="10" t="inlineStr">
         <is>
           <t>조건검색 요청 실시간 (ka10173)</t>
         </is>
       </c>
-      <c r="F122" s="11" t="inlineStr">
+      <c r="F124" s="11" t="inlineStr">
         <is>
           <t>ka10173</t>
         </is>
       </c>
-      <c r="G122" s="10" t="inlineStr">
+      <c r="G124" s="10" t="inlineStr">
         <is>
           <t>SEQ (필수)</t>
         </is>
       </c>
-      <c r="H122" s="10" t="inlineStr">
+      <c r="H124" s="10" t="inlineStr">
         <is>
           <t>--exchange [K] 기본:K (거래소 (K=KRX))
 --confirm *필수 (조회 확인 (필수))</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="10" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B123" s="10" t="inlineStr">
+      <c r="B125" s="10" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="C123" s="10" t="inlineStr">
+      <c r="C125" s="10" t="inlineStr">
         <is>
           <t>search</t>
         </is>
       </c>
-      <c r="D123" s="10" t="inlineStr">
+      <c r="D125" s="10" t="inlineStr">
         <is>
           <t>kiwoom order condition search</t>
         </is>
       </c>
-      <c r="E123" s="10" t="inlineStr">
+      <c r="E125" s="10" t="inlineStr">
         <is>
           <t>조건검색 요청 일반 (ka10172)</t>
         </is>
       </c>
-      <c r="F123" s="11" t="inlineStr">
+      <c r="F125" s="11" t="inlineStr">
         <is>
           <t>ka10172</t>
         </is>
       </c>
-      <c r="G123" s="10" t="inlineStr">
+      <c r="G125" s="10" t="inlineStr">
         <is>
           <t>SEQ (필수)</t>
         </is>
       </c>
-      <c r="H123" s="10" t="inlineStr">
+      <c r="H125" s="10" t="inlineStr">
         <is>
           <t>--exchange [K] 기본:K (거래소 (K=KRX))
 --cont-yn (연속조회여부)
@@ -5620,86 +5697,86 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="10" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B124" s="10" t="inlineStr">
+      <c r="B126" s="10" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="C124" s="10" t="inlineStr">
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>stop</t>
         </is>
       </c>
-      <c r="D124" s="10" t="inlineStr">
+      <c r="D126" s="10" t="inlineStr">
         <is>
           <t>kiwoom order condition stop</t>
         </is>
       </c>
-      <c r="E124" s="10" t="inlineStr">
+      <c r="E126" s="10" t="inlineStr">
         <is>
           <t>조건검색 실시간 해제 (ka10174)</t>
         </is>
       </c>
-      <c r="F124" s="11" t="inlineStr">
+      <c r="F126" s="11" t="inlineStr">
         <is>
           <t>ka10174</t>
         </is>
       </c>
-      <c r="G124" s="10" t="inlineStr">
+      <c r="G126" s="10" t="inlineStr">
         <is>
           <t>SEQ (필수)</t>
         </is>
       </c>
-      <c r="H124" s="10" t="inlineStr">
+      <c r="H126" s="10" t="inlineStr">
         <is>
           <t>--confirm *필수 (조회 확인 (필수))</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="10" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B125" s="10" t="inlineStr">
+      <c r="B127" s="10" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="C125" s="10" t="inlineStr">
+      <c r="C127" s="10" t="inlineStr">
         <is>
           <t>buy</t>
         </is>
       </c>
-      <c r="D125" s="10" t="inlineStr">
+      <c r="D127" s="10" t="inlineStr">
         <is>
           <t>kiwoom order credit buy</t>
         </is>
       </c>
-      <c r="E125" s="10" t="inlineStr">
+      <c r="E127" s="10" t="inlineStr">
         <is>
           <t>신용 매수주문 (kt10006)</t>
         </is>
       </c>
-      <c r="F125" s="11" t="inlineStr">
+      <c r="F127" s="11" t="inlineStr">
         <is>
           <t>kt10006</t>
         </is>
       </c>
-      <c r="G125" s="10" t="inlineStr">
+      <c r="G127" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)
 QTY (필수)</t>
         </is>
       </c>
-      <c r="H125" s="10" t="inlineStr">
+      <c r="H127" s="10" t="inlineStr">
         <is>
           <t>--price (주문가격 (시장가 주문시 생략))
 --type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
@@ -5709,44 +5786,44 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="10" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B126" s="10" t="inlineStr">
+      <c r="B128" s="10" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="C126" s="10" t="inlineStr">
+      <c r="C128" s="10" t="inlineStr">
         <is>
           <t>cancel</t>
         </is>
       </c>
-      <c r="D126" s="10" t="inlineStr">
+      <c r="D128" s="10" t="inlineStr">
         <is>
           <t>kiwoom order credit cancel</t>
         </is>
       </c>
-      <c r="E126" s="10" t="inlineStr">
+      <c r="E128" s="10" t="inlineStr">
         <is>
           <t>신용 취소주문 (kt10009)</t>
         </is>
       </c>
-      <c r="F126" s="11" t="inlineStr">
+      <c r="F128" s="11" t="inlineStr">
         <is>
           <t>kt10009</t>
         </is>
       </c>
-      <c r="G126" s="10" t="inlineStr">
+      <c r="G128" s="10" t="inlineStr">
         <is>
           <t>ORIG_ORDER_NO (필수)
 CODE (필수)</t>
         </is>
       </c>
-      <c r="H126" s="10" t="inlineStr">
+      <c r="H128" s="10" t="inlineStr">
         <is>
           <t>--qty (취소수량 (0=전량취소))
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
@@ -5754,38 +5831,38 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="10" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B127" s="10" t="inlineStr">
+      <c r="B129" s="10" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="C127" s="10" t="inlineStr">
+      <c r="C129" s="10" t="inlineStr">
         <is>
           <t>modify</t>
         </is>
       </c>
-      <c r="D127" s="10" t="inlineStr">
+      <c r="D129" s="10" t="inlineStr">
         <is>
           <t>kiwoom order credit modify</t>
         </is>
       </c>
-      <c r="E127" s="10" t="inlineStr">
+      <c r="E129" s="10" t="inlineStr">
         <is>
           <t>신용 정정주문 (kt10008)</t>
         </is>
       </c>
-      <c r="F127" s="11" t="inlineStr">
+      <c r="F129" s="11" t="inlineStr">
         <is>
           <t>kt10008</t>
         </is>
       </c>
-      <c r="G127" s="10" t="inlineStr">
+      <c r="G129" s="10" t="inlineStr">
         <is>
           <t>ORIG_ORDER_NO (필수)
 CODE (필수)
@@ -5793,7 +5870,7 @@
 PRICE (필수)</t>
         </is>
       </c>
-      <c r="H127" s="10" t="inlineStr">
+      <c r="H129" s="10" t="inlineStr">
         <is>
           <t>--exchange [KRX, NXT, SOR] 기본:KRX (거래소)
 --cond-price (정정 조건부가격)
@@ -5801,44 +5878,44 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="10" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B128" s="10" t="inlineStr">
+      <c r="B130" s="10" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="C128" s="10" t="inlineStr">
+      <c r="C130" s="10" t="inlineStr">
         <is>
           <t>sell</t>
         </is>
       </c>
-      <c r="D128" s="10" t="inlineStr">
+      <c r="D130" s="10" t="inlineStr">
         <is>
           <t>kiwoom order credit sell</t>
         </is>
       </c>
-      <c r="E128" s="10" t="inlineStr">
+      <c r="E130" s="10" t="inlineStr">
         <is>
           <t>신용 매도주문 (kt10007)</t>
         </is>
       </c>
-      <c r="F128" s="11" t="inlineStr">
+      <c r="F130" s="11" t="inlineStr">
         <is>
           <t>kt10007</t>
         </is>
       </c>
-      <c r="G128" s="10" t="inlineStr">
+      <c r="G130" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)
 QTY (필수)</t>
         </is>
       </c>
-      <c r="H128" s="10" t="inlineStr">
+      <c r="H130" s="10" t="inlineStr">
         <is>
           <t>--price (주문가격 (시장가 주문시 생략))
 --type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
@@ -5848,86 +5925,86 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="10" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B129" s="10" t="inlineStr">
+      <c r="B131" s="10" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C129" s="10" t="inlineStr">
+      <c r="C131" s="10" t="inlineStr">
         <is>
           <t>balance</t>
         </is>
       </c>
-      <c r="D129" s="10" t="inlineStr">
+      <c r="D131" s="10" t="inlineStr">
         <is>
           <t>kiwoom order gold balance</t>
         </is>
       </c>
-      <c r="E129" s="10" t="inlineStr">
+      <c r="E131" s="10" t="inlineStr">
         <is>
           <t>금현물 잔고확인 (kt50020)</t>
         </is>
       </c>
-      <c r="F129" s="11" t="inlineStr">
+      <c r="F131" s="11" t="inlineStr">
         <is>
           <t>kt50020</t>
         </is>
       </c>
-      <c r="G129" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="10" t="inlineStr">
+      <c r="G131" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" s="10" t="inlineStr">
         <is>
           <t>--confirm *필수 (조회 확인 (필수))</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="10" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B130" s="10" t="inlineStr">
+      <c r="B132" s="10" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C130" s="10" t="inlineStr">
+      <c r="C132" s="10" t="inlineStr">
         <is>
           <t>buy</t>
         </is>
       </c>
-      <c r="D130" s="10" t="inlineStr">
+      <c r="D132" s="10" t="inlineStr">
         <is>
           <t>kiwoom order gold buy</t>
         </is>
       </c>
-      <c r="E130" s="10" t="inlineStr">
+      <c r="E132" s="10" t="inlineStr">
         <is>
           <t>금현물 매수주문 (kt50000)</t>
         </is>
       </c>
-      <c r="F130" s="11" t="inlineStr">
+      <c r="F132" s="11" t="inlineStr">
         <is>
           <t>kt50000</t>
         </is>
       </c>
-      <c r="G130" s="10" t="inlineStr">
+      <c r="G132" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)
 QTY (필수)</t>
         </is>
       </c>
-      <c r="H130" s="10" t="inlineStr">
+      <c r="H132" s="10" t="inlineStr">
         <is>
           <t>--price (주문가격 (시장가 주문시 생략))
 --type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
@@ -5936,44 +6013,44 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="10" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B131" s="10" t="inlineStr">
+      <c r="B133" s="10" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C131" s="10" t="inlineStr">
+      <c r="C133" s="10" t="inlineStr">
         <is>
           <t>cancel</t>
         </is>
       </c>
-      <c r="D131" s="10" t="inlineStr">
+      <c r="D133" s="10" t="inlineStr">
         <is>
           <t>kiwoom order gold cancel</t>
         </is>
       </c>
-      <c r="E131" s="10" t="inlineStr">
+      <c r="E133" s="10" t="inlineStr">
         <is>
           <t>금현물 취소주문 (kt50003)</t>
         </is>
       </c>
-      <c r="F131" s="11" t="inlineStr">
+      <c r="F133" s="11" t="inlineStr">
         <is>
           <t>kt50003</t>
         </is>
       </c>
-      <c r="G131" s="10" t="inlineStr">
+      <c r="G133" s="10" t="inlineStr">
         <is>
           <t>ORIG_ORDER_NO (필수)
 CODE (필수)</t>
         </is>
       </c>
-      <c r="H131" s="10" t="inlineStr">
+      <c r="H133" s="10" t="inlineStr">
         <is>
           <t>--qty (취소수량 (0=전량취소))
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
@@ -5981,90 +6058,6 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="10" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="B132" s="10" t="inlineStr">
-        <is>
-          <t>gold</t>
-        </is>
-      </c>
-      <c r="C132" s="10" t="inlineStr">
-        <is>
-          <t>deposit</t>
-        </is>
-      </c>
-      <c r="D132" s="10" t="inlineStr">
-        <is>
-          <t>kiwoom order gold deposit</t>
-        </is>
-      </c>
-      <c r="E132" s="10" t="inlineStr">
-        <is>
-          <t>금현물 예수금 (kt50021)</t>
-        </is>
-      </c>
-      <c r="F132" s="11" t="inlineStr">
-        <is>
-          <t>kt50021</t>
-        </is>
-      </c>
-      <c r="G132" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H132" s="10" t="inlineStr">
-        <is>
-          <t>--confirm *필수 (조회 확인 (필수))</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="10" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="B133" s="10" t="inlineStr">
-        <is>
-          <t>gold</t>
-        </is>
-      </c>
-      <c r="C133" s="10" t="inlineStr">
-        <is>
-          <t>executions</t>
-        </is>
-      </c>
-      <c r="D133" s="10" t="inlineStr">
-        <is>
-          <t>kiwoom order gold executions</t>
-        </is>
-      </c>
-      <c r="E133" s="10" t="inlineStr">
-        <is>
-          <t>금현물 주문체결조회 (kt50031)</t>
-        </is>
-      </c>
-      <c r="F133" s="11" t="inlineStr">
-        <is>
-          <t>kt50031</t>
-        </is>
-      </c>
-      <c r="G133" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="10" t="inlineStr">
-        <is>
-          <t>--confirm *필수 (조회 확인 (필수))</t>
-        </is>
-      </c>
-    </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
@@ -6078,22 +6071,22 @@
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>executions-all</t>
+          <t>deposit</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>kiwoom order gold executions-all</t>
+          <t>kiwoom order gold deposit</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>금현물 주문체결전체조회 (kt50030)</t>
+          <t>금현물 예수금 (kt50021)</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>kt50030</t>
+          <t>kt50021</t>
         </is>
       </c>
       <c r="G134" s="10" t="inlineStr">
@@ -6120,22 +6113,22 @@
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>executions</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>kiwoom order gold history</t>
+          <t>kiwoom order gold executions</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>금현물 거래내역조회 (kt50032)</t>
+          <t>금현물 주문체결조회 (kt50031)</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>kt50032</t>
+          <t>kt50031</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
@@ -6162,25 +6155,109 @@
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
+          <t>executions-all</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>kiwoom order gold executions-all</t>
+        </is>
+      </c>
+      <c r="E136" s="10" t="inlineStr">
+        <is>
+          <t>금현물 주문체결전체조회 (kt50030)</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>kt50030</t>
+        </is>
+      </c>
+      <c r="G136" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" s="10" t="inlineStr">
+        <is>
+          <t>--confirm *필수 (조회 확인 (필수))</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>kiwoom order gold history</t>
+        </is>
+      </c>
+      <c r="E137" s="10" t="inlineStr">
+        <is>
+          <t>금현물 거래내역조회 (kt50032)</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>kt50032</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" s="10" t="inlineStr">
+        <is>
+          <t>--confirm *필수 (조회 확인 (필수))</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
           <t>modify</t>
         </is>
       </c>
-      <c r="D136" s="10" t="inlineStr">
+      <c r="D138" s="10" t="inlineStr">
         <is>
           <t>kiwoom order gold modify</t>
         </is>
       </c>
-      <c r="E136" s="10" t="inlineStr">
+      <c r="E138" s="10" t="inlineStr">
         <is>
           <t>금현물 정정주문 (kt50002)</t>
         </is>
       </c>
-      <c r="F136" s="11" t="inlineStr">
+      <c r="F138" s="11" t="inlineStr">
         <is>
           <t>kt50002</t>
         </is>
       </c>
-      <c r="G136" s="10" t="inlineStr">
+      <c r="G138" s="10" t="inlineStr">
         <is>
           <t>ORIG_ORDER_NO (필수)
 CODE (필수)
@@ -6188,93 +6265,93 @@
 PRICE (필수)</t>
         </is>
       </c>
-      <c r="H136" s="10" t="inlineStr">
+      <c r="H138" s="10" t="inlineStr">
         <is>
           <t>--exchange [KRX, NXT, SOR] 기본:KRX (거래소)
 --confirm *필수 (주문 확인 (필수))</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="10" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B137" s="10" t="inlineStr">
+      <c r="B139" s="10" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C137" s="10" t="inlineStr">
+      <c r="C139" s="10" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="D137" s="10" t="inlineStr">
+      <c r="D139" s="10" t="inlineStr">
         <is>
           <t>kiwoom order gold pending</t>
         </is>
       </c>
-      <c r="E137" s="10" t="inlineStr">
+      <c r="E139" s="10" t="inlineStr">
         <is>
           <t>금현물 미체결조회 (kt50075)</t>
         </is>
       </c>
-      <c r="F137" s="11" t="inlineStr">
+      <c r="F139" s="11" t="inlineStr">
         <is>
           <t>kt50075</t>
         </is>
       </c>
-      <c r="G137" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H137" s="10" t="inlineStr">
+      <c r="G139" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" s="10" t="inlineStr">
         <is>
           <t>--confirm *필수 (조회 확인 (필수))</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="10" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B138" s="10" t="inlineStr">
+      <c r="B140" s="10" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="C138" s="10" t="inlineStr">
+      <c r="C140" s="10" t="inlineStr">
         <is>
           <t>sell</t>
         </is>
       </c>
-      <c r="D138" s="10" t="inlineStr">
+      <c r="D140" s="10" t="inlineStr">
         <is>
           <t>kiwoom order gold sell</t>
         </is>
       </c>
-      <c r="E138" s="10" t="inlineStr">
+      <c r="E140" s="10" t="inlineStr">
         <is>
           <t>금현물 매도주문 (kt50001)</t>
         </is>
       </c>
-      <c r="F138" s="11" t="inlineStr">
+      <c r="F140" s="11" t="inlineStr">
         <is>
           <t>kt50001</t>
         </is>
       </c>
-      <c r="G138" s="10" t="inlineStr">
+      <c r="G140" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)
 QTY (필수)</t>
         </is>
       </c>
-      <c r="H138" s="10" t="inlineStr">
+      <c r="H140" s="10" t="inlineStr">
         <is>
           <t>--price (주문가격 (시장가 주문시 생략))
 --type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
@@ -6283,38 +6360,38 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="10" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B139" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C139" s="10" t="inlineStr">
+      <c r="B141" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
         <is>
           <t>modify</t>
         </is>
       </c>
-      <c r="D139" s="10" t="inlineStr">
+      <c r="D141" s="10" t="inlineStr">
         <is>
           <t>kiwoom order modify</t>
         </is>
       </c>
-      <c r="E139" s="10" t="inlineStr">
+      <c r="E141" s="10" t="inlineStr">
         <is>
           <t>주식 정정주문 (kt10002)</t>
         </is>
       </c>
-      <c r="F139" s="11" t="inlineStr">
+      <c r="F141" s="11" t="inlineStr">
         <is>
           <t>kt10002</t>
         </is>
       </c>
-      <c r="G139" s="10" t="inlineStr">
+      <c r="G141" s="10" t="inlineStr">
         <is>
           <t>ORIG_ORDER_NO (필수)
 CODE (필수)
@@ -6322,7 +6399,7 @@
 PRICE (필수)</t>
         </is>
       </c>
-      <c r="H139" s="10" t="inlineStr">
+      <c r="H141" s="10" t="inlineStr">
         <is>
           <t>--exchange [KRX, NXT, SOR] 기본:KRX (거래소)
 --cond-price (정정 조건부가격)
@@ -6330,44 +6407,44 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="10" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="B140" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C140" s="10" t="inlineStr">
+      <c r="B142" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
         <is>
           <t>sell</t>
         </is>
       </c>
-      <c r="D140" s="10" t="inlineStr">
+      <c r="D142" s="10" t="inlineStr">
         <is>
           <t>kiwoom order sell</t>
         </is>
       </c>
-      <c r="E140" s="10" t="inlineStr">
+      <c r="E142" s="10" t="inlineStr">
         <is>
           <t>주식 매도주문 (kt10001)</t>
         </is>
       </c>
-      <c r="F140" s="11" t="inlineStr">
+      <c r="F142" s="11" t="inlineStr">
         <is>
           <t>kt10001</t>
         </is>
       </c>
-      <c r="G140" s="10" t="inlineStr">
+      <c r="G142" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)
 QTY (필수)</t>
         </is>
       </c>
-      <c r="H140" s="10" t="inlineStr">
+      <c r="H142" s="10" t="inlineStr">
         <is>
           <t>--price (주문가격 (시장가 주문시 생략))
 --type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
@@ -6377,85 +6454,85 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="12" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B141" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C141" s="12" t="inlineStr">
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
         <is>
           <t>after-hours</t>
         </is>
       </c>
-      <c r="D141" s="12" t="inlineStr">
+      <c r="D143" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock after-hours</t>
         </is>
       </c>
-      <c r="E141" s="12" t="inlineStr">
+      <c r="E143" s="12" t="inlineStr">
         <is>
           <t>시간외단일가 조회</t>
         </is>
       </c>
-      <c r="F141" s="13" t="inlineStr">
+      <c r="F143" s="13" t="inlineStr">
         <is>
           <t>ka10087</t>
         </is>
       </c>
-      <c r="G141" s="12" t="inlineStr">
+      <c r="G143" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H141" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="12" t="inlineStr">
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B142" s="12" t="inlineStr">
+      <c r="B144" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C142" s="12" t="inlineStr">
+      <c r="C144" s="12" t="inlineStr">
         <is>
           <t>broker-stock</t>
         </is>
       </c>
-      <c r="D142" s="12" t="inlineStr">
+      <c r="D144" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis broker-stock</t>
         </is>
       </c>
-      <c r="E142" s="12" t="inlineStr">
+      <c r="E144" s="12" t="inlineStr">
         <is>
           <t>증권사별종목매매동향 조회</t>
         </is>
       </c>
-      <c r="F142" s="13" t="inlineStr">
+      <c r="F144" s="13" t="inlineStr">
         <is>
           <t>ka10078</t>
         </is>
       </c>
-      <c r="G142" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H142" s="12" t="inlineStr">
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H144" s="12" t="inlineStr">
         <is>
           <t>--broker *필수 (회원사코드)
 --code *필수 (종목코드)
@@ -6464,85 +6541,85 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="12" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B143" s="12" t="inlineStr">
+      <c r="B145" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C143" s="12" t="inlineStr">
+      <c r="C145" s="12" t="inlineStr">
         <is>
           <t>daily-detail</t>
         </is>
       </c>
-      <c r="D143" s="12" t="inlineStr">
+      <c r="D145" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis daily-detail</t>
         </is>
       </c>
-      <c r="E143" s="12" t="inlineStr">
+      <c r="E145" s="12" t="inlineStr">
         <is>
           <t>일별거래상세 조회</t>
         </is>
       </c>
-      <c r="F143" s="13" t="inlineStr">
+      <c r="F145" s="13" t="inlineStr">
         <is>
           <t>ka10015</t>
         </is>
       </c>
-      <c r="G143" s="12" t="inlineStr">
+      <c r="G145" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H143" s="12" t="inlineStr">
+      <c r="H145" s="12" t="inlineStr">
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="12" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B144" s="12" t="inlineStr">
+      <c r="B146" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C144" s="12" t="inlineStr">
+      <c r="C146" s="12" t="inlineStr">
         <is>
           <t>instant-volume</t>
         </is>
       </c>
-      <c r="D144" s="12" t="inlineStr">
+      <c r="D146" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis instant-volume</t>
         </is>
       </c>
-      <c r="E144" s="12" t="inlineStr">
+      <c r="E146" s="12" t="inlineStr">
         <is>
           <t>거래원순간거래량 조회</t>
         </is>
       </c>
-      <c r="F144" s="13" t="inlineStr">
+      <c r="F146" s="13" t="inlineStr">
         <is>
           <t>ka10052</t>
         </is>
       </c>
-      <c r="G144" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H144" s="12" t="inlineStr">
+      <c r="G146" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H146" s="12" t="inlineStr">
         <is>
           <t>--broker *필수 (회원사코드)
 --code (종목코드 (선택))
@@ -6553,43 +6630,43 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="12" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B145" s="12" t="inlineStr">
+      <c r="B147" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C145" s="12" t="inlineStr">
+      <c r="C147" s="12" t="inlineStr">
         <is>
           <t>open-change</t>
         </is>
       </c>
-      <c r="D145" s="12" t="inlineStr">
+      <c r="D147" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis open-change</t>
         </is>
       </c>
-      <c r="E145" s="12" t="inlineStr">
+      <c r="E147" s="12" t="inlineStr">
         <is>
           <t>시가대비등락률 조회</t>
         </is>
       </c>
-      <c r="F145" s="13" t="inlineStr">
+      <c r="F147" s="13" t="inlineStr">
         <is>
           <t>ka10028</t>
         </is>
       </c>
-      <c r="G145" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H145" s="12" t="inlineStr">
+      <c r="G147" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" s="12" t="inlineStr">
         <is>
           <t>--sort [1, 2, 3, 4] 기본:1 (정렬구분 (1=시가, 2=고가, 3=저가, 4=기준가))
 --volume-cond (거래량조건)
@@ -6603,86 +6680,86 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="12" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B146" s="12" t="inlineStr">
+      <c r="B148" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C146" s="12" t="inlineStr">
+      <c r="C148" s="12" t="inlineStr">
         <is>
           <t>per-rank</t>
         </is>
       </c>
-      <c r="D146" s="12" t="inlineStr">
+      <c r="D148" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis per-rank</t>
         </is>
       </c>
-      <c r="E146" s="12" t="inlineStr">
+      <c r="E148" s="12" t="inlineStr">
         <is>
           <t>고저PER 조회</t>
         </is>
       </c>
-      <c r="F146" s="13" t="inlineStr">
+      <c r="F148" s="13" t="inlineStr">
         <is>
           <t>ka10026</t>
         </is>
       </c>
-      <c r="G146" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H146" s="12" t="inlineStr">
+      <c r="G148" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" s="12" t="inlineStr">
         <is>
           <t>--type [low-pbr, high-pbr, low-per, high-per, low-roe, high-roe] 기본:low-per (PER구분 (low-pbr/high-pbr/low-per/high-per/low-roe/high-roe))
 --exchange [KRX, NXT, all] 기본:all (거래소구분 (KRX/NXT/all))</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="12" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B147" s="12" t="inlineStr">
+      <c r="B149" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C147" s="12" t="inlineStr">
+      <c r="C149" s="12" t="inlineStr">
         <is>
           <t>price-cluster</t>
         </is>
       </c>
-      <c r="D147" s="12" t="inlineStr">
+      <c r="D149" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis price-cluster</t>
         </is>
       </c>
-      <c r="E147" s="12" t="inlineStr">
+      <c r="E149" s="12" t="inlineStr">
         <is>
           <t>매물대집중 조회</t>
         </is>
       </c>
-      <c r="F147" s="13" t="inlineStr">
+      <c r="F149" s="13" t="inlineStr">
         <is>
           <t>ka10025</t>
         </is>
       </c>
-      <c r="G147" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H147" s="12" t="inlineStr">
+      <c r="G149" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H149" s="12" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분 (all/kospi/kosdaq))
 --ratio 기본:50 (매물집중비율 (0~100))
@@ -6693,43 +6770,43 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="12" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B148" s="12" t="inlineStr">
+      <c r="B150" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C148" s="12" t="inlineStr">
+      <c r="C150" s="12" t="inlineStr">
         <is>
           <t>trader-analysis</t>
         </is>
       </c>
-      <c r="D148" s="12" t="inlineStr">
+      <c r="D150" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis trader-analysis</t>
         </is>
       </c>
-      <c r="E148" s="12" t="inlineStr">
+      <c r="E150" s="12" t="inlineStr">
         <is>
           <t>거래원매물대분석 조회</t>
         </is>
       </c>
-      <c r="F148" s="13" t="inlineStr">
+      <c r="F150" s="13" t="inlineStr">
         <is>
           <t>ka10043</t>
         </is>
       </c>
-      <c r="G148" s="12" t="inlineStr">
+      <c r="G150" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H148" s="12" t="inlineStr">
+      <c r="H150" s="12" t="inlineStr">
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
@@ -6742,43 +6819,43 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="12" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B149" s="12" t="inlineStr">
+      <c r="B151" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C149" s="12" t="inlineStr">
+      <c r="C151" s="12" t="inlineStr">
         <is>
           <t>vi-trigger</t>
         </is>
       </c>
-      <c r="D149" s="12" t="inlineStr">
+      <c r="D151" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis vi-trigger</t>
         </is>
       </c>
-      <c r="E149" s="12" t="inlineStr">
+      <c r="E151" s="12" t="inlineStr">
         <is>
           <t>변동성완화장치(VI) 발동종목 조회</t>
         </is>
       </c>
-      <c r="F149" s="13" t="inlineStr">
+      <c r="F151" s="13" t="inlineStr">
         <is>
           <t>ka10054</t>
         </is>
       </c>
-      <c r="G149" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H149" s="12" t="inlineStr">
+      <c r="G151" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" s="12" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분 (all/kospi/kosdaq))
 --session [0, 1, 2] (장전구분 (0=전체, 1=정규시장, 2=시간외단일가))
@@ -6796,43 +6873,43 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="12" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B150" s="12" t="inlineStr">
+      <c r="B152" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C150" s="12" t="inlineStr">
+      <c r="C152" s="12" t="inlineStr">
         <is>
           <t>volume-renewal</t>
         </is>
       </c>
-      <c r="D150" s="12" t="inlineStr">
+      <c r="D152" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis volume-renewal</t>
         </is>
       </c>
-      <c r="E150" s="12" t="inlineStr">
+      <c r="E152" s="12" t="inlineStr">
         <is>
           <t>거래량갱신 조회</t>
         </is>
       </c>
-      <c r="F150" s="13" t="inlineStr">
+      <c r="F152" s="13" t="inlineStr">
         <is>
           <t>ka10024</t>
         </is>
       </c>
-      <c r="G150" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H150" s="12" t="inlineStr">
+      <c r="G152" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" s="12" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분 (all/kospi/kosdaq))
 --cycle [5, 10, 20, 60, 250] 기본:20 (주기구분 (5/10/20/60/250일))
@@ -6841,90 +6918,6 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B151" s="12" t="inlineStr">
-        <is>
-          <t>analysis</t>
-        </is>
-      </c>
-      <c r="C151" s="12" t="inlineStr">
-        <is>
-          <t>warrant</t>
-        </is>
-      </c>
-      <c r="D151" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock analysis warrant</t>
-        </is>
-      </c>
-      <c r="E151" s="12" t="inlineStr">
-        <is>
-          <t>신주인수권전체시세 조회</t>
-        </is>
-      </c>
-      <c r="F151" s="13" t="inlineStr">
-        <is>
-          <t>ka10011</t>
-        </is>
-      </c>
-      <c r="G151" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" s="12" t="inlineStr">
-        <is>
-          <t>--type [00, 05, 07] 기본:00 (신주인수권구분 (00=전체, 05=신주인수권증권, 07=신주인수권증서))</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B152" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C152" s="12" t="inlineStr">
-        <is>
-          <t>brokers</t>
-        </is>
-      </c>
-      <c r="D152" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock brokers</t>
-        </is>
-      </c>
-      <c r="E152" s="12" t="inlineStr">
-        <is>
-          <t>회원사(증권사) 리스트 조회</t>
-        </is>
-      </c>
-      <c r="F152" s="13" t="inlineStr">
-        <is>
-          <t>ka10102</t>
-        </is>
-      </c>
-      <c r="G152" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H152" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="153">
       <c r="A153" s="12" t="inlineStr">
         <is>
@@ -6933,78 +6926,162 @@
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
+          <t>analysis</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
+      </c>
+      <c r="D153" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock analysis warrant</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="inlineStr">
+        <is>
+          <t>신주인수권전체시세 조회</t>
+        </is>
+      </c>
+      <c r="F153" s="13" t="inlineStr">
+        <is>
+          <t>ka10011</t>
+        </is>
+      </c>
+      <c r="G153" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" s="12" t="inlineStr">
+        <is>
+          <t>--type [00, 05, 07] 기본:00 (신주인수권구분 (00=전체, 05=신주인수권증권, 07=신주인수권증서))</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B154" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C154" s="12" t="inlineStr">
+        <is>
+          <t>brokers</t>
+        </is>
+      </c>
+      <c r="D154" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock brokers</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="inlineStr">
+        <is>
+          <t>회원사(증권사) 리스트 조회</t>
+        </is>
+      </c>
+      <c r="F154" s="13" t="inlineStr">
+        <is>
+          <t>ka10102</t>
+        </is>
+      </c>
+      <c r="G154" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C153" s="12" t="inlineStr">
+      <c r="C155" s="12" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="D153" s="12" t="inlineStr">
+      <c r="D155" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart day</t>
         </is>
       </c>
-      <c r="E153" s="12" t="inlineStr">
+      <c r="E155" s="12" t="inlineStr">
         <is>
           <t>일봉 차트 조회</t>
         </is>
       </c>
-      <c r="F153" s="13" t="inlineStr">
+      <c r="F155" s="13" t="inlineStr">
         <is>
           <t>ka10081</t>
         </is>
       </c>
-      <c r="G153" s="12" t="inlineStr">
+      <c r="G155" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H153" s="12" t="inlineStr">
+      <c r="H155" s="12" t="inlineStr">
         <is>
           <t>--base-date *필수 (기준일자 (YYYYMMDD))
 --adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="12" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B154" s="12" t="inlineStr">
+      <c r="B156" s="12" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C154" s="12" t="inlineStr">
+      <c r="C156" s="12" t="inlineStr">
         <is>
           <t>intraday-investor</t>
         </is>
       </c>
-      <c r="D154" s="12" t="inlineStr">
+      <c r="D156" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart intraday-investor</t>
         </is>
       </c>
-      <c r="E154" s="12" t="inlineStr">
+      <c r="E156" s="12" t="inlineStr">
         <is>
           <t>장중투자자별매매 차트 조회</t>
         </is>
       </c>
-      <c r="F154" s="13" t="inlineStr">
+      <c r="F156" s="13" t="inlineStr">
         <is>
           <t>ka10064</t>
         </is>
       </c>
-      <c r="G154" s="12" t="inlineStr">
+      <c r="G156" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H154" s="12" t="inlineStr">
+      <c r="H156" s="12" t="inlineStr">
         <is>
           <t>--market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
 --amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
@@ -7012,43 +7089,43 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="12" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B155" s="12" t="inlineStr">
+      <c r="B157" s="12" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C155" s="12" t="inlineStr">
+      <c r="C157" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="D155" s="12" t="inlineStr">
+      <c r="D157" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart investor</t>
         </is>
       </c>
-      <c r="E155" s="12" t="inlineStr">
+      <c r="E157" s="12" t="inlineStr">
         <is>
           <t>종목별투자자기관별 차트 조회</t>
         </is>
       </c>
-      <c r="F155" s="13" t="inlineStr">
+      <c r="F157" s="13" t="inlineStr">
         <is>
           <t>ka10060</t>
         </is>
       </c>
-      <c r="G155" s="12" t="inlineStr">
+      <c r="G157" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H155" s="12" t="inlineStr">
+      <c r="H157" s="12" t="inlineStr">
         <is>
           <t>--date *필수 (일자 (YYYYMMDD))
 --amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
@@ -7057,43 +7134,43 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="12" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B156" s="12" t="inlineStr">
+      <c r="B158" s="12" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C156" s="12" t="inlineStr">
+      <c r="C158" s="12" t="inlineStr">
         <is>
           <t>minute</t>
         </is>
       </c>
-      <c r="D156" s="12" t="inlineStr">
+      <c r="D158" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart minute</t>
         </is>
       </c>
-      <c r="E156" s="12" t="inlineStr">
+      <c r="E158" s="12" t="inlineStr">
         <is>
           <t>분봉 차트 조회</t>
         </is>
       </c>
-      <c r="F156" s="13" t="inlineStr">
+      <c r="F158" s="13" t="inlineStr">
         <is>
           <t>ka10080</t>
         </is>
       </c>
-      <c r="G156" s="12" t="inlineStr">
+      <c r="G158" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H156" s="12" t="inlineStr">
+      <c r="H158" s="12" t="inlineStr">
         <is>
           <t>--interval [1, 3, 5, 10, 15, 30, 45, 60] 기본:5 (분봉 간격 (1/3/5/10/15/30/45/60))
 --adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))
@@ -7101,262 +7178,178 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="12" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B157" s="12" t="inlineStr">
+      <c r="B159" s="12" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C157" s="12" t="inlineStr">
+      <c r="C159" s="12" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="D157" s="12" t="inlineStr">
+      <c r="D159" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart month</t>
         </is>
       </c>
-      <c r="E157" s="12" t="inlineStr">
+      <c r="E159" s="12" t="inlineStr">
         <is>
           <t>월봉 차트 조회</t>
         </is>
       </c>
-      <c r="F157" s="13" t="inlineStr">
+      <c r="F159" s="13" t="inlineStr">
         <is>
           <t>ka10083</t>
         </is>
       </c>
-      <c r="G157" s="12" t="inlineStr">
+      <c r="G159" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H157" s="12" t="inlineStr">
+      <c r="H159" s="12" t="inlineStr">
         <is>
           <t>--base-date *필수 (기준일자 (YYYYMMDD))
 --adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="12" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B158" s="12" t="inlineStr">
+      <c r="B160" s="12" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C158" s="12" t="inlineStr">
+      <c r="C160" s="12" t="inlineStr">
         <is>
           <t>tick</t>
         </is>
       </c>
-      <c r="D158" s="12" t="inlineStr">
+      <c r="D160" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart tick</t>
         </is>
       </c>
-      <c r="E158" s="12" t="inlineStr">
+      <c r="E160" s="12" t="inlineStr">
         <is>
           <t>틱 차트 조회</t>
         </is>
       </c>
-      <c r="F158" s="13" t="inlineStr">
+      <c r="F160" s="13" t="inlineStr">
         <is>
           <t>ka10079</t>
         </is>
       </c>
-      <c r="G158" s="12" t="inlineStr">
+      <c r="G160" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H158" s="12" t="inlineStr">
+      <c r="H160" s="12" t="inlineStr">
         <is>
           <t>--range [1, 3, 5, 10, 30] 기본:1 (틱범위 (1/3/5/10/30))
 --adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="12" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B159" s="12" t="inlineStr">
+      <c r="B161" s="12" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C159" s="12" t="inlineStr">
+      <c r="C161" s="12" t="inlineStr">
         <is>
           <t>week</t>
         </is>
       </c>
-      <c r="D159" s="12" t="inlineStr">
+      <c r="D161" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart week</t>
         </is>
       </c>
-      <c r="E159" s="12" t="inlineStr">
+      <c r="E161" s="12" t="inlineStr">
         <is>
           <t>주봉 차트 조회</t>
         </is>
       </c>
-      <c r="F159" s="13" t="inlineStr">
+      <c r="F161" s="13" t="inlineStr">
         <is>
           <t>ka10082</t>
         </is>
       </c>
-      <c r="G159" s="12" t="inlineStr">
+      <c r="G161" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H159" s="12" t="inlineStr">
+      <c r="H161" s="12" t="inlineStr">
         <is>
           <t>--base-date *필수 (기준일자 (YYYYMMDD))
 --adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="12" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B160" s="12" t="inlineStr">
+      <c r="B162" s="12" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C160" s="12" t="inlineStr">
+      <c r="C162" s="12" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="D160" s="12" t="inlineStr">
+      <c r="D162" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart year</t>
         </is>
       </c>
-      <c r="E160" s="12" t="inlineStr">
+      <c r="E162" s="12" t="inlineStr">
         <is>
           <t>년봉 차트 조회</t>
         </is>
       </c>
-      <c r="F160" s="13" t="inlineStr">
+      <c r="F162" s="13" t="inlineStr">
         <is>
           <t>ka10094</t>
         </is>
       </c>
-      <c r="G160" s="12" t="inlineStr">
+      <c r="G162" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H160" s="12" t="inlineStr">
+      <c r="H162" s="12" t="inlineStr">
         <is>
           <t>--base-date *필수 (기준일자 (YYYYMMDD))
 --adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B161" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C161" s="12" t="inlineStr">
-        <is>
-          <t>compare</t>
-        </is>
-      </c>
-      <c r="D161" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock compare</t>
-        </is>
-      </c>
-      <c r="E161" s="12" t="inlineStr">
-        <is>
-          <t>종목 비교 (2개 이상)</t>
-        </is>
-      </c>
-      <c r="F161" s="13" t="inlineStr">
-        <is>
-          <t>ka10001</t>
-        </is>
-      </c>
-      <c r="G161" s="12" t="inlineStr">
-        <is>
-          <t>CODES (복수) (필수)</t>
-        </is>
-      </c>
-      <c r="H161" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B162" s="12" t="inlineStr">
-        <is>
-          <t>credit</t>
-        </is>
-      </c>
-      <c r="C162" s="12" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="D162" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock credit available</t>
-        </is>
-      </c>
-      <c r="E162" s="12" t="inlineStr">
-        <is>
-          <t>신용융자 가능종목 조회</t>
-        </is>
-      </c>
-      <c r="F162" s="13" t="inlineStr">
-        <is>
-          <t>kt20016</t>
-        </is>
-      </c>
-      <c r="G162" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H162" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="163">
       <c r="A163" s="12" t="inlineStr">
         <is>
@@ -7365,32 +7358,32 @@
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>credit</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>inquiry</t>
+          <t>compare</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock credit inquiry</t>
+          <t>kiwoom stock compare</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr">
         <is>
-          <t>신용융자 가능문의</t>
+          <t>종목 비교 (2개 이상)</t>
         </is>
       </c>
       <c r="F163" s="13" t="inlineStr">
         <is>
-          <t>kt20017</t>
+          <t>ka10001</t>
         </is>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H163" s="12" t="inlineStr">
@@ -7412,205 +7405,205 @@
       </c>
       <c r="C164" s="12" t="inlineStr">
         <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="D164" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock credit available</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>신용융자 가능종목 조회</t>
+        </is>
+      </c>
+      <c r="F164" s="13" t="inlineStr">
+        <is>
+          <t>kt20016</t>
+        </is>
+      </c>
+      <c r="G164" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H164" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="inlineStr">
+        <is>
+          <t>credit</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="inlineStr">
+        <is>
+          <t>inquiry</t>
+        </is>
+      </c>
+      <c r="D165" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock credit inquiry</t>
+        </is>
+      </c>
+      <c r="E165" s="12" t="inlineStr">
+        <is>
+          <t>신용융자 가능문의</t>
+        </is>
+      </c>
+      <c r="F165" s="13" t="inlineStr">
+        <is>
+          <t>kt20017</t>
+        </is>
+      </c>
+      <c r="G165" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B166" s="12" t="inlineStr">
+        <is>
+          <t>credit</t>
+        </is>
+      </c>
+      <c r="C166" s="12" t="inlineStr">
+        <is>
           <t>trend</t>
         </is>
       </c>
-      <c r="D164" s="12" t="inlineStr">
+      <c r="D166" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock credit trend</t>
         </is>
       </c>
-      <c r="E164" s="12" t="inlineStr">
+      <c r="E166" s="12" t="inlineStr">
         <is>
           <t>신용매매동향 조회</t>
         </is>
       </c>
-      <c r="F164" s="13" t="inlineStr">
+      <c r="F166" s="13" t="inlineStr">
         <is>
           <t>ka10013</t>
         </is>
       </c>
-      <c r="G164" s="12" t="inlineStr">
+      <c r="G166" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H164" s="12" t="inlineStr">
+      <c r="H166" s="12" t="inlineStr">
         <is>
           <t>--date *필수 (일자 (YYYYMMDD))
 --type [loan, short-sell] 기본:loan (구분 (loan=융자, short-sell=대주))</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="12" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B165" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C165" s="12" t="inlineStr">
+      <c r="B167" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C167" s="12" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="D165" s="12" t="inlineStr">
+      <c r="D167" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock daily</t>
         </is>
       </c>
-      <c r="E165" s="12" t="inlineStr">
+      <c r="E167" s="12" t="inlineStr">
         <is>
           <t>일/주/월별 시세 조회</t>
         </is>
       </c>
-      <c r="F165" s="13" t="inlineStr">
+      <c r="F167" s="13" t="inlineStr">
         <is>
           <t>ka10005</t>
         </is>
       </c>
-      <c r="G165" s="12" t="inlineStr">
+      <c r="G167" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H165" s="12" t="inlineStr">
+      <c r="H167" s="12" t="inlineStr">
         <is>
           <t>--type [day, week, month] 기본:day (조회 구분 (day/week/month))</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="12" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B166" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C166" s="12" t="inlineStr">
+      <c r="B168" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C168" s="12" t="inlineStr">
         <is>
           <t>daily-price</t>
         </is>
       </c>
-      <c r="D166" s="12" t="inlineStr">
+      <c r="D168" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock daily-price</t>
         </is>
       </c>
-      <c r="E166" s="12" t="inlineStr">
+      <c r="E168" s="12" t="inlineStr">
         <is>
           <t>일별주가 조회</t>
         </is>
       </c>
-      <c r="F166" s="13" t="inlineStr">
+      <c r="F168" s="13" t="inlineStr">
         <is>
           <t>ka10086</t>
         </is>
       </c>
-      <c r="G166" s="12" t="inlineStr">
+      <c r="G168" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H166" s="12" t="inlineStr">
+      <c r="H168" s="12" t="inlineStr">
         <is>
           <t>--date *필수 (조회일자 (YYYYMMDD))
 --display [0, 1] (표시구분 (0=수량, 1=금액백만원))</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B167" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C167" s="12" t="inlineStr">
-        <is>
-          <t>daily-strength</t>
-        </is>
-      </c>
-      <c r="D167" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock daily-strength</t>
-        </is>
-      </c>
-      <c r="E167" s="12" t="inlineStr">
-        <is>
-          <t>체결강도추이 일별</t>
-        </is>
-      </c>
-      <c r="F167" s="13" t="inlineStr">
-        <is>
-          <t>ka10047</t>
-        </is>
-      </c>
-      <c r="G167" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H167" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B168" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C168" s="12" t="inlineStr">
-        <is>
-          <t>detail</t>
-        </is>
-      </c>
-      <c r="D168" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock detail</t>
-        </is>
-      </c>
-      <c r="E168" s="12" t="inlineStr">
-        <is>
-          <t>종목정보 상세 조회</t>
-        </is>
-      </c>
-      <c r="F168" s="13" t="inlineStr">
-        <is>
-          <t>ka10100</t>
-        </is>
-      </c>
-      <c r="G168" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H168" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="169">
       <c r="A169" s="12" t="inlineStr">
         <is>
@@ -7624,22 +7617,22 @@
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>exec</t>
+          <t>daily-strength</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock exec</t>
+          <t>kiwoom stock daily-strength</t>
         </is>
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>체결정보 조회</t>
+          <t>체결강도추이 일별</t>
         </is>
       </c>
       <c r="F169" s="13" t="inlineStr">
         <is>
-          <t>ka10003</t>
+          <t>ka10047</t>
         </is>
       </c>
       <c r="G169" s="12" t="inlineStr">
@@ -7666,22 +7659,22 @@
       </c>
       <c r="C170" s="12" t="inlineStr">
         <is>
-          <t>foreign</t>
+          <t>detail</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock foreign</t>
+          <t>kiwoom stock detail</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr">
         <is>
-          <t>외국인 종목별 매매동향 조회</t>
+          <t>종목정보 상세 조회</t>
         </is>
       </c>
       <c r="F170" s="13" t="inlineStr">
         <is>
-          <t>ka10008</t>
+          <t>ka10100</t>
         </is>
       </c>
       <c r="G170" s="12" t="inlineStr">
@@ -7708,22 +7701,22 @@
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>exec</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock info</t>
+          <t>kiwoom stock exec</t>
         </is>
       </c>
       <c r="E171" s="12" t="inlineStr">
         <is>
-          <t>종목 기본정보 조회</t>
+          <t>체결정보 조회</t>
         </is>
       </c>
       <c r="F171" s="13" t="inlineStr">
         <is>
-          <t>ka10001</t>
+          <t>ka10003</t>
         </is>
       </c>
       <c r="G171" s="12" t="inlineStr">
@@ -7750,22 +7743,22 @@
       </c>
       <c r="C172" s="12" t="inlineStr">
         <is>
-          <t>institution</t>
+          <t>foreign</t>
         </is>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock institution</t>
+          <t>kiwoom stock foreign</t>
         </is>
       </c>
       <c r="E172" s="12" t="inlineStr">
         <is>
-          <t>주식기관 조회</t>
+          <t>외국인 종목별 매매동향 조회</t>
         </is>
       </c>
       <c r="F172" s="13" t="inlineStr">
         <is>
-          <t>ka10009</t>
+          <t>ka10008</t>
         </is>
       </c>
       <c r="G172" s="12" t="inlineStr">
@@ -7787,35 +7780,119 @@
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C173" s="12" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D173" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock info</t>
+        </is>
+      </c>
+      <c r="E173" s="12" t="inlineStr">
+        <is>
+          <t>종목 기본정보 조회</t>
+        </is>
+      </c>
+      <c r="F173" s="13" t="inlineStr">
+        <is>
+          <t>ka10001</t>
+        </is>
+      </c>
+      <c r="G173" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H173" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B174" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C174" s="12" t="inlineStr">
+        <is>
+          <t>institution</t>
+        </is>
+      </c>
+      <c r="D174" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock institution</t>
+        </is>
+      </c>
+      <c r="E174" s="12" t="inlineStr">
+        <is>
+          <t>주식기관 조회</t>
+        </is>
+      </c>
+      <c r="F174" s="13" t="inlineStr">
+        <is>
+          <t>ka10009</t>
+        </is>
+      </c>
+      <c r="G174" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H174" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B175" s="12" t="inlineStr">
+        <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C173" s="12" t="inlineStr">
+      <c r="C175" s="12" t="inlineStr">
         <is>
           <t>after-close</t>
         </is>
       </c>
-      <c r="D173" s="12" t="inlineStr">
+      <c r="D175" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor after-close</t>
         </is>
       </c>
-      <c r="E173" s="12" t="inlineStr">
+      <c r="E175" s="12" t="inlineStr">
         <is>
           <t>장마감후투자자별매매 조회</t>
         </is>
       </c>
-      <c r="F173" s="13" t="inlineStr">
+      <c r="F175" s="13" t="inlineStr">
         <is>
           <t>ka10066</t>
         </is>
       </c>
-      <c r="G173" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="12" t="inlineStr">
+      <c r="G175" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="12" t="inlineStr">
         <is>
           <t>--market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
 --amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
@@ -7824,43 +7901,43 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="12" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B174" s="12" t="inlineStr">
+      <c r="B176" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C174" s="12" t="inlineStr">
+      <c r="C176" s="12" t="inlineStr">
         <is>
           <t>by-stock</t>
         </is>
       </c>
-      <c r="D174" s="12" t="inlineStr">
+      <c r="D176" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor by-stock</t>
         </is>
       </c>
-      <c r="E174" s="12" t="inlineStr">
+      <c r="E176" s="12" t="inlineStr">
         <is>
           <t>종목별투자자기관별 조회</t>
         </is>
       </c>
-      <c r="F174" s="13" t="inlineStr">
+      <c r="F176" s="13" t="inlineStr">
         <is>
           <t>ka10059</t>
         </is>
       </c>
-      <c r="G174" s="12" t="inlineStr">
+      <c r="G176" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H174" s="12" t="inlineStr">
+      <c r="H176" s="12" t="inlineStr">
         <is>
           <t>--date *필수 (일자 (YYYYMMDD))
 --amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
@@ -7869,43 +7946,43 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="12" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B175" s="12" t="inlineStr">
+      <c r="B177" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C175" s="12" t="inlineStr">
+      <c r="C177" s="12" t="inlineStr">
         <is>
           <t>by-stock-total</t>
         </is>
       </c>
-      <c r="D175" s="12" t="inlineStr">
+      <c r="D177" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor by-stock-total</t>
         </is>
       </c>
-      <c r="E175" s="12" t="inlineStr">
+      <c r="E177" s="12" t="inlineStr">
         <is>
           <t>종목별투자자기관별합계 조회</t>
         </is>
       </c>
-      <c r="F175" s="13" t="inlineStr">
+      <c r="F177" s="13" t="inlineStr">
         <is>
           <t>ka10061</t>
         </is>
       </c>
-      <c r="G175" s="12" t="inlineStr">
+      <c r="G177" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H175" s="12" t="inlineStr">
+      <c r="H177" s="12" t="inlineStr">
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
@@ -7915,43 +7992,43 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="12" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B176" s="12" t="inlineStr">
+      <c r="B178" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C176" s="12" t="inlineStr">
+      <c r="C178" s="12" t="inlineStr">
         <is>
           <t>consecutive</t>
         </is>
       </c>
-      <c r="D176" s="12" t="inlineStr">
+      <c r="D178" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor consecutive</t>
         </is>
       </c>
-      <c r="E176" s="12" t="inlineStr">
+      <c r="E178" s="12" t="inlineStr">
         <is>
           <t>기관/외국인 연속매매현황 조회</t>
         </is>
       </c>
-      <c r="F176" s="13" t="inlineStr">
+      <c r="F178" s="13" t="inlineStr">
         <is>
           <t>ka10131</t>
         </is>
       </c>
-      <c r="G176" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H176" s="12" t="inlineStr">
+      <c r="G178" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" s="12" t="inlineStr">
         <is>
           <t>--period 기본:5 (기간 (일수))
 --from (시작일자 (YYYYMMDD, 선택))
@@ -7964,43 +8041,43 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="12" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B177" s="12" t="inlineStr">
+      <c r="B179" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C177" s="12" t="inlineStr">
+      <c r="C179" s="12" t="inlineStr">
         <is>
           <t>daily-by-investor</t>
         </is>
       </c>
-      <c r="D177" s="12" t="inlineStr">
+      <c r="D179" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor daily-by-investor</t>
         </is>
       </c>
-      <c r="E177" s="12" t="inlineStr">
+      <c r="E179" s="12" t="inlineStr">
         <is>
           <t>투자자별일별매매종목 조회</t>
         </is>
       </c>
-      <c r="F177" s="13" t="inlineStr">
+      <c r="F179" s="13" t="inlineStr">
         <is>
           <t>ka10058</t>
         </is>
       </c>
-      <c r="G177" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H177" s="12" t="inlineStr">
+      <c r="G179" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="12" t="inlineStr">
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
@@ -8011,43 +8088,43 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="12" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B178" s="12" t="inlineStr">
+      <c r="B180" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C178" s="12" t="inlineStr">
+      <c r="C180" s="12" t="inlineStr">
         <is>
           <t>daily-trade</t>
         </is>
       </c>
-      <c r="D178" s="12" t="inlineStr">
+      <c r="D180" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor daily-trade</t>
         </is>
       </c>
-      <c r="E178" s="12" t="inlineStr">
+      <c r="E180" s="12" t="inlineStr">
         <is>
           <t>일별기관매매종목 조회</t>
         </is>
       </c>
-      <c r="F178" s="13" t="inlineStr">
+      <c r="F180" s="13" t="inlineStr">
         <is>
           <t>ka10044</t>
         </is>
       </c>
-      <c r="G178" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H178" s="12" t="inlineStr">
+      <c r="G180" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H180" s="12" t="inlineStr">
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
@@ -8057,43 +8134,43 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="12" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B179" s="12" t="inlineStr">
+      <c r="B181" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C179" s="12" t="inlineStr">
+      <c r="C181" s="12" t="inlineStr">
         <is>
           <t>intraday</t>
         </is>
       </c>
-      <c r="D179" s="12" t="inlineStr">
+      <c r="D181" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor intraday</t>
         </is>
       </c>
-      <c r="E179" s="12" t="inlineStr">
+      <c r="E181" s="12" t="inlineStr">
         <is>
           <t>장중투자자별매매 조회</t>
         </is>
       </c>
-      <c r="F179" s="13" t="inlineStr">
+      <c r="F181" s="13" t="inlineStr">
         <is>
           <t>ka10063</t>
         </is>
       </c>
-      <c r="G179" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H179" s="12" t="inlineStr">
+      <c r="G181" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="12" t="inlineStr">
         <is>
           <t>--market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
 --amount-qty 기본:1 (금액수량구분 (1=금액&amp;수량))
@@ -8104,43 +8181,43 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="12" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B180" s="12" t="inlineStr">
+      <c r="B182" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C180" s="12" t="inlineStr">
+      <c r="C182" s="12" t="inlineStr">
         <is>
           <t>program-by-stock</t>
         </is>
       </c>
-      <c r="D180" s="12" t="inlineStr">
+      <c r="D182" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor program-by-stock</t>
         </is>
       </c>
-      <c r="E180" s="12" t="inlineStr">
+      <c r="E182" s="12" t="inlineStr">
         <is>
           <t>종목별프로그램매매현황 조회</t>
         </is>
       </c>
-      <c r="F180" s="13" t="inlineStr">
+      <c r="F182" s="13" t="inlineStr">
         <is>
           <t>ka90004</t>
         </is>
       </c>
-      <c r="G180" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H180" s="12" t="inlineStr">
+      <c r="G182" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" s="12" t="inlineStr">
         <is>
           <t>--date *필수 (일자 (YYYYMMDD))
 --market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
@@ -8148,43 +8225,43 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="12" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B181" s="12" t="inlineStr">
+      <c r="B183" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C181" s="12" t="inlineStr">
+      <c r="C183" s="12" t="inlineStr">
         <is>
           <t>program-top</t>
         </is>
       </c>
-      <c r="D181" s="12" t="inlineStr">
+      <c r="D183" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor program-top</t>
         </is>
       </c>
-      <c r="E181" s="12" t="inlineStr">
+      <c r="E183" s="12" t="inlineStr">
         <is>
           <t>프로그램순매수상위50 조회</t>
         </is>
       </c>
-      <c r="F181" s="13" t="inlineStr">
+      <c r="F183" s="13" t="inlineStr">
         <is>
           <t>ka90003</t>
         </is>
       </c>
-      <c r="G181" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H181" s="12" t="inlineStr">
+      <c r="G183" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="12" t="inlineStr">
         <is>
           <t>--trade [1, 2] 기본:2 (매매구분 (1=순매도, 2=순매수))
 --amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
@@ -8193,43 +8270,43 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="12" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B182" s="12" t="inlineStr">
+      <c r="B184" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C182" s="12" t="inlineStr">
+      <c r="C184" s="12" t="inlineStr">
         <is>
           <t>stock-institution</t>
         </is>
       </c>
-      <c r="D182" s="12" t="inlineStr">
+      <c r="D184" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor stock-institution</t>
         </is>
       </c>
-      <c r="E182" s="12" t="inlineStr">
+      <c r="E184" s="12" t="inlineStr">
         <is>
           <t>종목별기관매매추이 조회</t>
         </is>
       </c>
-      <c r="F182" s="13" t="inlineStr">
+      <c r="F184" s="13" t="inlineStr">
         <is>
           <t>ka10045</t>
         </is>
       </c>
-      <c r="G182" s="12" t="inlineStr">
+      <c r="G184" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H182" s="12" t="inlineStr">
+      <c r="H184" s="12" t="inlineStr">
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
@@ -8238,43 +8315,43 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="12" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B183" s="12" t="inlineStr">
+      <c r="B185" s="12" t="inlineStr">
         <is>
           <t>lending</t>
         </is>
       </c>
-      <c r="C183" s="12" t="inlineStr">
+      <c r="C185" s="12" t="inlineStr">
         <is>
           <t>by-stock</t>
         </is>
       </c>
-      <c r="D183" s="12" t="inlineStr">
+      <c r="D185" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock lending by-stock</t>
         </is>
       </c>
-      <c r="E183" s="12" t="inlineStr">
+      <c r="E185" s="12" t="inlineStr">
         <is>
           <t>대차거래추이 종목별 조회</t>
         </is>
       </c>
-      <c r="F183" s="13" t="inlineStr">
+      <c r="F185" s="13" t="inlineStr">
         <is>
           <t>ka20068</t>
         </is>
       </c>
-      <c r="G183" s="12" t="inlineStr">
+      <c r="G185" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H183" s="12" t="inlineStr">
+      <c r="H185" s="12" t="inlineStr">
         <is>
           <t>--from (시작일자 (YYYYMMDD, 선택))
 --to (종료일자 (YYYYMMDD, 선택))
@@ -8282,86 +8359,86 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="12" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B184" s="12" t="inlineStr">
+      <c r="B186" s="12" t="inlineStr">
         <is>
           <t>lending</t>
         </is>
       </c>
-      <c r="C184" s="12" t="inlineStr">
+      <c r="C186" s="12" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="D184" s="12" t="inlineStr">
+      <c r="D186" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock lending detail</t>
         </is>
       </c>
-      <c r="E184" s="12" t="inlineStr">
+      <c r="E186" s="12" t="inlineStr">
         <is>
           <t>대차거래내역 조회</t>
         </is>
       </c>
-      <c r="F184" s="13" t="inlineStr">
+      <c r="F186" s="13" t="inlineStr">
         <is>
           <t>ka90012</t>
         </is>
       </c>
-      <c r="G184" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H184" s="12" t="inlineStr">
+      <c r="G186" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" s="12" t="inlineStr">
         <is>
           <t>--date *필수 (일자 (YYYYMMDD))
 --market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="12" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B185" s="12" t="inlineStr">
+      <c r="B187" s="12" t="inlineStr">
         <is>
           <t>lending</t>
         </is>
       </c>
-      <c r="C185" s="12" t="inlineStr">
+      <c r="C187" s="12" t="inlineStr">
         <is>
           <t>top10</t>
         </is>
       </c>
-      <c r="D185" s="12" t="inlineStr">
+      <c r="D187" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock lending top10</t>
         </is>
       </c>
-      <c r="E185" s="12" t="inlineStr">
+      <c r="E187" s="12" t="inlineStr">
         <is>
           <t>대차거래상위10종목 조회</t>
         </is>
       </c>
-      <c r="F185" s="13" t="inlineStr">
+      <c r="F187" s="13" t="inlineStr">
         <is>
           <t>ka10069</t>
         </is>
       </c>
-      <c r="G185" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H185" s="12" t="inlineStr">
+      <c r="G187" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" s="12" t="inlineStr">
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to (종료일자 (YYYYMMDD, 선택))
@@ -8369,43 +8446,43 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="12" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B186" s="12" t="inlineStr">
+      <c r="B188" s="12" t="inlineStr">
         <is>
           <t>lending</t>
         </is>
       </c>
-      <c r="C186" s="12" t="inlineStr">
+      <c r="C188" s="12" t="inlineStr">
         <is>
           <t>trend</t>
         </is>
       </c>
-      <c r="D186" s="12" t="inlineStr">
+      <c r="D188" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock lending trend</t>
         </is>
       </c>
-      <c r="E186" s="12" t="inlineStr">
+      <c r="E188" s="12" t="inlineStr">
         <is>
           <t>대차거래추이 조회</t>
         </is>
       </c>
-      <c r="F186" s="13" t="inlineStr">
+      <c r="F188" s="13" t="inlineStr">
         <is>
           <t>ka10068</t>
         </is>
       </c>
-      <c r="G186" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H186" s="12" t="inlineStr">
+      <c r="G188" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" s="12" t="inlineStr">
         <is>
           <t>--from (시작일자 (YYYYMMDD, 선택))
 --to (종료일자 (YYYYMMDD, 선택))
@@ -8413,86 +8490,6 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B187" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C187" s="12" t="inlineStr">
-        <is>
-          <t>orderbook</t>
-        </is>
-      </c>
-      <c r="D187" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock orderbook</t>
-        </is>
-      </c>
-      <c r="E187" s="12" t="inlineStr">
-        <is>
-          <t>호가창 조회</t>
-        </is>
-      </c>
-      <c r="F187" s="13" t="inlineStr">
-        <is>
-          <t>ka10004</t>
-        </is>
-      </c>
-      <c r="G187" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H187" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B188" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C188" s="12" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="D188" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock price</t>
-        </is>
-      </c>
-      <c r="E188" s="12" t="inlineStr">
-        <is>
-          <t>종목 현재가 간단 조회</t>
-        </is>
-      </c>
-      <c r="F188" s="13" t="inlineStr"/>
-      <c r="G188" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H188" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="189">
       <c r="A189" s="12" t="inlineStr">
         <is>
@@ -8506,22 +8503,22 @@
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>quote-info</t>
+          <t>orderbook</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock quote-info</t>
+          <t>kiwoom stock orderbook</t>
         </is>
       </c>
       <c r="E189" s="12" t="inlineStr">
         <is>
-          <t>시세표성정보 조회</t>
+          <t>호가창 조회</t>
         </is>
       </c>
       <c r="F189" s="13" t="inlineStr">
         <is>
-          <t>ka10007</t>
+          <t>ka10004</t>
         </is>
       </c>
       <c r="G189" s="12" t="inlineStr">
@@ -8548,32 +8545,28 @@
       </c>
       <c r="C190" s="12" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>price</t>
         </is>
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock search</t>
+          <t>kiwoom stock price</t>
         </is>
       </c>
       <c r="E190" s="12" t="inlineStr">
         <is>
-          <t>종목 리스트 / 검색</t>
-        </is>
-      </c>
-      <c r="F190" s="13" t="inlineStr">
-        <is>
-          <t>ka10099</t>
-        </is>
-      </c>
+          <t>종목 현재가 간단 조회</t>
+        </is>
+      </c>
+      <c r="F190" s="13" t="inlineStr"/>
       <c r="G190" s="12" t="inlineStr">
         <is>
-          <t>KEYWORD (선택)</t>
+          <t>CODE (필수)</t>
         </is>
       </c>
       <c r="H190" s="12" t="inlineStr">
         <is>
-          <t>--market [all, kospi, kosdaq, k-otc, konex, etf, elw] 기본:all (시장구분 (all/kospi/kosdaq/k-otc/konex/etf/elw))</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8590,120 +8583,116 @@
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
+          <t>quote-info</t>
+        </is>
+      </c>
+      <c r="D191" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock quote-info</t>
+        </is>
+      </c>
+      <c r="E191" s="12" t="inlineStr">
+        <is>
+          <t>시세표성정보 조회</t>
+        </is>
+      </c>
+      <c r="F191" s="13" t="inlineStr">
+        <is>
+          <t>ka10007</t>
+        </is>
+      </c>
+      <c r="G191" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H191" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B192" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C192" s="12" t="inlineStr">
+        <is>
+          <t>search</t>
+        </is>
+      </c>
+      <c r="D192" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock search</t>
+        </is>
+      </c>
+      <c r="E192" s="12" t="inlineStr">
+        <is>
+          <t>캐시에서 종목 검색</t>
+        </is>
+      </c>
+      <c r="F192" s="13" t="inlineStr"/>
+      <c r="G192" s="12" t="inlineStr">
+        <is>
+          <t>KEYWORD (선택)</t>
+        </is>
+      </c>
+      <c r="H192" s="12" t="inlineStr">
+        <is>
+          <t>--market [all, kospi, kosdaq, etf, elw, etn] 기본:all (시장/유형 필터 (all/kospi/kosdaq/etf/elw/etn))</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B193" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C193" s="12" t="inlineStr">
+        <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D191" s="12" t="inlineStr">
+      <c r="D193" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock short</t>
         </is>
       </c>
-      <c r="E191" s="12" t="inlineStr">
+      <c r="E193" s="12" t="inlineStr">
         <is>
           <t>공매도 추이 조회</t>
         </is>
       </c>
-      <c r="F191" s="13" t="inlineStr">
+      <c r="F193" s="13" t="inlineStr">
         <is>
           <t>ka10014</t>
         </is>
       </c>
-      <c r="G191" s="12" t="inlineStr">
+      <c r="G193" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H191" s="12" t="inlineStr">
+      <c r="H193" s="12" t="inlineStr">
         <is>
           <t>--from (시작일자 (YYYYMMDD, 기본=30일전))
 --to (종료일자 (YYYYMMDD, 기본=오늘))</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B192" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C192" s="12" t="inlineStr">
-        <is>
-          <t>tick-strength</t>
-        </is>
-      </c>
-      <c r="D192" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock tick-strength</t>
-        </is>
-      </c>
-      <c r="E192" s="12" t="inlineStr">
-        <is>
-          <t>체결강도추이 시간별</t>
-        </is>
-      </c>
-      <c r="F192" s="13" t="inlineStr">
-        <is>
-          <t>ka10046</t>
-        </is>
-      </c>
-      <c r="G192" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H192" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B193" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C193" s="12" t="inlineStr">
-        <is>
-          <t>timeprice</t>
-        </is>
-      </c>
-      <c r="D193" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock timeprice</t>
-        </is>
-      </c>
-      <c r="E193" s="12" t="inlineStr">
-        <is>
-          <t>시분 시세 조회</t>
-        </is>
-      </c>
-      <c r="F193" s="13" t="inlineStr">
-        <is>
-          <t>ka10006</t>
-        </is>
-      </c>
-      <c r="G193" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H193" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="194">
       <c r="A194" s="12" t="inlineStr">
         <is>
@@ -8717,30 +8706,156 @@
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
+          <t>sync</t>
+        </is>
+      </c>
+      <c r="D194" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock sync</t>
+        </is>
+      </c>
+      <c r="E194" s="12" t="inlineStr">
+        <is>
+          <t>전 시장 종목 리스트를 다운받아 캐시에 저장</t>
+        </is>
+      </c>
+      <c r="F194" s="13" t="inlineStr">
+        <is>
+          <t>ka10099</t>
+        </is>
+      </c>
+      <c r="G194" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H194" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B195" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C195" s="12" t="inlineStr">
+        <is>
+          <t>tick-strength</t>
+        </is>
+      </c>
+      <c r="D195" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock tick-strength</t>
+        </is>
+      </c>
+      <c r="E195" s="12" t="inlineStr">
+        <is>
+          <t>체결강도추이 시간별</t>
+        </is>
+      </c>
+      <c r="F195" s="13" t="inlineStr">
+        <is>
+          <t>ka10046</t>
+        </is>
+      </c>
+      <c r="G195" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H195" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B196" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C196" s="12" t="inlineStr">
+        <is>
+          <t>timeprice</t>
+        </is>
+      </c>
+      <c r="D196" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock timeprice</t>
+        </is>
+      </c>
+      <c r="E196" s="12" t="inlineStr">
+        <is>
+          <t>시분 시세 조회</t>
+        </is>
+      </c>
+      <c r="F196" s="13" t="inlineStr">
+        <is>
+          <t>ka10006</t>
+        </is>
+      </c>
+      <c r="G196" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H196" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B197" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C197" s="12" t="inlineStr">
+        <is>
           <t>today-exec</t>
         </is>
       </c>
-      <c r="D194" s="12" t="inlineStr">
+      <c r="D197" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock today-exec</t>
         </is>
       </c>
-      <c r="E194" s="12" t="inlineStr">
+      <c r="E197" s="12" t="inlineStr">
         <is>
           <t>당일/전일 체결 조회</t>
         </is>
       </c>
-      <c r="F194" s="13" t="inlineStr">
+      <c r="F197" s="13" t="inlineStr">
         <is>
           <t>ka10084</t>
         </is>
       </c>
-      <c r="G194" s="12" t="inlineStr">
+      <c r="G197" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H194" s="12" t="inlineStr">
+      <c r="H197" s="12" t="inlineStr">
         <is>
           <t>--when [1, 2] 기본:1 (당일전일 (1=당일, 2=전일))
 --mode [0, 1] (틱/분 (0=틱, 1=분))
@@ -8748,243 +8863,129 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="12" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B195" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C195" s="12" t="inlineStr">
+      <c r="B198" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C198" s="12" t="inlineStr">
         <is>
           <t>today-volume</t>
         </is>
       </c>
-      <c r="D195" s="12" t="inlineStr">
+      <c r="D198" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock today-volume</t>
         </is>
       </c>
-      <c r="E195" s="12" t="inlineStr">
+      <c r="E198" s="12" t="inlineStr">
         <is>
           <t>당일/전일 체결량 조회</t>
         </is>
       </c>
-      <c r="F195" s="13" t="inlineStr">
+      <c r="F198" s="13" t="inlineStr">
         <is>
           <t>ka10055</t>
         </is>
       </c>
-      <c r="G195" s="12" t="inlineStr">
+      <c r="G198" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H195" s="12" t="inlineStr">
+      <c r="H198" s="12" t="inlineStr">
         <is>
           <t>--when [1, 2] 기본:1 (당일전일 (1=당일, 2=전일))</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="12" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B196" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C196" s="12" t="inlineStr">
+      <c r="B199" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C199" s="12" t="inlineStr">
         <is>
           <t>trader</t>
         </is>
       </c>
-      <c r="D196" s="12" t="inlineStr">
+      <c r="D199" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock trader</t>
         </is>
       </c>
-      <c r="E196" s="12" t="inlineStr">
+      <c r="E199" s="12" t="inlineStr">
         <is>
           <t>거래원 조회</t>
         </is>
       </c>
-      <c r="F196" s="13" t="inlineStr">
+      <c r="F199" s="13" t="inlineStr">
         <is>
           <t>ka10002</t>
         </is>
       </c>
-      <c r="G196" s="12" t="inlineStr">
+      <c r="G199" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H196" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="12" t="inlineStr">
+      <c r="H199" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B197" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C197" s="12" t="inlineStr">
+      <c r="B200" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C200" s="12" t="inlineStr">
         <is>
           <t>watchlist</t>
         </is>
       </c>
-      <c r="D197" s="12" t="inlineStr">
+      <c r="D200" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock watchlist</t>
         </is>
       </c>
-      <c r="E197" s="12" t="inlineStr">
+      <c r="E200" s="12" t="inlineStr">
         <is>
           <t>관심종목정보 조회 (코드를 |로 구분, 예: 005930|000660)</t>
         </is>
       </c>
-      <c r="F197" s="13" t="inlineStr">
+      <c r="F200" s="13" t="inlineStr">
         <is>
           <t>ka10095</t>
         </is>
       </c>
-      <c r="G197" s="12" t="inlineStr">
+      <c r="G200" s="12" t="inlineStr">
         <is>
           <t>CODES (필수)</t>
         </is>
       </c>
-      <c r="H197" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="14" t="inlineStr">
-        <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="B198" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C198" s="14" t="inlineStr">
-        <is>
-          <t>after-hours</t>
-        </is>
-      </c>
-      <c r="D198" s="14" t="inlineStr">
-        <is>
-          <t>kiwoom stream after-hours</t>
-        </is>
-      </c>
-      <c r="E198" s="14" t="inlineStr">
-        <is>
-          <t>주식시간외호가 실시간 (0E)</t>
-        </is>
-      </c>
-      <c r="F198" s="15" t="inlineStr"/>
-      <c r="G198" s="14" t="inlineStr">
-        <is>
-          <t>CODES (복수) (필수)</t>
-        </is>
-      </c>
-      <c r="H198" s="14" t="inlineStr">
-        <is>
-          <t>--raw (JSON 원본 출력)</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="14" t="inlineStr">
-        <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="B199" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C199" s="14" t="inlineStr">
-        <is>
-          <t>balance</t>
-        </is>
-      </c>
-      <c r="D199" s="14" t="inlineStr">
-        <is>
-          <t>kiwoom stream balance</t>
-        </is>
-      </c>
-      <c r="E199" s="14" t="inlineStr">
-        <is>
-          <t>잔고 실시간 (04)</t>
-        </is>
-      </c>
-      <c r="F199" s="15" t="inlineStr"/>
-      <c r="G199" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H199" s="14" t="inlineStr">
-        <is>
-          <t>--raw (JSON 원본 출력)</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="14" t="inlineStr">
-        <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="B200" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C200" s="14" t="inlineStr">
-        <is>
-          <t>best-bid</t>
-        </is>
-      </c>
-      <c r="D200" s="14" t="inlineStr">
-        <is>
-          <t>kiwoom stream best-bid</t>
-        </is>
-      </c>
-      <c r="E200" s="14" t="inlineStr">
-        <is>
-          <t>주식우선호가 실시간 (0C)</t>
-        </is>
-      </c>
-      <c r="F200" s="15" t="inlineStr"/>
-      <c r="G200" s="14" t="inlineStr">
-        <is>
-          <t>CODES (복수) (필수)</t>
-        </is>
-      </c>
-      <c r="H200" s="14" t="inlineStr">
-        <is>
-          <t>--raw (JSON 원본 출력)</t>
+      <c r="H200" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9001,140 +9002,140 @@
       </c>
       <c r="C201" s="14" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>after-hours</t>
         </is>
       </c>
       <c r="D201" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream custom</t>
+          <t>kiwoom stream after-hours</t>
         </is>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>커스텀 실시간 타입으로 스트리밍</t>
+          <t>주식시간외호가 실시간 (0E)</t>
         </is>
       </c>
       <c r="F201" s="15" t="inlineStr"/>
       <c r="G201" s="14" t="inlineStr">
         <is>
+          <t>CODES (복수) (필수)</t>
+        </is>
+      </c>
+      <c r="H201" s="14" t="inlineStr">
+        <is>
+          <t>--raw (JSON 원본 출력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="14" t="inlineStr">
+        <is>
+          <t>stream</t>
+        </is>
+      </c>
+      <c r="B202" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C202" s="14" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="D202" s="14" t="inlineStr">
+        <is>
+          <t>kiwoom stream balance</t>
+        </is>
+      </c>
+      <c r="E202" s="14" t="inlineStr">
+        <is>
+          <t>잔고 실시간 (04)</t>
+        </is>
+      </c>
+      <c r="F202" s="15" t="inlineStr"/>
+      <c r="G202" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" s="14" t="inlineStr">
+        <is>
+          <t>--raw (JSON 원본 출력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="14" t="inlineStr">
+        <is>
+          <t>stream</t>
+        </is>
+      </c>
+      <c r="B203" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C203" s="14" t="inlineStr">
+        <is>
+          <t>best-bid</t>
+        </is>
+      </c>
+      <c r="D203" s="14" t="inlineStr">
+        <is>
+          <t>kiwoom stream best-bid</t>
+        </is>
+      </c>
+      <c r="E203" s="14" t="inlineStr">
+        <is>
+          <t>주식우선호가 실시간 (0C)</t>
+        </is>
+      </c>
+      <c r="F203" s="15" t="inlineStr"/>
+      <c r="G203" s="14" t="inlineStr">
+        <is>
+          <t>CODES (복수) (필수)</t>
+        </is>
+      </c>
+      <c r="H203" s="14" t="inlineStr">
+        <is>
+          <t>--raw (JSON 원본 출력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="14" t="inlineStr">
+        <is>
+          <t>stream</t>
+        </is>
+      </c>
+      <c r="B204" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C204" s="14" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D204" s="14" t="inlineStr">
+        <is>
+          <t>kiwoom stream custom</t>
+        </is>
+      </c>
+      <c r="E204" s="14" t="inlineStr">
+        <is>
+          <t>커스텀 실시간 타입으로 스트리밍</t>
+        </is>
+      </c>
+      <c r="F204" s="15" t="inlineStr"/>
+      <c r="G204" s="14" t="inlineStr">
+        <is>
           <t>TYPE_CODES (필수)
 CODES (복수) (선택)</t>
         </is>
       </c>
-      <c r="H201" s="14" t="inlineStr">
-        <is>
-          <t>--raw (JSON 원본 출력)</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="14" t="inlineStr">
-        <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="B202" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C202" s="14" t="inlineStr">
-        <is>
-          <t>elw-indicator</t>
-        </is>
-      </c>
-      <c r="D202" s="14" t="inlineStr">
-        <is>
-          <t>kiwoom stream elw-indicator</t>
-        </is>
-      </c>
-      <c r="E202" s="14" t="inlineStr">
-        <is>
-          <t>ELW 지표 실시간 (0u)</t>
-        </is>
-      </c>
-      <c r="F202" s="15" t="inlineStr"/>
-      <c r="G202" s="14" t="inlineStr">
-        <is>
-          <t>CODES (복수) (필수)</t>
-        </is>
-      </c>
-      <c r="H202" s="14" t="inlineStr">
-        <is>
-          <t>--raw (JSON 원본 출력)</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="14" t="inlineStr">
-        <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="B203" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C203" s="14" t="inlineStr">
-        <is>
-          <t>elw-theory</t>
-        </is>
-      </c>
-      <c r="D203" s="14" t="inlineStr">
-        <is>
-          <t>kiwoom stream elw-theory</t>
-        </is>
-      </c>
-      <c r="E203" s="14" t="inlineStr">
-        <is>
-          <t>ELW 이론가 실시간 (0m)</t>
-        </is>
-      </c>
-      <c r="F203" s="15" t="inlineStr"/>
-      <c r="G203" s="14" t="inlineStr">
-        <is>
-          <t>CODES (복수) (필수)</t>
-        </is>
-      </c>
-      <c r="H203" s="14" t="inlineStr">
-        <is>
-          <t>--raw (JSON 원본 출력)</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="14" t="inlineStr">
-        <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="B204" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C204" s="14" t="inlineStr">
-        <is>
-          <t>etf-nav</t>
-        </is>
-      </c>
-      <c r="D204" s="14" t="inlineStr">
-        <is>
-          <t>kiwoom stream etf-nav</t>
-        </is>
-      </c>
-      <c r="E204" s="14" t="inlineStr">
-        <is>
-          <t>ETF NAV 실시간 (0G)</t>
-        </is>
-      </c>
-      <c r="F204" s="15" t="inlineStr"/>
-      <c r="G204" s="14" t="inlineStr">
-        <is>
-          <t>CODES (복수) (필수)</t>
-        </is>
-      </c>
       <c r="H204" s="14" t="inlineStr">
         <is>
           <t>--raw (JSON 원본 출력)</t>
@@ -9154,17 +9155,17 @@
       </c>
       <c r="C205" s="14" t="inlineStr">
         <is>
-          <t>expected</t>
+          <t>elw-indicator</t>
         </is>
       </c>
       <c r="D205" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream expected</t>
+          <t>kiwoom stream elw-indicator</t>
         </is>
       </c>
       <c r="E205" s="14" t="inlineStr">
         <is>
-          <t>주식예상체결 실시간 (0H)</t>
+          <t>ELW 지표 실시간 (0u)</t>
         </is>
       </c>
       <c r="F205" s="15" t="inlineStr"/>
@@ -9192,17 +9193,17 @@
       </c>
       <c r="C206" s="14" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>elw-theory</t>
         </is>
       </c>
       <c r="D206" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream gold</t>
+          <t>kiwoom stream elw-theory</t>
         </is>
       </c>
       <c r="E206" s="14" t="inlineStr">
         <is>
-          <t>국제금환산가격 실시간 (0I)</t>
+          <t>ELW 이론가 실시간 (0m)</t>
         </is>
       </c>
       <c r="F206" s="15" t="inlineStr"/>
@@ -9230,23 +9231,23 @@
       </c>
       <c r="C207" s="14" t="inlineStr">
         <is>
-          <t>market-time</t>
+          <t>etf-nav</t>
         </is>
       </c>
       <c r="D207" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream market-time</t>
+          <t>kiwoom stream etf-nav</t>
         </is>
       </c>
       <c r="E207" s="14" t="inlineStr">
         <is>
-          <t>장시작시간 실시간 (0s)</t>
+          <t>ETF NAV 실시간 (0G)</t>
         </is>
       </c>
       <c r="F207" s="15" t="inlineStr"/>
       <c r="G207" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H207" s="14" t="inlineStr">
@@ -9268,17 +9269,17 @@
       </c>
       <c r="C208" s="14" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>expected</t>
         </is>
       </c>
       <c r="D208" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream multi</t>
+          <t>kiwoom stream expected</t>
         </is>
       </c>
       <c r="E208" s="14" t="inlineStr">
         <is>
-          <t>주식체결+호가잔량 동시 스트리밍 (0B+0D)</t>
+          <t>주식예상체결 실시간 (0H)</t>
         </is>
       </c>
       <c r="F208" s="15" t="inlineStr"/>
@@ -9306,23 +9307,23 @@
       </c>
       <c r="C209" s="14" t="inlineStr">
         <is>
-          <t>order</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="D209" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream order</t>
+          <t>kiwoom stream gold</t>
         </is>
       </c>
       <c r="E209" s="14" t="inlineStr">
         <is>
-          <t>주문체결 실시간 (00)</t>
+          <t>국제금환산가격 실시간 (0I)</t>
         </is>
       </c>
       <c r="F209" s="15" t="inlineStr"/>
       <c r="G209" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H209" s="14" t="inlineStr">
@@ -9344,23 +9345,23 @@
       </c>
       <c r="C210" s="14" t="inlineStr">
         <is>
-          <t>orderbook</t>
+          <t>market-time</t>
         </is>
       </c>
       <c r="D210" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream orderbook</t>
+          <t>kiwoom stream market-time</t>
         </is>
       </c>
       <c r="E210" s="14" t="inlineStr">
         <is>
-          <t>주식호가잔량 실시간 (0D)</t>
+          <t>장시작시간 실시간 (0s)</t>
         </is>
       </c>
       <c r="F210" s="15" t="inlineStr"/>
       <c r="G210" s="14" t="inlineStr">
         <is>
-          <t>CODES (복수) (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H210" s="14" t="inlineStr">
@@ -9382,17 +9383,17 @@
       </c>
       <c r="C211" s="14" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="D211" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream price</t>
+          <t>kiwoom stream multi</t>
         </is>
       </c>
       <c r="E211" s="14" t="inlineStr">
         <is>
-          <t>주식기세 실시간 (0A)</t>
+          <t>주식체결+호가잔량 동시 스트리밍 (0B+0D)</t>
         </is>
       </c>
       <c r="F211" s="15" t="inlineStr"/>
@@ -9420,23 +9421,23 @@
       </c>
       <c r="C212" s="14" t="inlineStr">
         <is>
-          <t>program</t>
+          <t>order</t>
         </is>
       </c>
       <c r="D212" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream program</t>
+          <t>kiwoom stream order</t>
         </is>
       </c>
       <c r="E212" s="14" t="inlineStr">
         <is>
-          <t>종목프로그램매매 실시간 (0w)</t>
+          <t>주문체결 실시간 (00)</t>
         </is>
       </c>
       <c r="F212" s="15" t="inlineStr"/>
       <c r="G212" s="14" t="inlineStr">
         <is>
-          <t>CODES (복수) (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H212" s="14" t="inlineStr">
@@ -9458,17 +9459,17 @@
       </c>
       <c r="C213" s="14" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>orderbook</t>
         </is>
       </c>
       <c r="D213" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream quote</t>
+          <t>kiwoom stream orderbook</t>
         </is>
       </c>
       <c r="E213" s="14" t="inlineStr">
         <is>
-          <t>주식체결 실시간 (0B)</t>
+          <t>주식호가잔량 실시간 (0D)</t>
         </is>
       </c>
       <c r="F213" s="15" t="inlineStr"/>
@@ -9496,17 +9497,17 @@
       </c>
       <c r="C214" s="14" t="inlineStr">
         <is>
-          <t>sector-change</t>
+          <t>price</t>
         </is>
       </c>
       <c r="D214" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream sector-change</t>
+          <t>kiwoom stream price</t>
         </is>
       </c>
       <c r="E214" s="14" t="inlineStr">
         <is>
-          <t>업종등락 실시간 (0U)</t>
+          <t>주식기세 실시간 (0A)</t>
         </is>
       </c>
       <c r="F214" s="15" t="inlineStr"/>
@@ -9534,17 +9535,17 @@
       </c>
       <c r="C215" s="14" t="inlineStr">
         <is>
-          <t>sector-index</t>
+          <t>program</t>
         </is>
       </c>
       <c r="D215" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream sector-index</t>
+          <t>kiwoom stream program</t>
         </is>
       </c>
       <c r="E215" s="14" t="inlineStr">
         <is>
-          <t>업종지수 실시간 (0J)</t>
+          <t>종목프로그램매매 실시간 (0w)</t>
         </is>
       </c>
       <c r="F215" s="15" t="inlineStr"/>
@@ -9572,17 +9573,17 @@
       </c>
       <c r="C216" s="14" t="inlineStr">
         <is>
-          <t>stock-info</t>
+          <t>quote</t>
         </is>
       </c>
       <c r="D216" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream stock-info</t>
+          <t>kiwoom stream quote</t>
         </is>
       </c>
       <c r="E216" s="14" t="inlineStr">
         <is>
-          <t>주식종목정보 실시간 (0g)</t>
+          <t>주식체결 실시간 (0B)</t>
         </is>
       </c>
       <c r="F216" s="15" t="inlineStr"/>
@@ -9610,17 +9611,17 @@
       </c>
       <c r="C217" s="14" t="inlineStr">
         <is>
-          <t>trader</t>
+          <t>sector-change</t>
         </is>
       </c>
       <c r="D217" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream trader</t>
+          <t>kiwoom stream sector-change</t>
         </is>
       </c>
       <c r="E217" s="14" t="inlineStr">
         <is>
-          <t>주식당일거래원 실시간 (0F)</t>
+          <t>업종등락 실시간 (0U)</t>
         </is>
       </c>
       <c r="F217" s="15" t="inlineStr"/>
@@ -9648,28 +9649,28 @@
       </c>
       <c r="C218" s="14" t="inlineStr">
         <is>
-          <t>types</t>
+          <t>sector-index</t>
         </is>
       </c>
       <c r="D218" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream types</t>
+          <t>kiwoom stream sector-index</t>
         </is>
       </c>
       <c r="E218" s="14" t="inlineStr">
         <is>
-          <t>사용 가능한 실시간 타입 코드 목록</t>
+          <t>업종지수 실시간 (0J)</t>
         </is>
       </c>
       <c r="F218" s="15" t="inlineStr"/>
       <c r="G218" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H218" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>--raw (JSON 원본 출력)</t>
         </is>
       </c>
     </row>
@@ -9686,17 +9687,17 @@
       </c>
       <c r="C219" s="14" t="inlineStr">
         <is>
-          <t>vi</t>
+          <t>stock-info</t>
         </is>
       </c>
       <c r="D219" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream vi</t>
+          <t>kiwoom stream stock-info</t>
         </is>
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>VI발동/해제 실시간 (1h)</t>
+          <t>주식종목정보 실시간 (0g)</t>
         </is>
       </c>
       <c r="F219" s="15" t="inlineStr"/>
@@ -9712,45 +9713,159 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="6" t="inlineStr">
+      <c r="A220" s="14" t="inlineStr">
+        <is>
+          <t>stream</t>
+        </is>
+      </c>
+      <c r="B220" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C220" s="14" t="inlineStr">
+        <is>
+          <t>trader</t>
+        </is>
+      </c>
+      <c r="D220" s="14" t="inlineStr">
+        <is>
+          <t>kiwoom stream trader</t>
+        </is>
+      </c>
+      <c r="E220" s="14" t="inlineStr">
+        <is>
+          <t>주식당일거래원 실시간 (0F)</t>
+        </is>
+      </c>
+      <c r="F220" s="15" t="inlineStr"/>
+      <c r="G220" s="14" t="inlineStr">
+        <is>
+          <t>CODES (복수) (필수)</t>
+        </is>
+      </c>
+      <c r="H220" s="14" t="inlineStr">
+        <is>
+          <t>--raw (JSON 원본 출력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="14" t="inlineStr">
+        <is>
+          <t>stream</t>
+        </is>
+      </c>
+      <c r="B221" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C221" s="14" t="inlineStr">
+        <is>
+          <t>types</t>
+        </is>
+      </c>
+      <c r="D221" s="14" t="inlineStr">
+        <is>
+          <t>kiwoom stream types</t>
+        </is>
+      </c>
+      <c r="E221" s="14" t="inlineStr">
+        <is>
+          <t>사용 가능한 실시간 타입 코드 목록</t>
+        </is>
+      </c>
+      <c r="F221" s="15" t="inlineStr"/>
+      <c r="G221" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="14" t="inlineStr">
+        <is>
+          <t>stream</t>
+        </is>
+      </c>
+      <c r="B222" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C222" s="14" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="D222" s="14" t="inlineStr">
+        <is>
+          <t>kiwoom stream vi</t>
+        </is>
+      </c>
+      <c r="E222" s="14" t="inlineStr">
+        <is>
+          <t>VI발동/해제 실시간 (1h)</t>
+        </is>
+      </c>
+      <c r="F222" s="15" t="inlineStr"/>
+      <c r="G222" s="14" t="inlineStr">
+        <is>
+          <t>CODES (복수) (필수)</t>
+        </is>
+      </c>
+      <c r="H222" s="14" t="inlineStr">
+        <is>
+          <t>--raw (JSON 원본 출력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="6" t="inlineStr">
         <is>
           <t>watch</t>
         </is>
       </c>
-      <c r="B220" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C220" s="6" t="inlineStr">
+      <c r="B223" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C223" s="6" t="inlineStr">
         <is>
           <t>watch</t>
         </is>
       </c>
-      <c r="D220" s="6" t="inlineStr">
+      <c r="D223" s="6" t="inlineStr">
         <is>
           <t>kiwoom watch</t>
         </is>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="E223" s="6" t="inlineStr">
         <is>
           <t>실시간 종목 모니터링 (TUI 대시보드)</t>
         </is>
       </c>
-      <c r="F220" s="7" t="inlineStr"/>
-      <c r="G220" s="6" t="inlineStr">
+      <c r="F223" s="7" t="inlineStr"/>
+      <c r="G223" s="6" t="inlineStr">
         <is>
           <t>CODES (복수) (필수)</t>
         </is>
       </c>
-      <c r="H220" s="6" t="inlineStr">
+      <c r="H223" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H220"/>
+  <autoFilter ref="A1:H223"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9800,7 +9915,7 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
@@ -9845,7 +9960,7 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
@@ -9950,7 +10065,7 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/kiwoom_cli_commands.xlsx
+++ b/kiwoom_cli_commands.xlsx
@@ -1940,23 +1940,23 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>domain</t>
+          <t>profiles</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>kiwoom config domain</t>
+          <t>kiwoom config profiles</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>도메인 변경 (prod/mock)</t>
+          <t>등록된 프로필 목록</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>DOMAIN (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1978,23 +1978,24 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>profiles</t>
+          <t>set</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>kiwoom config profiles</t>
+          <t>kiwoom config set</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>등록된 프로필 목록</t>
+          <t>프로필 설정 변경</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KEY (필수)
+VALUE (필수)</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -9934,7 +9935,7 @@
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>인증 (토큰)</t>
+          <t>인증</t>
         </is>
       </c>
     </row>
@@ -9949,7 +9950,7 @@
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>Raw API 호출</t>
+          <t>Raw API</t>
         </is>
       </c>
     </row>

--- a/kiwoom_cli_commands.xlsx
+++ b/kiwoom_cli_commands.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 명령어" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="전체 명령어" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체 명령어'!$A$1:$H$223</definedName>
@@ -2041,8 +2041,8 @@
           <t>--profile 기본:default (프로필 이름)
 --appkey (키움 API App Key)
 --secretkey (키움 API Secret Key)
---domain [prod, mock] 기본:mock (도메인 (prod: 실거래, mock: 모의투자))
---account (기본 계좌번호)</t>
+--domain [prod, mock] 기본:mock (도메인)
+--account (계좌번호)</t>
         </is>
       </c>
     </row>
@@ -5519,7 +5519,7 @@
 --type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
 --cond-price (조건부가격 (스톱지정가 등))
---confirm *필수 (주문 확인 (필수))</t>
+--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
         <is>
           <t>--qty (취소수량 (0=전량취소))
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
---confirm *필수 (주문 확인 (필수))</t>
+--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>--confirm *필수 (조회 확인 (필수))</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5649,7 @@
       <c r="H124" s="10" t="inlineStr">
         <is>
           <t>--exchange [K] 기본:K (거래소 (K=KRX))
---confirm *필수 (조회 확인 (필수))</t>
+--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5694,7 @@
           <t>--exchange [K] 기본:K (거래소 (K=KRX))
 --cont-yn (연속조회여부)
 --next-key (연속조회키)
---confirm *필수 (조회 확인 (필수))</t>
+--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>--confirm *필수 (조회 확인 (필수))</t>
+          <t>--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5783,7 @@
 --type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
 --cond-price (조건부가격)
---confirm *필수 (주문 확인 (필수))</t>
+--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
         <is>
           <t>--qty (취소수량 (0=전량취소))
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
---confirm *필수 (주문 확인 (필수))</t>
+--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5875,7 @@
         <is>
           <t>--exchange [KRX, NXT, SOR] 기본:KRX (거래소)
 --cond-price (정정 조건부가격)
---confirm *필수 (주문 확인 (필수))</t>
+--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
 --type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
 --cond-price (조건부가격)
---confirm *필수 (주문 확인 (필수))</t>
+--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>--confirm *필수 (조회 확인 (필수))</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
           <t>--price (주문가격 (시장가 주문시 생략))
 --type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
---confirm *필수 (주문 확인 (필수))</t>
+--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>
@@ -6055,7 +6055,7 @@
         <is>
           <t>--qty (취소수량 (0=전량취소))
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
---confirm *필수 (주문 확인 (필수))</t>
+--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>--confirm *필수 (조회 확인 (필수))</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>--confirm *필수 (조회 확인 (필수))</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>--confirm *필수 (조회 확인 (필수))</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>--confirm *필수 (조회 확인 (필수))</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       <c r="H138" s="10" t="inlineStr">
         <is>
           <t>--exchange [KRX, NXT, SOR] 기본:KRX (거래소)
---confirm *필수 (주문 확인 (필수))</t>
+--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>--confirm *필수 (조회 확인 (필수))</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
           <t>--price (주문가격 (시장가 주문시 생략))
 --type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
---confirm *필수 (주문 확인 (필수))</t>
+--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
         <is>
           <t>--exchange [KRX, NXT, SOR] 기본:KRX (거래소)
 --cond-price (정정 조건부가격)
---confirm *필수 (주문 확인 (필수))</t>
+--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
 --type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
 --cond-price (조건부가격 (스톱지정가 등))
---confirm *필수 (주문 확인 (필수))</t>
+--confirm (확인 프롬프트 없이 주문 실행)</t>
         </is>
       </c>
     </row>

--- a/kiwoom_cli_commands.xlsx
+++ b/kiwoom_cli_commands.xlsx
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>접근토큰 발급 (비밀번호 확인 후 암호화된 인증정보 사용)</t>
+          <t>접근토큰 발급</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr"/>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>접근토큰 폐기 (비밀번호 확인 필요)</t>
+          <t>접근토큰 폐기</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
@@ -2150,7 +2150,8 @@
 --appkey (키움 API App Key)
 --secretkey (키움 API Secret Key)
 --domain [prod, mock] 기본:mock (도메인)
---account (계좌번호)</t>
+--account (계좌번호)
+--token-storage [keychain, env] 기본:keychain (접근토큰 저장 방식)</t>
         </is>
       </c>
     </row>

--- a/kiwoom_cli_commands.xlsx
+++ b/kiwoom_cli_commands.xlsx
@@ -1917,7 +1917,8 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>--raw (JSON 원본 출력)</t>
+          <t>--raw (JSON 원본 출력)
+--next-key (연속조회 커서 (이전 응답의 meta.cont.next_key))</t>
         </is>
       </c>
     </row>

--- a/kiwoom_cli_commands.xlsx
+++ b/kiwoom_cli_commands.xlsx
@@ -11,7 +11,7 @@
     <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체 명령어'!$A$1:$H$226</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체 명령어'!$A$1:$H$227</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H226"/>
+  <dimension ref="A1:H227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5625,7 +5625,9 @@
 --type [after-hours, best, best-fok, best-ioc, conditional, first, fok, ioc, limit, loc, market, market-fok, market-ioc, mid, mid-fok, mid-ioc, moc, pre-market, single, stop, stop-limit, twap, twap-limit, vwap, vwap-limit] 기본:market (주문유형)
 --exchange [KRX, NXT, SOR, nasdaq, nyse, amex] (거래소 (기본: 국내 KRX / 미국 자동판별))
 --cond-price (조건부가격 (국내 전용))
---confirm (확인 프롬프트 없이 주문 실행)</t>
+--confirm (확인 프롬프트 없이 주문 실행)
+--dry-run (전송될 내용만 출력하고 주문을 전송하지 않음)
+--client-order-id (멱등성 키 (같은 키 재실행 시 재전송 없이 이전 응답 반환))</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5668,9 @@
         <is>
           <t>--qty (취소수량 (0=전량취소, 미국은 전량취소만 지원))
 --exchange [KRX, NXT, SOR, nasdaq, nyse, amex] (거래소 (기본: 국내 KRX / 미국 자동판별))
---confirm (확인 프롬프트 없이 주문 실행)</t>
+--confirm (확인 프롬프트 없이 주문 실행)
+--dry-run (전송될 내용만 출력하고 주문을 전송하지 않음)
+--client-order-id (멱등성 키 (같은 키 재실행 시 재전송 없이 이전 응답 반환))</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6503,9 @@
           <t>--exchange [KRX, NXT, SOR, nasdaq, nyse, amex] (거래소 (기본: 국내 KRX / 미국 자동판별))
 --cond-price (정정 조건부가격 (국내 전용))
 --stop (STOP가격 (미국 정정 전용))
---confirm (확인 프롬프트 없이 주문 실행)</t>
+--confirm (확인 프롬프트 없이 주문 실행)
+--dry-run (전송될 내용만 출력하고 주문을 전송하지 않음)
+--client-order-id (멱등성 키 (같은 키 재실행 시 재전송 없이 이전 응답 반환))</t>
         </is>
       </c>
     </row>
@@ -6543,49 +6549,51 @@
 --exchange [KRX, NXT, SOR, nasdaq, nyse, amex] (거래소 (기본: 국내 KRX / 미국 자동판별))
 --cond-price (조건부가격 (국내 전용))
 --stop (STOP가격 (미국 stop/stop-limit 전용))
---confirm (확인 프롬프트 없이 주문 실행)</t>
+--confirm (확인 프롬프트 없이 주문 실행)
+--dry-run (전송될 내용만 출력하고 주문을 전송하지 않음)
+--client-order-id (멱등성 키 (같은 키 재실행 시 재전송 없이 이전 응답 반환))</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B146" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C146" s="12" t="inlineStr">
-        <is>
-          <t>after-hours</t>
-        </is>
-      </c>
-      <c r="D146" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock after-hours</t>
-        </is>
-      </c>
-      <c r="E146" s="12" t="inlineStr">
-        <is>
-          <t>시간외단일가 조회</t>
-        </is>
-      </c>
-      <c r="F146" s="13" t="inlineStr">
-        <is>
-          <t>ka10087</t>
-        </is>
-      </c>
-      <c r="G146" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H146" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="B146" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>validate</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>kiwoom order validate</t>
+        </is>
+      </c>
+      <c r="E146" s="10" t="inlineStr">
+        <is>
+          <t>주문 사전점검 — 주문을 전송하지 않는 read-only 프리플라이트</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="inlineStr"/>
+      <c r="G146" s="10" t="inlineStr">
+        <is>
+          <t>SIDE (필수)
+CODE (필수)
+QTY (필수)</t>
+        </is>
+      </c>
+      <c r="H146" s="10" t="inlineStr">
+        <is>
+          <t>--price (주문가격 (생략 시 현재가로 예상비용 계산))
+--type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
+--exchange [KRX, NXT] 기본:KRX (거래소)</t>
         </is>
       </c>
     </row>
@@ -6597,35 +6605,77 @@
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>after-hours</t>
+        </is>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock after-hours</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>시간외단일가 조회</t>
+        </is>
+      </c>
+      <c r="F147" s="13" t="inlineStr">
+        <is>
+          <t>ka10087</t>
+        </is>
+      </c>
+      <c r="G147" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H147" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B148" s="12" t="inlineStr">
+        <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C147" s="12" t="inlineStr">
+      <c r="C148" s="12" t="inlineStr">
         <is>
           <t>broker-stock</t>
         </is>
       </c>
-      <c r="D147" s="12" t="inlineStr">
+      <c r="D148" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis broker-stock</t>
         </is>
       </c>
-      <c r="E147" s="12" t="inlineStr">
+      <c r="E148" s="12" t="inlineStr">
         <is>
           <t>증권사별종목매매동향 조회</t>
         </is>
       </c>
-      <c r="F147" s="13" t="inlineStr">
+      <c r="F148" s="13" t="inlineStr">
         <is>
           <t>ka10078</t>
         </is>
       </c>
-      <c r="G147" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H147" s="12" t="inlineStr">
+      <c r="G148" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" s="12" t="inlineStr">
         <is>
           <t>--broker *필수 (회원사코드)
 --code *필수 (종목코드)
@@ -6634,48 +6684,6 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B148" s="12" t="inlineStr">
-        <is>
-          <t>analysis</t>
-        </is>
-      </c>
-      <c r="C148" s="12" t="inlineStr">
-        <is>
-          <t>daily-detail</t>
-        </is>
-      </c>
-      <c r="D148" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock analysis daily-detail</t>
-        </is>
-      </c>
-      <c r="E148" s="12" t="inlineStr">
-        <is>
-          <t>일별거래상세 조회</t>
-        </is>
-      </c>
-      <c r="F148" s="13" t="inlineStr">
-        <is>
-          <t>ka10015</t>
-        </is>
-      </c>
-      <c r="G148" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H148" s="12" t="inlineStr">
-        <is>
-          <t>--from *필수 (시작일자 (YYYYMMDD))</t>
-        </is>
-      </c>
-    </row>
     <row r="149">
       <c r="A149" s="12" t="inlineStr">
         <is>
@@ -6689,30 +6697,72 @@
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
+          <t>daily-detail</t>
+        </is>
+      </c>
+      <c r="D149" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock analysis daily-detail</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="inlineStr">
+        <is>
+          <t>일별거래상세 조회</t>
+        </is>
+      </c>
+      <c r="F149" s="13" t="inlineStr">
+        <is>
+          <t>ka10015</t>
+        </is>
+      </c>
+      <c r="G149" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H149" s="12" t="inlineStr">
+        <is>
+          <t>--from *필수 (시작일자 (YYYYMMDD))</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B150" s="12" t="inlineStr">
+        <is>
+          <t>analysis</t>
+        </is>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
           <t>instant-volume</t>
         </is>
       </c>
-      <c r="D149" s="12" t="inlineStr">
+      <c r="D150" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis instant-volume</t>
         </is>
       </c>
-      <c r="E149" s="12" t="inlineStr">
+      <c r="E150" s="12" t="inlineStr">
         <is>
           <t>거래원순간거래량 조회</t>
         </is>
       </c>
-      <c r="F149" s="13" t="inlineStr">
+      <c r="F150" s="13" t="inlineStr">
         <is>
           <t>ka10052</t>
         </is>
       </c>
-      <c r="G149" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H149" s="12" t="inlineStr">
+      <c r="G150" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" s="12" t="inlineStr">
         <is>
           <t>--broker *필수 (회원사코드)
 --code (종목코드 (선택))
@@ -6723,43 +6773,43 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="12" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B150" s="12" t="inlineStr">
+      <c r="B151" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C150" s="12" t="inlineStr">
+      <c r="C151" s="12" t="inlineStr">
         <is>
           <t>open-change</t>
         </is>
       </c>
-      <c r="D150" s="12" t="inlineStr">
+      <c r="D151" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis open-change</t>
         </is>
       </c>
-      <c r="E150" s="12" t="inlineStr">
+      <c r="E151" s="12" t="inlineStr">
         <is>
           <t>시가대비등락률 조회</t>
         </is>
       </c>
-      <c r="F150" s="13" t="inlineStr">
+      <c r="F151" s="13" t="inlineStr">
         <is>
           <t>ka10028</t>
         </is>
       </c>
-      <c r="G150" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H150" s="12" t="inlineStr">
+      <c r="G151" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" s="12" t="inlineStr">
         <is>
           <t>--sort [1, 2, 3, 4] 기본:1 (정렬구분 (1=시가, 2=고가, 3=저가, 4=기준가))
 --volume-cond (거래량조건)
@@ -6773,86 +6823,86 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="12" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B151" s="12" t="inlineStr">
+      <c r="B152" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C151" s="12" t="inlineStr">
+      <c r="C152" s="12" t="inlineStr">
         <is>
           <t>per-rank</t>
         </is>
       </c>
-      <c r="D151" s="12" t="inlineStr">
+      <c r="D152" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis per-rank</t>
         </is>
       </c>
-      <c r="E151" s="12" t="inlineStr">
+      <c r="E152" s="12" t="inlineStr">
         <is>
           <t>고저PER 조회</t>
         </is>
       </c>
-      <c r="F151" s="13" t="inlineStr">
+      <c r="F152" s="13" t="inlineStr">
         <is>
           <t>ka10026</t>
         </is>
       </c>
-      <c r="G151" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" s="12" t="inlineStr">
+      <c r="G152" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" s="12" t="inlineStr">
         <is>
           <t>--type [low-pbr, high-pbr, low-per, high-per, low-roe, high-roe] 기본:low-per (PER구분 (low-pbr/high-pbr/low-per/high-per/low-roe/high-roe))
 --exchange [KRX, NXT, all] 기본:all (거래소구분 (KRX/NXT/all))</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="12" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B152" s="12" t="inlineStr">
+      <c r="B153" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C152" s="12" t="inlineStr">
+      <c r="C153" s="12" t="inlineStr">
         <is>
           <t>price-cluster</t>
         </is>
       </c>
-      <c r="D152" s="12" t="inlineStr">
+      <c r="D153" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis price-cluster</t>
         </is>
       </c>
-      <c r="E152" s="12" t="inlineStr">
+      <c r="E153" s="12" t="inlineStr">
         <is>
           <t>매물대집중 조회</t>
         </is>
       </c>
-      <c r="F152" s="13" t="inlineStr">
+      <c r="F153" s="13" t="inlineStr">
         <is>
           <t>ka10025</t>
         </is>
       </c>
-      <c r="G152" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H152" s="12" t="inlineStr">
+      <c r="G153" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" s="12" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분 (all/kospi/kosdaq))
 --ratio 기본:50 (매물집중비율 (0~100))
@@ -6863,43 +6913,43 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="12" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B153" s="12" t="inlineStr">
+      <c r="B154" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C153" s="12" t="inlineStr">
+      <c r="C154" s="12" t="inlineStr">
         <is>
           <t>trader-analysis</t>
         </is>
       </c>
-      <c r="D153" s="12" t="inlineStr">
+      <c r="D154" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis trader-analysis</t>
         </is>
       </c>
-      <c r="E153" s="12" t="inlineStr">
+      <c r="E154" s="12" t="inlineStr">
         <is>
           <t>거래원매물대분석 조회</t>
         </is>
       </c>
-      <c r="F153" s="13" t="inlineStr">
+      <c r="F154" s="13" t="inlineStr">
         <is>
           <t>ka10043</t>
         </is>
       </c>
-      <c r="G153" s="12" t="inlineStr">
+      <c r="G154" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H153" s="12" t="inlineStr">
+      <c r="H154" s="12" t="inlineStr">
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
@@ -6912,43 +6962,43 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="12" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B154" s="12" t="inlineStr">
+      <c r="B155" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C154" s="12" t="inlineStr">
+      <c r="C155" s="12" t="inlineStr">
         <is>
           <t>vi-trigger</t>
         </is>
       </c>
-      <c r="D154" s="12" t="inlineStr">
+      <c r="D155" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis vi-trigger</t>
         </is>
       </c>
-      <c r="E154" s="12" t="inlineStr">
+      <c r="E155" s="12" t="inlineStr">
         <is>
           <t>변동성완화장치(VI) 발동종목 조회</t>
         </is>
       </c>
-      <c r="F154" s="13" t="inlineStr">
+      <c r="F155" s="13" t="inlineStr">
         <is>
           <t>ka10054</t>
         </is>
       </c>
-      <c r="G154" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H154" s="12" t="inlineStr">
+      <c r="G155" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" s="12" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분 (all/kospi/kosdaq))
 --session [0, 1, 2] (장전구분 (0=전체, 1=정규시장, 2=시간외단일가))
@@ -6966,43 +7016,43 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="12" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B155" s="12" t="inlineStr">
+      <c r="B156" s="12" t="inlineStr">
         <is>
           <t>analysis</t>
         </is>
       </c>
-      <c r="C155" s="12" t="inlineStr">
+      <c r="C156" s="12" t="inlineStr">
         <is>
           <t>volume-renewal</t>
         </is>
       </c>
-      <c r="D155" s="12" t="inlineStr">
+      <c r="D156" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock analysis volume-renewal</t>
         </is>
       </c>
-      <c r="E155" s="12" t="inlineStr">
+      <c r="E156" s="12" t="inlineStr">
         <is>
           <t>거래량갱신 조회</t>
         </is>
       </c>
-      <c r="F155" s="13" t="inlineStr">
+      <c r="F156" s="13" t="inlineStr">
         <is>
           <t>ka10024</t>
         </is>
       </c>
-      <c r="G155" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H155" s="12" t="inlineStr">
+      <c r="G156" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H156" s="12" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분 (all/kospi/kosdaq))
 --cycle [5, 10, 20, 60, 250] 기본:20 (주기구분 (5/10/20/60/250일))
@@ -7011,48 +7061,6 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B156" s="12" t="inlineStr">
-        <is>
-          <t>analysis</t>
-        </is>
-      </c>
-      <c r="C156" s="12" t="inlineStr">
-        <is>
-          <t>warrant</t>
-        </is>
-      </c>
-      <c r="D156" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock analysis warrant</t>
-        </is>
-      </c>
-      <c r="E156" s="12" t="inlineStr">
-        <is>
-          <t>신주인수권전체시세 조회</t>
-        </is>
-      </c>
-      <c r="F156" s="13" t="inlineStr">
-        <is>
-          <t>ka10011</t>
-        </is>
-      </c>
-      <c r="G156" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H156" s="12" t="inlineStr">
-        <is>
-          <t>--type [00, 05, 07] 기본:00 (신주인수권구분 (00=전체, 05=신주인수권증권, 07=신주인수권증서))</t>
-        </is>
-      </c>
-    </row>
     <row r="157">
       <c r="A157" s="12" t="inlineStr">
         <is>
@@ -7061,27 +7069,27 @@
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>analysis</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>brokers</t>
+          <t>warrant</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock brokers</t>
+          <t>kiwoom stock analysis warrant</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>회원사(증권사) 리스트 조회</t>
+          <t>신주인수권전체시세 조회</t>
         </is>
       </c>
       <c r="F157" s="13" t="inlineStr">
         <is>
-          <t>ka10102</t>
+          <t>ka10011</t>
         </is>
       </c>
       <c r="G157" s="12" t="inlineStr">
@@ -7091,7 +7099,7 @@
       </c>
       <c r="H157" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>--type [00, 05, 07] 기본:00 (신주인수권구분 (00=전체, 05=신주인수권증권, 07=신주인수권증서))</t>
         </is>
       </c>
     </row>
@@ -7103,31 +7111,73 @@
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C158" s="12" t="inlineStr">
+        <is>
+          <t>brokers</t>
+        </is>
+      </c>
+      <c r="D158" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock brokers</t>
+        </is>
+      </c>
+      <c r="E158" s="12" t="inlineStr">
+        <is>
+          <t>회원사(증권사) 리스트 조회</t>
+        </is>
+      </c>
+      <c r="F158" s="13" t="inlineStr">
+        <is>
+          <t>ka10102</t>
+        </is>
+      </c>
+      <c r="G158" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H158" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="inlineStr">
+        <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C158" s="12" t="inlineStr">
+      <c r="C159" s="12" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="D158" s="12" t="inlineStr">
+      <c r="D159" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart day</t>
         </is>
       </c>
-      <c r="E158" s="12" t="inlineStr">
+      <c r="E159" s="12" t="inlineStr">
         <is>
           <t>일봉 차트 조회 (국내 ka10081 / 미국 usa06012)</t>
         </is>
       </c>
-      <c r="F158" s="13" t="inlineStr"/>
-      <c r="G158" s="12" t="inlineStr">
+      <c r="F159" s="13" t="inlineStr"/>
+      <c r="G159" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H158" s="12" t="inlineStr">
+      <c r="H159" s="12" t="inlineStr">
         <is>
           <t>--base-date *필수 (기준일자 (YYYYMMDD))
 --adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))
@@ -7136,43 +7186,43 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="12" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B159" s="12" t="inlineStr">
+      <c r="B160" s="12" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C159" s="12" t="inlineStr">
+      <c r="C160" s="12" t="inlineStr">
         <is>
           <t>intraday-investor</t>
         </is>
       </c>
-      <c r="D159" s="12" t="inlineStr">
+      <c r="D160" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart intraday-investor</t>
         </is>
       </c>
-      <c r="E159" s="12" t="inlineStr">
+      <c r="E160" s="12" t="inlineStr">
         <is>
           <t>장중투자자별매매 차트 조회</t>
         </is>
       </c>
-      <c r="F159" s="13" t="inlineStr">
+      <c r="F160" s="13" t="inlineStr">
         <is>
           <t>ka10064</t>
         </is>
       </c>
-      <c r="G159" s="12" t="inlineStr">
+      <c r="G160" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H159" s="12" t="inlineStr">
+      <c r="H160" s="12" t="inlineStr">
         <is>
           <t>--market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
 --amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
@@ -7180,43 +7230,43 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="12" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B160" s="12" t="inlineStr">
+      <c r="B161" s="12" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C160" s="12" t="inlineStr">
+      <c r="C161" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="D160" s="12" t="inlineStr">
+      <c r="D161" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart investor</t>
         </is>
       </c>
-      <c r="E160" s="12" t="inlineStr">
+      <c r="E161" s="12" t="inlineStr">
         <is>
           <t>종목별투자자기관별 차트 조회</t>
         </is>
       </c>
-      <c r="F160" s="13" t="inlineStr">
+      <c r="F161" s="13" t="inlineStr">
         <is>
           <t>ka10060</t>
         </is>
       </c>
-      <c r="G160" s="12" t="inlineStr">
+      <c r="G161" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H160" s="12" t="inlineStr">
+      <c r="H161" s="12" t="inlineStr">
         <is>
           <t>--date *필수 (일자 (YYYYMMDD))
 --amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
@@ -7225,39 +7275,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="12" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B161" s="12" t="inlineStr">
+      <c r="B162" s="12" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C161" s="12" t="inlineStr">
+      <c r="C162" s="12" t="inlineStr">
         <is>
           <t>minute</t>
         </is>
       </c>
-      <c r="D161" s="12" t="inlineStr">
+      <c r="D162" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart minute</t>
         </is>
       </c>
-      <c r="E161" s="12" t="inlineStr">
+      <c r="E162" s="12" t="inlineStr">
         <is>
           <t>분봉 차트 조회 (국내 ka10080 / 미국 usa06011)</t>
         </is>
       </c>
-      <c r="F161" s="13" t="inlineStr"/>
-      <c r="G161" s="12" t="inlineStr">
+      <c r="F162" s="13" t="inlineStr"/>
+      <c r="G162" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H161" s="12" t="inlineStr">
+      <c r="H162" s="12" t="inlineStr">
         <is>
           <t>--interval [1, 3, 5, 10, 15, 30, 45, 60] 기본:5 (분봉 간격 (1/3/5/10/15/30/45/60))
 --adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))
@@ -7267,39 +7317,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="12" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B162" s="12" t="inlineStr">
+      <c r="B163" s="12" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C162" s="12" t="inlineStr">
+      <c r="C163" s="12" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="D162" s="12" t="inlineStr">
+      <c r="D163" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart month</t>
         </is>
       </c>
-      <c r="E162" s="12" t="inlineStr">
+      <c r="E163" s="12" t="inlineStr">
         <is>
           <t>월봉 차트 조회 (국내 ka10083 / 미국 usa06014)</t>
         </is>
       </c>
-      <c r="F162" s="13" t="inlineStr"/>
-      <c r="G162" s="12" t="inlineStr">
+      <c r="F163" s="13" t="inlineStr"/>
+      <c r="G163" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H162" s="12" t="inlineStr">
+      <c r="H163" s="12" t="inlineStr">
         <is>
           <t>--base-date *필수 (기준일자 (YYYYMMDD))
 --adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))
@@ -7308,39 +7358,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="12" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B163" s="12" t="inlineStr">
+      <c r="B164" s="12" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C163" s="12" t="inlineStr">
+      <c r="C164" s="12" t="inlineStr">
         <is>
           <t>tick</t>
         </is>
       </c>
-      <c r="D163" s="12" t="inlineStr">
+      <c r="D164" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart tick</t>
         </is>
       </c>
-      <c r="E163" s="12" t="inlineStr">
+      <c r="E164" s="12" t="inlineStr">
         <is>
           <t>틱 차트 조회 (국내 ka10079 / 미국 usa06010)</t>
         </is>
       </c>
-      <c r="F163" s="13" t="inlineStr"/>
-      <c r="G163" s="12" t="inlineStr">
+      <c r="F164" s="13" t="inlineStr"/>
+      <c r="G164" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H163" s="12" t="inlineStr">
+      <c r="H164" s="12" t="inlineStr">
         <is>
           <t>--range [1, 3, 5, 10, 30] 기본:1 (틱범위 (1/3/5/10/30))
 --adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))
@@ -7349,39 +7399,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="12" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B164" s="12" t="inlineStr">
+      <c r="B165" s="12" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C164" s="12" t="inlineStr">
+      <c r="C165" s="12" t="inlineStr">
         <is>
           <t>week</t>
         </is>
       </c>
-      <c r="D164" s="12" t="inlineStr">
+      <c r="D165" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart week</t>
         </is>
       </c>
-      <c r="E164" s="12" t="inlineStr">
+      <c r="E165" s="12" t="inlineStr">
         <is>
           <t>주봉 차트 조회 (국내 ka10082 / 미국 usa06013)</t>
         </is>
       </c>
-      <c r="F164" s="13" t="inlineStr"/>
-      <c r="G164" s="12" t="inlineStr">
+      <c r="F165" s="13" t="inlineStr"/>
+      <c r="G165" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H164" s="12" t="inlineStr">
+      <c r="H165" s="12" t="inlineStr">
         <is>
           <t>--base-date *필수 (기준일자 (YYYYMMDD))
 --adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))
@@ -7390,39 +7440,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="12" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B165" s="12" t="inlineStr">
+      <c r="B166" s="12" t="inlineStr">
         <is>
           <t>chart</t>
         </is>
       </c>
-      <c r="C165" s="12" t="inlineStr">
+      <c r="C166" s="12" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="D165" s="12" t="inlineStr">
+      <c r="D166" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock chart year</t>
         </is>
       </c>
-      <c r="E165" s="12" t="inlineStr">
+      <c r="E166" s="12" t="inlineStr">
         <is>
           <t>년봉 차트 조회 (국내 ka10094 / 미국 usa06015)</t>
         </is>
       </c>
-      <c r="F165" s="13" t="inlineStr"/>
-      <c r="G165" s="12" t="inlineStr">
+      <c r="F166" s="13" t="inlineStr"/>
+      <c r="G166" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H165" s="12" t="inlineStr">
+      <c r="H166" s="12" t="inlineStr">
         <is>
           <t>--base-date *필수 (기준일자 (YYYYMMDD))
 --adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))
@@ -7431,48 +7481,6 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B166" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C166" s="12" t="inlineStr">
-        <is>
-          <t>compare</t>
-        </is>
-      </c>
-      <c r="D166" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock compare</t>
-        </is>
-      </c>
-      <c r="E166" s="12" t="inlineStr">
-        <is>
-          <t>종목 비교 (2개 이상)</t>
-        </is>
-      </c>
-      <c r="F166" s="13" t="inlineStr">
-        <is>
-          <t>ka10001</t>
-        </is>
-      </c>
-      <c r="G166" s="12" t="inlineStr">
-        <is>
-          <t>CODES (복수) (필수)</t>
-        </is>
-      </c>
-      <c r="H166" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="167">
       <c r="A167" s="12" t="inlineStr">
         <is>
@@ -7481,32 +7489,32 @@
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>credit</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>compare</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock credit available</t>
+          <t>kiwoom stock compare</t>
         </is>
       </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>신용융자 가능종목 조회</t>
+          <t>종목 비교 (2개 이상)</t>
         </is>
       </c>
       <c r="F167" s="13" t="inlineStr">
         <is>
-          <t>kt20016</t>
+          <t>ka10001</t>
         </is>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H167" s="12" t="inlineStr">
@@ -7528,22 +7536,22 @@
       </c>
       <c r="C168" s="12" t="inlineStr">
         <is>
-          <t>inquiry</t>
+          <t>available</t>
         </is>
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock credit inquiry</t>
+          <t>kiwoom stock credit available</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr">
         <is>
-          <t>신용융자 가능문의</t>
+          <t>신용융자 가능종목 조회</t>
         </is>
       </c>
       <c r="F168" s="13" t="inlineStr">
         <is>
-          <t>kt20017</t>
+          <t>kt20016</t>
         </is>
       </c>
       <c r="G168" s="12" t="inlineStr">
@@ -7570,78 +7578,78 @@
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
+          <t>inquiry</t>
+        </is>
+      </c>
+      <c r="D169" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock credit inquiry</t>
+        </is>
+      </c>
+      <c r="E169" s="12" t="inlineStr">
+        <is>
+          <t>신용융자 가능문의</t>
+        </is>
+      </c>
+      <c r="F169" s="13" t="inlineStr">
+        <is>
+          <t>kt20017</t>
+        </is>
+      </c>
+      <c r="G169" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B170" s="12" t="inlineStr">
+        <is>
+          <t>credit</t>
+        </is>
+      </c>
+      <c r="C170" s="12" t="inlineStr">
+        <is>
           <t>trend</t>
         </is>
       </c>
-      <c r="D169" s="12" t="inlineStr">
+      <c r="D170" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock credit trend</t>
         </is>
       </c>
-      <c r="E169" s="12" t="inlineStr">
+      <c r="E170" s="12" t="inlineStr">
         <is>
           <t>신용매매동향 조회</t>
         </is>
       </c>
-      <c r="F169" s="13" t="inlineStr">
+      <c r="F170" s="13" t="inlineStr">
         <is>
           <t>ka10013</t>
         </is>
       </c>
-      <c r="G169" s="12" t="inlineStr">
+      <c r="G170" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H169" s="12" t="inlineStr">
+      <c r="H170" s="12" t="inlineStr">
         <is>
           <t>--date *필수 (일자 (YYYYMMDD))
 --type [loan, short-sell] 기본:loan (구분 (loan=융자, short-sell=대주))</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B170" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C170" s="12" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="D170" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock daily</t>
-        </is>
-      </c>
-      <c r="E170" s="12" t="inlineStr">
-        <is>
-          <t>일/주/월별 시세 조회</t>
-        </is>
-      </c>
-      <c r="F170" s="13" t="inlineStr">
-        <is>
-          <t>ka10005</t>
-        </is>
-      </c>
-      <c r="G170" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H170" s="12" t="inlineStr">
-        <is>
-          <t>--type [day, week, month] 기본:day (조회 구분 (day/week/month))</t>
-        </is>
-      </c>
-    </row>
     <row r="171">
       <c r="A171" s="12" t="inlineStr">
         <is>
@@ -7655,78 +7663,78 @@
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="D171" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock daily</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="inlineStr">
+        <is>
+          <t>일/주/월별 시세 조회</t>
+        </is>
+      </c>
+      <c r="F171" s="13" t="inlineStr">
+        <is>
+          <t>ka10005</t>
+        </is>
+      </c>
+      <c r="G171" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H171" s="12" t="inlineStr">
+        <is>
+          <t>--type [day, week, month] 기본:day (조회 구분 (day/week/month))</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B172" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C172" s="12" t="inlineStr">
+        <is>
           <t>daily-price</t>
         </is>
       </c>
-      <c r="D171" s="12" t="inlineStr">
+      <c r="D172" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock daily-price</t>
         </is>
       </c>
-      <c r="E171" s="12" t="inlineStr">
+      <c r="E172" s="12" t="inlineStr">
         <is>
           <t>일별주가 조회</t>
         </is>
       </c>
-      <c r="F171" s="13" t="inlineStr">
+      <c r="F172" s="13" t="inlineStr">
         <is>
           <t>ka10086</t>
         </is>
       </c>
-      <c r="G171" s="12" t="inlineStr">
+      <c r="G172" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H171" s="12" t="inlineStr">
+      <c r="H172" s="12" t="inlineStr">
         <is>
           <t>--date *필수 (조회일자 (YYYYMMDD))
 --display [0, 1] (표시구분 (0=수량, 1=금액백만원))</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B172" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C172" s="12" t="inlineStr">
-        <is>
-          <t>daily-strength</t>
-        </is>
-      </c>
-      <c r="D172" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock daily-strength</t>
-        </is>
-      </c>
-      <c r="E172" s="12" t="inlineStr">
-        <is>
-          <t>체결강도추이 일별</t>
-        </is>
-      </c>
-      <c r="F172" s="13" t="inlineStr">
-        <is>
-          <t>ka10047</t>
-        </is>
-      </c>
-      <c r="G172" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H172" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="173">
       <c r="A173" s="12" t="inlineStr">
         <is>
@@ -7740,22 +7748,22 @@
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>detail</t>
+          <t>daily-strength</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock detail</t>
+          <t>kiwoom stock daily-strength</t>
         </is>
       </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>종목정보 상세 조회</t>
+          <t>체결강도추이 일별</t>
         </is>
       </c>
       <c r="F173" s="13" t="inlineStr">
         <is>
-          <t>ka10100</t>
+          <t>ka10047</t>
         </is>
       </c>
       <c r="G173" s="12" t="inlineStr">
@@ -7782,22 +7790,22 @@
       </c>
       <c r="C174" s="12" t="inlineStr">
         <is>
-          <t>exec</t>
+          <t>detail</t>
         </is>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock exec</t>
+          <t>kiwoom stock detail</t>
         </is>
       </c>
       <c r="E174" s="12" t="inlineStr">
         <is>
-          <t>체결정보 조회</t>
+          <t>종목정보 상세 조회</t>
         </is>
       </c>
       <c r="F174" s="13" t="inlineStr">
         <is>
-          <t>ka10003</t>
+          <t>ka10100</t>
         </is>
       </c>
       <c r="G174" s="12" t="inlineStr">
@@ -7824,22 +7832,22 @@
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>foreign</t>
+          <t>exec</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock foreign</t>
+          <t>kiwoom stock exec</t>
         </is>
       </c>
       <c r="E175" s="12" t="inlineStr">
         <is>
-          <t>외국인 종목별 매매동향 조회</t>
+          <t>체결정보 조회</t>
         </is>
       </c>
       <c r="F175" s="13" t="inlineStr">
         <is>
-          <t>ka10008</t>
+          <t>ka10003</t>
         </is>
       </c>
       <c r="G175" s="12" t="inlineStr">
@@ -7866,20 +7874,24 @@
       </c>
       <c r="C176" s="12" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>foreign</t>
         </is>
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock info</t>
+          <t>kiwoom stock foreign</t>
         </is>
       </c>
       <c r="E176" s="12" t="inlineStr">
         <is>
-          <t>종목 기본정보 조회</t>
-        </is>
-      </c>
-      <c r="F176" s="13" t="inlineStr"/>
+          <t>외국인 종목별 매매동향 조회</t>
+        </is>
+      </c>
+      <c r="F176" s="13" t="inlineStr">
+        <is>
+          <t>ka10008</t>
+        </is>
+      </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -7887,7 +7899,7 @@
       </c>
       <c r="H176" s="12" t="inlineStr">
         <is>
-          <t>--exchange [nasdaq, nyse, amex] (미국 거래소 (미국 종목 강제 라우팅))</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7904,24 +7916,20 @@
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>institution</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock institution</t>
+          <t>kiwoom stock info</t>
         </is>
       </c>
       <c r="E177" s="12" t="inlineStr">
         <is>
-          <t>주식기관 조회</t>
-        </is>
-      </c>
-      <c r="F177" s="13" t="inlineStr">
-        <is>
-          <t>ka10009</t>
-        </is>
-      </c>
+          <t>종목 기본정보 조회</t>
+        </is>
+      </c>
+      <c r="F177" s="13" t="inlineStr"/>
       <c r="G177" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -7929,7 +7937,7 @@
       </c>
       <c r="H177" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>--exchange [nasdaq, nyse, amex] (미국 거래소 (미국 종목 강제 라우팅))</t>
         </is>
       </c>
     </row>
@@ -7941,35 +7949,77 @@
       </c>
       <c r="B178" s="12" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C178" s="12" t="inlineStr">
+        <is>
+          <t>institution</t>
+        </is>
+      </c>
+      <c r="D178" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock institution</t>
+        </is>
+      </c>
+      <c r="E178" s="12" t="inlineStr">
+        <is>
+          <t>주식기관 조회</t>
+        </is>
+      </c>
+      <c r="F178" s="13" t="inlineStr">
+        <is>
+          <t>ka10009</t>
+        </is>
+      </c>
+      <c r="G178" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H178" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B179" s="12" t="inlineStr">
+        <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C178" s="12" t="inlineStr">
+      <c r="C179" s="12" t="inlineStr">
         <is>
           <t>after-close</t>
         </is>
       </c>
-      <c r="D178" s="12" t="inlineStr">
+      <c r="D179" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor after-close</t>
         </is>
       </c>
-      <c r="E178" s="12" t="inlineStr">
+      <c r="E179" s="12" t="inlineStr">
         <is>
           <t>장마감후투자자별매매 조회</t>
         </is>
       </c>
-      <c r="F178" s="13" t="inlineStr">
+      <c r="F179" s="13" t="inlineStr">
         <is>
           <t>ka10066</t>
         </is>
       </c>
-      <c r="G178" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H178" s="12" t="inlineStr">
+      <c r="G179" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="12" t="inlineStr">
         <is>
           <t>--market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
 --amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
@@ -7978,43 +8028,43 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="12" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B179" s="12" t="inlineStr">
+      <c r="B180" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C179" s="12" t="inlineStr">
+      <c r="C180" s="12" t="inlineStr">
         <is>
           <t>by-stock</t>
         </is>
       </c>
-      <c r="D179" s="12" t="inlineStr">
+      <c r="D180" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor by-stock</t>
         </is>
       </c>
-      <c r="E179" s="12" t="inlineStr">
+      <c r="E180" s="12" t="inlineStr">
         <is>
           <t>종목별투자자기관별 조회</t>
         </is>
       </c>
-      <c r="F179" s="13" t="inlineStr">
+      <c r="F180" s="13" t="inlineStr">
         <is>
           <t>ka10059</t>
         </is>
       </c>
-      <c r="G179" s="12" t="inlineStr">
+      <c r="G180" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H179" s="12" t="inlineStr">
+      <c r="H180" s="12" t="inlineStr">
         <is>
           <t>--date *필수 (일자 (YYYYMMDD))
 --amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
@@ -8023,43 +8073,43 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="12" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B180" s="12" t="inlineStr">
+      <c r="B181" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C180" s="12" t="inlineStr">
+      <c r="C181" s="12" t="inlineStr">
         <is>
           <t>by-stock-total</t>
         </is>
       </c>
-      <c r="D180" s="12" t="inlineStr">
+      <c r="D181" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor by-stock-total</t>
         </is>
       </c>
-      <c r="E180" s="12" t="inlineStr">
+      <c r="E181" s="12" t="inlineStr">
         <is>
           <t>종목별투자자기관별합계 조회</t>
         </is>
       </c>
-      <c r="F180" s="13" t="inlineStr">
+      <c r="F181" s="13" t="inlineStr">
         <is>
           <t>ka10061</t>
         </is>
       </c>
-      <c r="G180" s="12" t="inlineStr">
+      <c r="G181" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H180" s="12" t="inlineStr">
+      <c r="H181" s="12" t="inlineStr">
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
@@ -8069,43 +8119,43 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="12" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B181" s="12" t="inlineStr">
+      <c r="B182" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C181" s="12" t="inlineStr">
+      <c r="C182" s="12" t="inlineStr">
         <is>
           <t>consecutive</t>
         </is>
       </c>
-      <c r="D181" s="12" t="inlineStr">
+      <c r="D182" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor consecutive</t>
         </is>
       </c>
-      <c r="E181" s="12" t="inlineStr">
+      <c r="E182" s="12" t="inlineStr">
         <is>
           <t>기관/외국인 연속매매현황 조회</t>
         </is>
       </c>
-      <c r="F181" s="13" t="inlineStr">
+      <c r="F182" s="13" t="inlineStr">
         <is>
           <t>ka10131</t>
         </is>
       </c>
-      <c r="G181" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H181" s="12" t="inlineStr">
+      <c r="G182" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" s="12" t="inlineStr">
         <is>
           <t>--period 기본:5 (기간 (일수))
 --from (시작일자 (YYYYMMDD, 선택))
@@ -8118,43 +8168,43 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="12" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B182" s="12" t="inlineStr">
+      <c r="B183" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C182" s="12" t="inlineStr">
+      <c r="C183" s="12" t="inlineStr">
         <is>
           <t>daily-by-investor</t>
         </is>
       </c>
-      <c r="D182" s="12" t="inlineStr">
+      <c r="D183" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor daily-by-investor</t>
         </is>
       </c>
-      <c r="E182" s="12" t="inlineStr">
+      <c r="E183" s="12" t="inlineStr">
         <is>
           <t>투자자별일별매매종목 조회</t>
         </is>
       </c>
-      <c r="F182" s="13" t="inlineStr">
+      <c r="F183" s="13" t="inlineStr">
         <is>
           <t>ka10058</t>
         </is>
       </c>
-      <c r="G182" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H182" s="12" t="inlineStr">
+      <c r="G183" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="12" t="inlineStr">
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
@@ -8165,43 +8215,43 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="12" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B183" s="12" t="inlineStr">
+      <c r="B184" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C183" s="12" t="inlineStr">
+      <c r="C184" s="12" t="inlineStr">
         <is>
           <t>daily-trade</t>
         </is>
       </c>
-      <c r="D183" s="12" t="inlineStr">
+      <c r="D184" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor daily-trade</t>
         </is>
       </c>
-      <c r="E183" s="12" t="inlineStr">
+      <c r="E184" s="12" t="inlineStr">
         <is>
           <t>일별기관매매종목 조회</t>
         </is>
       </c>
-      <c r="F183" s="13" t="inlineStr">
+      <c r="F184" s="13" t="inlineStr">
         <is>
           <t>ka10044</t>
         </is>
       </c>
-      <c r="G183" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H183" s="12" t="inlineStr">
+      <c r="G184" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" s="12" t="inlineStr">
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
@@ -8211,43 +8261,43 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="12" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B184" s="12" t="inlineStr">
+      <c r="B185" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C184" s="12" t="inlineStr">
+      <c r="C185" s="12" t="inlineStr">
         <is>
           <t>intraday</t>
         </is>
       </c>
-      <c r="D184" s="12" t="inlineStr">
+      <c r="D185" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor intraday</t>
         </is>
       </c>
-      <c r="E184" s="12" t="inlineStr">
+      <c r="E185" s="12" t="inlineStr">
         <is>
           <t>장중투자자별매매 조회</t>
         </is>
       </c>
-      <c r="F184" s="13" t="inlineStr">
+      <c r="F185" s="13" t="inlineStr">
         <is>
           <t>ka10063</t>
         </is>
       </c>
-      <c r="G184" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H184" s="12" t="inlineStr">
+      <c r="G185" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" s="12" t="inlineStr">
         <is>
           <t>--market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
 --amount-qty 기본:1 (금액수량구분 (1=금액&amp;수량))
@@ -8258,43 +8308,43 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="12" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B185" s="12" t="inlineStr">
+      <c r="B186" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C185" s="12" t="inlineStr">
+      <c r="C186" s="12" t="inlineStr">
         <is>
           <t>program-by-stock</t>
         </is>
       </c>
-      <c r="D185" s="12" t="inlineStr">
+      <c r="D186" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor program-by-stock</t>
         </is>
       </c>
-      <c r="E185" s="12" t="inlineStr">
+      <c r="E186" s="12" t="inlineStr">
         <is>
           <t>종목별프로그램매매현황 조회</t>
         </is>
       </c>
-      <c r="F185" s="13" t="inlineStr">
+      <c r="F186" s="13" t="inlineStr">
         <is>
           <t>ka90004</t>
         </is>
       </c>
-      <c r="G185" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H185" s="12" t="inlineStr">
+      <c r="G186" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" s="12" t="inlineStr">
         <is>
           <t>--date *필수 (일자 (YYYYMMDD))
 --market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
@@ -8302,43 +8352,43 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="12" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B186" s="12" t="inlineStr">
+      <c r="B187" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C186" s="12" t="inlineStr">
+      <c r="C187" s="12" t="inlineStr">
         <is>
           <t>program-top</t>
         </is>
       </c>
-      <c r="D186" s="12" t="inlineStr">
+      <c r="D187" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor program-top</t>
         </is>
       </c>
-      <c r="E186" s="12" t="inlineStr">
+      <c r="E187" s="12" t="inlineStr">
         <is>
           <t>프로그램순매수상위50 조회</t>
         </is>
       </c>
-      <c r="F186" s="13" t="inlineStr">
+      <c r="F187" s="13" t="inlineStr">
         <is>
           <t>ka90003</t>
         </is>
       </c>
-      <c r="G186" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H186" s="12" t="inlineStr">
+      <c r="G187" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" s="12" t="inlineStr">
         <is>
           <t>--trade [1, 2] 기본:2 (매매구분 (1=순매도, 2=순매수))
 --amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
@@ -8347,43 +8397,43 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="12" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B187" s="12" t="inlineStr">
+      <c r="B188" s="12" t="inlineStr">
         <is>
           <t>investor</t>
         </is>
       </c>
-      <c r="C187" s="12" t="inlineStr">
+      <c r="C188" s="12" t="inlineStr">
         <is>
           <t>stock-institution</t>
         </is>
       </c>
-      <c r="D187" s="12" t="inlineStr">
+      <c r="D188" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock investor stock-institution</t>
         </is>
       </c>
-      <c r="E187" s="12" t="inlineStr">
+      <c r="E188" s="12" t="inlineStr">
         <is>
           <t>종목별기관매매추이 조회</t>
         </is>
       </c>
-      <c r="F187" s="13" t="inlineStr">
+      <c r="F188" s="13" t="inlineStr">
         <is>
           <t>ka10045</t>
         </is>
       </c>
-      <c r="G187" s="12" t="inlineStr">
+      <c r="G188" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H187" s="12" t="inlineStr">
+      <c r="H188" s="12" t="inlineStr">
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
@@ -8392,43 +8442,43 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="12" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B188" s="12" t="inlineStr">
+      <c r="B189" s="12" t="inlineStr">
         <is>
           <t>lending</t>
         </is>
       </c>
-      <c r="C188" s="12" t="inlineStr">
+      <c r="C189" s="12" t="inlineStr">
         <is>
           <t>by-stock</t>
         </is>
       </c>
-      <c r="D188" s="12" t="inlineStr">
+      <c r="D189" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock lending by-stock</t>
         </is>
       </c>
-      <c r="E188" s="12" t="inlineStr">
+      <c r="E189" s="12" t="inlineStr">
         <is>
           <t>대차거래추이 종목별 조회</t>
         </is>
       </c>
-      <c r="F188" s="13" t="inlineStr">
+      <c r="F189" s="13" t="inlineStr">
         <is>
           <t>ka20068</t>
         </is>
       </c>
-      <c r="G188" s="12" t="inlineStr">
+      <c r="G189" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H188" s="12" t="inlineStr">
+      <c r="H189" s="12" t="inlineStr">
         <is>
           <t>--from (시작일자 (YYYYMMDD, 선택))
 --to (종료일자 (YYYYMMDD, 선택))
@@ -8436,86 +8486,86 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="12" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B189" s="12" t="inlineStr">
+      <c r="B190" s="12" t="inlineStr">
         <is>
           <t>lending</t>
         </is>
       </c>
-      <c r="C189" s="12" t="inlineStr">
+      <c r="C190" s="12" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="D189" s="12" t="inlineStr">
+      <c r="D190" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock lending detail</t>
         </is>
       </c>
-      <c r="E189" s="12" t="inlineStr">
+      <c r="E190" s="12" t="inlineStr">
         <is>
           <t>대차거래내역 조회</t>
         </is>
       </c>
-      <c r="F189" s="13" t="inlineStr">
+      <c r="F190" s="13" t="inlineStr">
         <is>
           <t>ka90012</t>
         </is>
       </c>
-      <c r="G189" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H189" s="12" t="inlineStr">
+      <c r="G190" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" s="12" t="inlineStr">
         <is>
           <t>--date *필수 (일자 (YYYYMMDD))
 --market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="12" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B190" s="12" t="inlineStr">
+      <c r="B191" s="12" t="inlineStr">
         <is>
           <t>lending</t>
         </is>
       </c>
-      <c r="C190" s="12" t="inlineStr">
+      <c r="C191" s="12" t="inlineStr">
         <is>
           <t>top10</t>
         </is>
       </c>
-      <c r="D190" s="12" t="inlineStr">
+      <c r="D191" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock lending top10</t>
         </is>
       </c>
-      <c r="E190" s="12" t="inlineStr">
+      <c r="E191" s="12" t="inlineStr">
         <is>
           <t>대차거래상위10종목 조회</t>
         </is>
       </c>
-      <c r="F190" s="13" t="inlineStr">
+      <c r="F191" s="13" t="inlineStr">
         <is>
           <t>ka10069</t>
         </is>
       </c>
-      <c r="G190" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H190" s="12" t="inlineStr">
+      <c r="G191" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" s="12" t="inlineStr">
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to (종료일자 (YYYYMMDD, 선택))
@@ -8523,43 +8573,43 @@
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="12" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B191" s="12" t="inlineStr">
+      <c r="B192" s="12" t="inlineStr">
         <is>
           <t>lending</t>
         </is>
       </c>
-      <c r="C191" s="12" t="inlineStr">
+      <c r="C192" s="12" t="inlineStr">
         <is>
           <t>trend</t>
         </is>
       </c>
-      <c r="D191" s="12" t="inlineStr">
+      <c r="D192" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock lending trend</t>
         </is>
       </c>
-      <c r="E191" s="12" t="inlineStr">
+      <c r="E192" s="12" t="inlineStr">
         <is>
           <t>대차거래추이 조회</t>
         </is>
       </c>
-      <c r="F191" s="13" t="inlineStr">
+      <c r="F192" s="13" t="inlineStr">
         <is>
           <t>ka10068</t>
         </is>
       </c>
-      <c r="G191" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H191" s="12" t="inlineStr">
+      <c r="G192" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" s="12" t="inlineStr">
         <is>
           <t>--from (시작일자 (YYYYMMDD, 선택))
 --to (종료일자 (YYYYMMDD, 선택))
@@ -8567,44 +8617,6 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B192" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C192" s="12" t="inlineStr">
-        <is>
-          <t>orderbook</t>
-        </is>
-      </c>
-      <c r="D192" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock orderbook</t>
-        </is>
-      </c>
-      <c r="E192" s="12" t="inlineStr">
-        <is>
-          <t>호가창 조회</t>
-        </is>
-      </c>
-      <c r="F192" s="13" t="inlineStr"/>
-      <c r="G192" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H192" s="12" t="inlineStr">
-        <is>
-          <t>--exchange [nasdaq, nyse, amex] (미국 거래소 (미국 종목 강제 라우팅))</t>
-        </is>
-      </c>
-    </row>
     <row r="193">
       <c r="A193" s="12" t="inlineStr">
         <is>
@@ -8618,17 +8630,17 @@
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>orderbook</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock price</t>
+          <t>kiwoom stock orderbook</t>
         </is>
       </c>
       <c r="E193" s="12" t="inlineStr">
         <is>
-          <t>종목 현재가 간단 조회</t>
+          <t>호가창 조회</t>
         </is>
       </c>
       <c r="F193" s="13" t="inlineStr"/>
@@ -8656,24 +8668,20 @@
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>quote-info</t>
+          <t>price</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock quote-info</t>
+          <t>kiwoom stock price</t>
         </is>
       </c>
       <c r="E194" s="12" t="inlineStr">
         <is>
-          <t>시세표성정보 조회</t>
-        </is>
-      </c>
-      <c r="F194" s="13" t="inlineStr">
-        <is>
-          <t>ka10007</t>
-        </is>
-      </c>
+          <t>종목 현재가 간단 조회</t>
+        </is>
+      </c>
+      <c r="F194" s="13" t="inlineStr"/>
       <c r="G194" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -8681,7 +8689,7 @@
       </c>
       <c r="H194" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>--exchange [nasdaq, nyse, amex] (미국 거래소 (미국 종목 강제 라우팅))</t>
         </is>
       </c>
     </row>
@@ -8698,117 +8706,117 @@
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
+          <t>quote-info</t>
+        </is>
+      </c>
+      <c r="D195" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock quote-info</t>
+        </is>
+      </c>
+      <c r="E195" s="12" t="inlineStr">
+        <is>
+          <t>시세표성정보 조회</t>
+        </is>
+      </c>
+      <c r="F195" s="13" t="inlineStr">
+        <is>
+          <t>ka10007</t>
+        </is>
+      </c>
+      <c r="G195" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H195" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B196" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C196" s="12" t="inlineStr">
+        <is>
           <t>search</t>
         </is>
       </c>
-      <c r="D195" s="12" t="inlineStr">
+      <c r="D196" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock search</t>
         </is>
       </c>
-      <c r="E195" s="12" t="inlineStr">
+      <c r="E196" s="12" t="inlineStr">
         <is>
           <t>캐시에서 종목 검색</t>
         </is>
       </c>
-      <c r="F195" s="13" t="inlineStr"/>
-      <c r="G195" s="12" t="inlineStr">
+      <c r="F196" s="13" t="inlineStr"/>
+      <c r="G196" s="12" t="inlineStr">
         <is>
           <t>KEYWORD (선택)</t>
         </is>
       </c>
-      <c r="H195" s="12" t="inlineStr">
+      <c r="H196" s="12" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq, etf, elw, etn, us] 기본:all (시장/유형 필터 (all/kospi/kosdaq/etf/elw/etn/us))
 --exchange [nasdaq, nyse, amex, all] 기본:all (미국 거래소 필터 (--market us 일 때만 사용))</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="12" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="12" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B196" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C196" s="12" t="inlineStr">
+      <c r="B197" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C197" s="12" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D196" s="12" t="inlineStr">
+      <c r="D197" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock short</t>
         </is>
       </c>
-      <c r="E196" s="12" t="inlineStr">
+      <c r="E197" s="12" t="inlineStr">
         <is>
           <t>공매도 추이 조회</t>
         </is>
       </c>
-      <c r="F196" s="13" t="inlineStr">
+      <c r="F197" s="13" t="inlineStr">
         <is>
           <t>ka10014</t>
         </is>
       </c>
-      <c r="G196" s="12" t="inlineStr">
+      <c r="G197" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H196" s="12" t="inlineStr">
+      <c r="H197" s="12" t="inlineStr">
         <is>
           <t>--from (시작일자 (YYYYMMDD, 기본=30일전))
 --to (종료일자 (YYYYMMDD, 기본=오늘))</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B197" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C197" s="12" t="inlineStr">
-        <is>
-          <t>sync</t>
-        </is>
-      </c>
-      <c r="D197" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock sync</t>
-        </is>
-      </c>
-      <c r="E197" s="12" t="inlineStr">
-        <is>
-          <t>전 시장 종목 리스트를 다운받아 캐시에 저장</t>
-        </is>
-      </c>
-      <c r="F197" s="13" t="inlineStr">
-        <is>
-          <t>ka10099</t>
-        </is>
-      </c>
-      <c r="G197" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H197" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="198">
       <c r="A198" s="12" t="inlineStr">
         <is>
@@ -8822,27 +8830,27 @@
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>tick-strength</t>
+          <t>sync</t>
         </is>
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock tick-strength</t>
+          <t>kiwoom stock sync</t>
         </is>
       </c>
       <c r="E198" s="12" t="inlineStr">
         <is>
-          <t>체결강도추이 시간별</t>
+          <t>전 시장 종목 리스트를 다운받아 캐시에 저장</t>
         </is>
       </c>
       <c r="F198" s="13" t="inlineStr">
         <is>
-          <t>ka10046</t>
+          <t>ka10099</t>
         </is>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
-          <t>CODE (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H198" s="12" t="inlineStr">
@@ -8864,22 +8872,22 @@
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>timeprice</t>
+          <t>tick-strength</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock timeprice</t>
+          <t>kiwoom stock tick-strength</t>
         </is>
       </c>
       <c r="E199" s="12" t="inlineStr">
         <is>
-          <t>시분 시세 조회</t>
+          <t>체결강도추이 시간별</t>
         </is>
       </c>
       <c r="F199" s="13" t="inlineStr">
         <is>
-          <t>ka10006</t>
+          <t>ka10046</t>
         </is>
       </c>
       <c r="G199" s="12" t="inlineStr">
@@ -8906,30 +8914,72 @@
       </c>
       <c r="C200" s="12" t="inlineStr">
         <is>
+          <t>timeprice</t>
+        </is>
+      </c>
+      <c r="D200" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock timeprice</t>
+        </is>
+      </c>
+      <c r="E200" s="12" t="inlineStr">
+        <is>
+          <t>시분 시세 조회</t>
+        </is>
+      </c>
+      <c r="F200" s="13" t="inlineStr">
+        <is>
+          <t>ka10006</t>
+        </is>
+      </c>
+      <c r="G200" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H200" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B201" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C201" s="12" t="inlineStr">
+        <is>
           <t>today-exec</t>
         </is>
       </c>
-      <c r="D200" s="12" t="inlineStr">
+      <c r="D201" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock today-exec</t>
         </is>
       </c>
-      <c r="E200" s="12" t="inlineStr">
+      <c r="E201" s="12" t="inlineStr">
         <is>
           <t>당일/전일 체결 조회</t>
         </is>
       </c>
-      <c r="F200" s="13" t="inlineStr">
+      <c r="F201" s="13" t="inlineStr">
         <is>
           <t>ka10084</t>
         </is>
       </c>
-      <c r="G200" s="12" t="inlineStr">
+      <c r="G201" s="12" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
         </is>
       </c>
-      <c r="H200" s="12" t="inlineStr">
+      <c r="H201" s="12" t="inlineStr">
         <is>
           <t>--when [1, 2] 기본:1 (당일전일 (1=당일, 2=전일))
 --mode [0, 1] (틱/분 (0=틱, 1=분))
@@ -8937,48 +8987,6 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="12" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="B201" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C201" s="12" t="inlineStr">
-        <is>
-          <t>today-volume</t>
-        </is>
-      </c>
-      <c r="D201" s="12" t="inlineStr">
-        <is>
-          <t>kiwoom stock today-volume</t>
-        </is>
-      </c>
-      <c r="E201" s="12" t="inlineStr">
-        <is>
-          <t>당일/전일 체결량 조회</t>
-        </is>
-      </c>
-      <c r="F201" s="13" t="inlineStr">
-        <is>
-          <t>ka10055</t>
-        </is>
-      </c>
-      <c r="G201" s="12" t="inlineStr">
-        <is>
-          <t>CODE (필수)</t>
-        </is>
-      </c>
-      <c r="H201" s="12" t="inlineStr">
-        <is>
-          <t>--when [1, 2] 기본:1 (당일전일 (1=당일, 2=전일))</t>
-        </is>
-      </c>
-    </row>
     <row r="202">
       <c r="A202" s="12" t="inlineStr">
         <is>
@@ -8992,22 +9000,22 @@
       </c>
       <c r="C202" s="12" t="inlineStr">
         <is>
-          <t>trader</t>
+          <t>today-volume</t>
         </is>
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>kiwoom stock trader</t>
+          <t>kiwoom stock today-volume</t>
         </is>
       </c>
       <c r="E202" s="12" t="inlineStr">
         <is>
-          <t>거래원 조회</t>
+          <t>당일/전일 체결량 조회</t>
         </is>
       </c>
       <c r="F202" s="13" t="inlineStr">
         <is>
-          <t>ka10002</t>
+          <t>ka10055</t>
         </is>
       </c>
       <c r="G202" s="12" t="inlineStr">
@@ -9017,7 +9025,7 @@
       </c>
       <c r="H202" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>--when [1, 2] 기본:1 (당일전일 (1=당일, 2=전일))</t>
         </is>
       </c>
     </row>
@@ -9034,70 +9042,74 @@
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
+          <t>trader</t>
+        </is>
+      </c>
+      <c r="D203" s="12" t="inlineStr">
+        <is>
+          <t>kiwoom stock trader</t>
+        </is>
+      </c>
+      <c r="E203" s="12" t="inlineStr">
+        <is>
+          <t>거래원 조회</t>
+        </is>
+      </c>
+      <c r="F203" s="13" t="inlineStr">
+        <is>
+          <t>ka10002</t>
+        </is>
+      </c>
+      <c r="G203" s="12" t="inlineStr">
+        <is>
+          <t>CODE (필수)</t>
+        </is>
+      </c>
+      <c r="H203" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="12" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B204" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C204" s="12" t="inlineStr">
+        <is>
           <t>watchlist</t>
         </is>
       </c>
-      <c r="D203" s="12" t="inlineStr">
+      <c r="D204" s="12" t="inlineStr">
         <is>
           <t>kiwoom stock watchlist</t>
         </is>
       </c>
-      <c r="E203" s="12" t="inlineStr">
+      <c r="E204" s="12" t="inlineStr">
         <is>
           <t>관심종목정보 조회 (코드를 |로 구분, 예: 005930|000660)</t>
         </is>
       </c>
-      <c r="F203" s="13" t="inlineStr">
+      <c r="F204" s="13" t="inlineStr">
         <is>
           <t>ka10095</t>
         </is>
       </c>
-      <c r="G203" s="12" t="inlineStr">
+      <c r="G204" s="12" t="inlineStr">
         <is>
           <t>CODES (필수)</t>
         </is>
       </c>
-      <c r="H203" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="14" t="inlineStr">
-        <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="B204" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C204" s="14" t="inlineStr">
-        <is>
-          <t>after-hours</t>
-        </is>
-      </c>
-      <c r="D204" s="14" t="inlineStr">
-        <is>
-          <t>kiwoom stream after-hours</t>
-        </is>
-      </c>
-      <c r="E204" s="14" t="inlineStr">
-        <is>
-          <t>주식시간외호가 실시간 (0E)</t>
-        </is>
-      </c>
-      <c r="F204" s="15" t="inlineStr"/>
-      <c r="G204" s="14" t="inlineStr">
-        <is>
-          <t>CODES (복수) (필수)</t>
-        </is>
-      </c>
-      <c r="H204" s="14" t="inlineStr">
-        <is>
-          <t>--raw (JSON 원본 출력)</t>
+      <c r="H204" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9114,23 +9126,23 @@
       </c>
       <c r="C205" s="14" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>after-hours</t>
         </is>
       </c>
       <c r="D205" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream balance</t>
+          <t>kiwoom stream after-hours</t>
         </is>
       </c>
       <c r="E205" s="14" t="inlineStr">
         <is>
-          <t>잔고 실시간 (04)</t>
+          <t>주식시간외호가 실시간 (0E)</t>
         </is>
       </c>
       <c r="F205" s="15" t="inlineStr"/>
       <c r="G205" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H205" s="14" t="inlineStr">
@@ -9152,23 +9164,23 @@
       </c>
       <c r="C206" s="14" t="inlineStr">
         <is>
-          <t>best-bid</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="D206" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream best-bid</t>
+          <t>kiwoom stream balance</t>
         </is>
       </c>
       <c r="E206" s="14" t="inlineStr">
         <is>
-          <t>주식우선호가 실시간 (0C)</t>
+          <t>잔고 실시간 (04)</t>
         </is>
       </c>
       <c r="F206" s="15" t="inlineStr"/>
       <c r="G206" s="14" t="inlineStr">
         <is>
-          <t>CODES (복수) (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H206" s="14" t="inlineStr">
@@ -9190,64 +9202,64 @@
       </c>
       <c r="C207" s="14" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>best-bid</t>
         </is>
       </c>
       <c r="D207" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream custom</t>
+          <t>kiwoom stream best-bid</t>
         </is>
       </c>
       <c r="E207" s="14" t="inlineStr">
         <is>
-          <t>커스텀 실시간 타입으로 스트리밍</t>
+          <t>주식우선호가 실시간 (0C)</t>
         </is>
       </c>
       <c r="F207" s="15" t="inlineStr"/>
       <c r="G207" s="14" t="inlineStr">
         <is>
+          <t>CODES (복수) (필수)</t>
+        </is>
+      </c>
+      <c r="H207" s="14" t="inlineStr">
+        <is>
+          <t>--raw (JSON 원본 출력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="14" t="inlineStr">
+        <is>
+          <t>stream</t>
+        </is>
+      </c>
+      <c r="B208" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C208" s="14" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D208" s="14" t="inlineStr">
+        <is>
+          <t>kiwoom stream custom</t>
+        </is>
+      </c>
+      <c r="E208" s="14" t="inlineStr">
+        <is>
+          <t>커스텀 실시간 타입으로 스트리밍</t>
+        </is>
+      </c>
+      <c r="F208" s="15" t="inlineStr"/>
+      <c r="G208" s="14" t="inlineStr">
+        <is>
           <t>TYPE_CODES (필수)
 CODES (복수) (선택)</t>
         </is>
       </c>
-      <c r="H207" s="14" t="inlineStr">
-        <is>
-          <t>--raw (JSON 원본 출력)</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="14" t="inlineStr">
-        <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="B208" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C208" s="14" t="inlineStr">
-        <is>
-          <t>elw-indicator</t>
-        </is>
-      </c>
-      <c r="D208" s="14" t="inlineStr">
-        <is>
-          <t>kiwoom stream elw-indicator</t>
-        </is>
-      </c>
-      <c r="E208" s="14" t="inlineStr">
-        <is>
-          <t>ELW 지표 실시간 (0u)</t>
-        </is>
-      </c>
-      <c r="F208" s="15" t="inlineStr"/>
-      <c r="G208" s="14" t="inlineStr">
-        <is>
-          <t>CODES (복수) (필수)</t>
-        </is>
-      </c>
       <c r="H208" s="14" t="inlineStr">
         <is>
           <t>--raw (JSON 원본 출력)</t>
@@ -9267,17 +9279,17 @@
       </c>
       <c r="C209" s="14" t="inlineStr">
         <is>
-          <t>elw-theory</t>
+          <t>elw-indicator</t>
         </is>
       </c>
       <c r="D209" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream elw-theory</t>
+          <t>kiwoom stream elw-indicator</t>
         </is>
       </c>
       <c r="E209" s="14" t="inlineStr">
         <is>
-          <t>ELW 이론가 실시간 (0m)</t>
+          <t>ELW 지표 실시간 (0u)</t>
         </is>
       </c>
       <c r="F209" s="15" t="inlineStr"/>
@@ -9305,17 +9317,17 @@
       </c>
       <c r="C210" s="14" t="inlineStr">
         <is>
-          <t>etf-nav</t>
+          <t>elw-theory</t>
         </is>
       </c>
       <c r="D210" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream etf-nav</t>
+          <t>kiwoom stream elw-theory</t>
         </is>
       </c>
       <c r="E210" s="14" t="inlineStr">
         <is>
-          <t>ETF NAV 실시간 (0G)</t>
+          <t>ELW 이론가 실시간 (0m)</t>
         </is>
       </c>
       <c r="F210" s="15" t="inlineStr"/>
@@ -9343,17 +9355,17 @@
       </c>
       <c r="C211" s="14" t="inlineStr">
         <is>
-          <t>expected</t>
+          <t>etf-nav</t>
         </is>
       </c>
       <c r="D211" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream expected</t>
+          <t>kiwoom stream etf-nav</t>
         </is>
       </c>
       <c r="E211" s="14" t="inlineStr">
         <is>
-          <t>주식예상체결 실시간 (0H)</t>
+          <t>ETF NAV 실시간 (0G)</t>
         </is>
       </c>
       <c r="F211" s="15" t="inlineStr"/>
@@ -9381,17 +9393,17 @@
       </c>
       <c r="C212" s="14" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>expected</t>
         </is>
       </c>
       <c r="D212" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream gold</t>
+          <t>kiwoom stream expected</t>
         </is>
       </c>
       <c r="E212" s="14" t="inlineStr">
         <is>
-          <t>국제금환산가격 실시간 (0I)</t>
+          <t>주식예상체결 실시간 (0H)</t>
         </is>
       </c>
       <c r="F212" s="15" t="inlineStr"/>
@@ -9419,23 +9431,23 @@
       </c>
       <c r="C213" s="14" t="inlineStr">
         <is>
-          <t>market-time</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="D213" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream market-time</t>
+          <t>kiwoom stream gold</t>
         </is>
       </c>
       <c r="E213" s="14" t="inlineStr">
         <is>
-          <t>장시작시간 실시간 (0s)</t>
+          <t>국제금환산가격 실시간 (0I)</t>
         </is>
       </c>
       <c r="F213" s="15" t="inlineStr"/>
       <c r="G213" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H213" s="14" t="inlineStr">
@@ -9457,23 +9469,23 @@
       </c>
       <c r="C214" s="14" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>market-time</t>
         </is>
       </c>
       <c r="D214" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream multi</t>
+          <t>kiwoom stream market-time</t>
         </is>
       </c>
       <c r="E214" s="14" t="inlineStr">
         <is>
-          <t>주식체결+호가잔량 동시 스트리밍 (0B+0D)</t>
+          <t>장시작시간 실시간 (0s)</t>
         </is>
       </c>
       <c r="F214" s="15" t="inlineStr"/>
       <c r="G214" s="14" t="inlineStr">
         <is>
-          <t>CODES (복수) (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H214" s="14" t="inlineStr">
@@ -9495,23 +9507,23 @@
       </c>
       <c r="C215" s="14" t="inlineStr">
         <is>
-          <t>order</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="D215" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream order</t>
+          <t>kiwoom stream multi</t>
         </is>
       </c>
       <c r="E215" s="14" t="inlineStr">
         <is>
-          <t>주문체결 실시간 (00)</t>
+          <t>주식체결+호가잔량 동시 스트리밍 (0B+0D)</t>
         </is>
       </c>
       <c r="F215" s="15" t="inlineStr"/>
       <c r="G215" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H215" s="14" t="inlineStr">
@@ -9533,23 +9545,23 @@
       </c>
       <c r="C216" s="14" t="inlineStr">
         <is>
-          <t>orderbook</t>
+          <t>order</t>
         </is>
       </c>
       <c r="D216" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream orderbook</t>
+          <t>kiwoom stream order</t>
         </is>
       </c>
       <c r="E216" s="14" t="inlineStr">
         <is>
-          <t>주식호가잔량 실시간 (0D)</t>
+          <t>주문체결 실시간 (00)</t>
         </is>
       </c>
       <c r="F216" s="15" t="inlineStr"/>
       <c r="G216" s="14" t="inlineStr">
         <is>
-          <t>CODES (복수) (필수)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H216" s="14" t="inlineStr">
@@ -9571,17 +9583,17 @@
       </c>
       <c r="C217" s="14" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>orderbook</t>
         </is>
       </c>
       <c r="D217" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream price</t>
+          <t>kiwoom stream orderbook</t>
         </is>
       </c>
       <c r="E217" s="14" t="inlineStr">
         <is>
-          <t>주식기세 실시간 (0A)</t>
+          <t>주식호가잔량 실시간 (0D)</t>
         </is>
       </c>
       <c r="F217" s="15" t="inlineStr"/>
@@ -9609,17 +9621,17 @@
       </c>
       <c r="C218" s="14" t="inlineStr">
         <is>
-          <t>program</t>
+          <t>price</t>
         </is>
       </c>
       <c r="D218" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream program</t>
+          <t>kiwoom stream price</t>
         </is>
       </c>
       <c r="E218" s="14" t="inlineStr">
         <is>
-          <t>종목프로그램매매 실시간 (0w)</t>
+          <t>주식기세 실시간 (0A)</t>
         </is>
       </c>
       <c r="F218" s="15" t="inlineStr"/>
@@ -9647,17 +9659,17 @@
       </c>
       <c r="C219" s="14" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>program</t>
         </is>
       </c>
       <c r="D219" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream quote</t>
+          <t>kiwoom stream program</t>
         </is>
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>주식체결 실시간 (0B)</t>
+          <t>종목프로그램매매 실시간 (0w)</t>
         </is>
       </c>
       <c r="F219" s="15" t="inlineStr"/>
@@ -9685,17 +9697,17 @@
       </c>
       <c r="C220" s="14" t="inlineStr">
         <is>
-          <t>sector-change</t>
+          <t>quote</t>
         </is>
       </c>
       <c r="D220" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream sector-change</t>
+          <t>kiwoom stream quote</t>
         </is>
       </c>
       <c r="E220" s="14" t="inlineStr">
         <is>
-          <t>업종등락 실시간 (0U)</t>
+          <t>주식체결 실시간 (0B)</t>
         </is>
       </c>
       <c r="F220" s="15" t="inlineStr"/>
@@ -9723,17 +9735,17 @@
       </c>
       <c r="C221" s="14" t="inlineStr">
         <is>
-          <t>sector-index</t>
+          <t>sector-change</t>
         </is>
       </c>
       <c r="D221" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream sector-index</t>
+          <t>kiwoom stream sector-change</t>
         </is>
       </c>
       <c r="E221" s="14" t="inlineStr">
         <is>
-          <t>업종지수 실시간 (0J)</t>
+          <t>업종등락 실시간 (0U)</t>
         </is>
       </c>
       <c r="F221" s="15" t="inlineStr"/>
@@ -9761,17 +9773,17 @@
       </c>
       <c r="C222" s="14" t="inlineStr">
         <is>
-          <t>stock-info</t>
+          <t>sector-index</t>
         </is>
       </c>
       <c r="D222" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream stock-info</t>
+          <t>kiwoom stream sector-index</t>
         </is>
       </c>
       <c r="E222" s="14" t="inlineStr">
         <is>
-          <t>주식종목정보 실시간 (0g)</t>
+          <t>업종지수 실시간 (0J)</t>
         </is>
       </c>
       <c r="F222" s="15" t="inlineStr"/>
@@ -9799,17 +9811,17 @@
       </c>
       <c r="C223" s="14" t="inlineStr">
         <is>
-          <t>trader</t>
+          <t>stock-info</t>
         </is>
       </c>
       <c r="D223" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream trader</t>
+          <t>kiwoom stream stock-info</t>
         </is>
       </c>
       <c r="E223" s="14" t="inlineStr">
         <is>
-          <t>주식당일거래원 실시간 (0F)</t>
+          <t>주식종목정보 실시간 (0g)</t>
         </is>
       </c>
       <c r="F223" s="15" t="inlineStr"/>
@@ -9837,28 +9849,28 @@
       </c>
       <c r="C224" s="14" t="inlineStr">
         <is>
-          <t>types</t>
+          <t>trader</t>
         </is>
       </c>
       <c r="D224" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream types</t>
+          <t>kiwoom stream trader</t>
         </is>
       </c>
       <c r="E224" s="14" t="inlineStr">
         <is>
-          <t>사용 가능한 실시간 타입 코드 목록</t>
+          <t>주식당일거래원 실시간 (0F)</t>
         </is>
       </c>
       <c r="F224" s="15" t="inlineStr"/>
       <c r="G224" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODES (복수) (필수)</t>
         </is>
       </c>
       <c r="H224" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>--raw (JSON 원본 출력)</t>
         </is>
       </c>
     </row>
@@ -9875,71 +9887,109 @@
       </c>
       <c r="C225" s="14" t="inlineStr">
         <is>
-          <t>vi</t>
+          <t>types</t>
         </is>
       </c>
       <c r="D225" s="14" t="inlineStr">
         <is>
-          <t>kiwoom stream vi</t>
+          <t>kiwoom stream types</t>
         </is>
       </c>
       <c r="E225" s="14" t="inlineStr">
         <is>
-          <t>VI발동/해제 실시간 (1h)</t>
+          <t>사용 가능한 실시간 타입 코드 목록</t>
         </is>
       </c>
       <c r="F225" s="15" t="inlineStr"/>
       <c r="G225" s="14" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H225" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="14" t="inlineStr">
+        <is>
+          <t>stream</t>
+        </is>
+      </c>
+      <c r="B226" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C226" s="14" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="D226" s="14" t="inlineStr">
+        <is>
+          <t>kiwoom stream vi</t>
+        </is>
+      </c>
+      <c r="E226" s="14" t="inlineStr">
+        <is>
+          <t>VI발동/해제 실시간 (1h)</t>
+        </is>
+      </c>
+      <c r="F226" s="15" t="inlineStr"/>
+      <c r="G226" s="14" t="inlineStr">
+        <is>
           <t>CODES (복수) (필수)</t>
         </is>
       </c>
-      <c r="H225" s="14" t="inlineStr">
+      <c r="H226" s="14" t="inlineStr">
         <is>
           <t>--raw (JSON 원본 출력)</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="6" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="6" t="inlineStr">
         <is>
           <t>watch</t>
         </is>
       </c>
-      <c r="B226" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C226" s="6" t="inlineStr">
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
         <is>
           <t>watch</t>
         </is>
       </c>
-      <c r="D226" s="6" t="inlineStr">
+      <c r="D227" s="6" t="inlineStr">
         <is>
           <t>kiwoom watch</t>
         </is>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="E227" s="6" t="inlineStr">
         <is>
           <t>실시간 종목 모니터링 (TUI 대시보드)</t>
         </is>
       </c>
-      <c r="F226" s="7" t="inlineStr"/>
-      <c r="G226" s="6" t="inlineStr">
+      <c r="F227" s="7" t="inlineStr"/>
+      <c r="G227" s="6" t="inlineStr">
         <is>
           <t>CODES (복수) (필수)</t>
         </is>
       </c>
-      <c r="H226" s="6" t="inlineStr">
+      <c r="H227" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H226"/>
+  <autoFilter ref="A1:H227"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10064,7 +10114,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
@@ -10139,7 +10189,7 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/kiwoom_cli_commands.xlsx
+++ b/kiwoom_cli_commands.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="전체 명령어" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 명령어" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체 명령어'!$A$1:$H$231</definedName>
@@ -5791,7 +5791,7 @@
       <c r="H128" s="12" t="inlineStr">
         <is>
           <t>--price (주문가격 (시장가 주문시 생략, 미국주식은 소수점 4자리까지))
---type [after-hours, best, best-fok, best-ioc, conditional, first, fok, ioc, limit, loc, market, market-fok, market-ioc, mid, mid-fok, mid-ioc, moc, pre-market, single, stop, stop-limit, twap, twap-limit, vwap, vwap-limit] 기본:market (주문유형)
+--type [after-hours, best, best-fok, best-ioc, conditional, first, fok, ioc, limit, loc, market, market-fok, market-ioc, mid, mid-fok, mid-ioc, moc, pre-market, single, stop, stop-limit, twap, twap-limit, vwap, vwap-limit] (주문유형 (기본: --price 지정 시 limit, 미지정 시 market))
 --exchange [KRX, NXT, SOR, nasdaq, nyse, amex] (거래소 (기본: 국내 KRX / 미국 자동판별))
 --cond-price (조건부가격 (국내 전용))
 --confirm (확인 프롬프트 없이 주문 실행)
@@ -6055,10 +6055,12 @@
       <c r="H134" s="12" t="inlineStr">
         <is>
           <t>--price (주문가격 (시장가 주문시 생략))
---type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
+--type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] (주문유형 (기본: --price 지정 시 limit, 미지정 시 market))
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
 --cond-price (조건부가격)
---confirm (확인 프롬프트 없이 주문 실행)</t>
+--confirm (확인 프롬프트 없이 주문 실행)
+--dry-run (전송될 내용만 출력하고 주문을 전송하지 않음)
+--client-order-id (멱등성 키 (같은 키 재실행 시 재전송 없이 이전 응답 반환))</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6105,9 @@
         <is>
           <t>--qty (취소수량 (0=전량취소))
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
---confirm (확인 프롬프트 없이 주문 실행)</t>
+--confirm (확인 프롬프트 없이 주문 실행)
+--dry-run (전송될 내용만 출력하고 주문을 전송하지 않음)
+--client-order-id (멱등성 키 (같은 키 재실행 시 재전송 없이 이전 응답 반환))</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6154,9 @@
         <is>
           <t>--exchange [KRX, NXT, SOR] 기본:KRX (거래소)
 --cond-price (정정 조건부가격)
---confirm (확인 프롬프트 없이 주문 실행)</t>
+--confirm (확인 프롬프트 없이 주문 실행)
+--dry-run (전송될 내용만 출력하고 주문을 전송하지 않음)
+--client-order-id (멱등성 키 (같은 키 재실행 시 재전송 없이 이전 응답 반환))</t>
         </is>
       </c>
     </row>
@@ -6194,10 +6200,12 @@
       <c r="H137" s="12" t="inlineStr">
         <is>
           <t>--price (주문가격 (시장가 주문시 생략))
---type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
+--type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] (주문유형 (기본: --price 지정 시 limit, 미지정 시 market))
 --exchange [KRX, NXT, SOR] 기본:KRX (거래소)
 --cond-price (조건부가격)
---confirm (확인 프롬프트 없이 주문 실행)</t>
+--confirm (확인 프롬프트 없이 주문 실행)
+--dry-run (전송될 내용만 출력하고 주문을 전송하지 않음)
+--client-order-id (멱등성 키 (같은 키 재실행 시 재전송 없이 이전 응답 반환))</t>
         </is>
       </c>
     </row>
@@ -6283,8 +6291,10 @@
       <c r="H139" s="12" t="inlineStr">
         <is>
           <t>--price (주문가격 (시장가 주문시 생략))
---type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
---confirm (확인 프롬프트 없이 주문 실행)</t>
+--type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] (주문유형 (기본: --price 지정 시 limit, 미지정 시 market))
+--confirm (확인 프롬프트 없이 주문 실행)
+--dry-run (전송될 내용만 출력하고 주문을 전송하지 않음)
+--client-order-id (멱등성 키 (같은 키 재실행 시 재전송 없이 이전 응답 반환))</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6338,9 @@
       <c r="H140" s="12" t="inlineStr">
         <is>
           <t>--qty (취소수량 (0=전량취소))
---confirm (확인 프롬프트 없이 주문 실행)</t>
+--confirm (확인 프롬프트 없이 주문 실행)
+--dry-run (전송될 내용만 출력하고 주문을 전송하지 않음)
+--client-order-id (멱등성 키 (같은 키 재실행 시 재전송 없이 이전 응답 반환))</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6553,9 @@
       </c>
       <c r="H145" s="12" t="inlineStr">
         <is>
-          <t>--confirm (확인 프롬프트 없이 주문 실행)</t>
+          <t>--confirm (확인 프롬프트 없이 주문 실행)
+--dry-run (전송될 내용만 출력하고 주문을 전송하지 않음)
+--client-order-id (멱등성 키 (같은 키 재실행 시 재전송 없이 이전 응답 반환))</t>
         </is>
       </c>
     </row>
@@ -6627,8 +6641,10 @@
       <c r="H147" s="12" t="inlineStr">
         <is>
           <t>--price (주문가격 (시장가 주문시 생략))
---type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
---confirm (확인 프롬프트 없이 주문 실행)</t>
+--type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] (주문유형 (기본: --price 지정 시 limit, 미지정 시 market))
+--confirm (확인 프롬프트 없이 주문 실행)
+--dry-run (전송될 내용만 출력하고 주문을 전송하지 않음)
+--client-order-id (멱등성 키 (같은 키 재실행 시 재전송 없이 이전 응답 반환))</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6730,7 @@
       <c r="H149" s="12" t="inlineStr">
         <is>
           <t>--price (주문가격 (시장가 주문시 생략, 미국주식은 소수점 4자리까지))
---type [after-hours, best, best-fok, best-ioc, conditional, first, fok, ioc, limit, loc, market, market-fok, market-ioc, mid, mid-fok, mid-ioc, moc, pre-market, single, stop, stop-limit, twap, twap-limit, vwap, vwap-limit] 기본:market (주문유형)
+--type [after-hours, best, best-fok, best-ioc, conditional, first, fok, ioc, limit, loc, market, market-fok, market-ioc, mid, mid-fok, mid-ioc, moc, pre-market, single, stop, stop-limit, twap, twap-limit, vwap, vwap-limit] (주문유형 (기본: --price 지정 시 limit, 미지정 시 market))
 --exchange [KRX, NXT, SOR, nasdaq, nyse, amex] (거래소 (기본: 국내 KRX / 미국 자동판별))
 --cond-price (조건부가격 (국내 전용))
 --stop (STOP가격 (미국 stop/stop-limit 전용))

--- a/kiwoom_cli_commands.xlsx
+++ b/kiwoom_cli_commands.xlsx
@@ -2162,9 +2162,9 @@
           <t>--profile 기본:default (프로필 이름)
 --appkey (키움 API App Key)
 --secretkey (키움 API Secret Key)
---domain [prod, mock] 기본:mock (도메인)
+--domain [prod, mock] (도메인)
 --account (계좌번호)
---token-storage [keychain, env] 기본:keychain (접근토큰 저장 방식)</t>
+--token-storage [keychain, env] (접근토큰 저장 방식)</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,8 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>--paths (경로+한줄설명 평면 목록만 출력 (전체 트리 대비 토큰 절약 — 발견용))
+--depth (하위 명령 재귀 깊이 제한 (예: --depth 1 = 한 단계만))</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2470,11 @@
           <t>ELW 잔량 순위</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr"/>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>ka30010</t>
+        </is>
+      </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2509,7 +2514,11 @@
           <t>거래원별 ELW 순매매 상위</t>
         </is>
       </c>
-      <c r="F47" s="11" t="inlineStr"/>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>ka30002</t>
+        </is>
+      </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2551,7 +2560,11 @@
           <t>ELW 등락율 순위</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr"/>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>ka30009</t>
+        </is>
+      </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2591,7 +2604,11 @@
           <t>ELW 종목 상세정보</t>
         </is>
       </c>
-      <c r="F49" s="11" t="inlineStr"/>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>ka30012</t>
+        </is>
+      </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -2629,7 +2646,11 @@
           <t>ELW 괴리율</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr"/>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>ka30004</t>
+        </is>
+      </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2671,7 +2692,11 @@
           <t>ELW LP 보유 일별 추이</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr"/>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>ka30003</t>
+        </is>
+      </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
           <t>UNDERLYING_CODE (필수)</t>
@@ -2709,7 +2734,11 @@
           <t>ELW 근접율</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr"/>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>ka30011</t>
+        </is>
+      </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -2747,7 +2776,11 @@
           <t>ELW 조건 검색</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr"/>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>ka30005</t>
+        </is>
+      </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2789,7 +2822,11 @@
           <t>ELW 민감도 지표</t>
         </is>
       </c>
-      <c r="F54" s="11" t="inlineStr"/>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>ka10050</t>
+        </is>
+      </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -2827,7 +2864,11 @@
           <t>ELW 일별 민감도 지표</t>
         </is>
       </c>
-      <c r="F55" s="11" t="inlineStr"/>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>ka10048</t>
+        </is>
+      </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -2865,7 +2906,11 @@
           <t>ELW 가격 급등락</t>
         </is>
       </c>
-      <c r="F56" s="11" t="inlineStr"/>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>ka30001</t>
+        </is>
+      </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2911,7 +2956,11 @@
           <t>ETF 전체 시세</t>
         </is>
       </c>
-      <c r="F57" s="11" t="inlineStr"/>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>ka40004</t>
+        </is>
+      </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2954,7 +3003,11 @@
           <t>ETF 일별추이</t>
         </is>
       </c>
-      <c r="F58" s="11" t="inlineStr"/>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>ka40003</t>
+        </is>
+      </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -2992,7 +3045,11 @@
           <t>ETF 일자별 체결</t>
         </is>
       </c>
-      <c r="F59" s="11" t="inlineStr"/>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>ka40008</t>
+        </is>
+      </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -3030,7 +3087,11 @@
           <t>ETF 종목정보</t>
         </is>
       </c>
-      <c r="F60" s="11" t="inlineStr"/>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>ka40002</t>
+        </is>
+      </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -3068,7 +3129,11 @@
           <t>ETF 수익율 조회</t>
         </is>
       </c>
-      <c r="F61" s="11" t="inlineStr"/>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>ka40001</t>
+        </is>
+      </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -3107,7 +3172,11 @@
           <t>ETF 시간대별 체결</t>
         </is>
       </c>
-      <c r="F62" s="11" t="inlineStr"/>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>ka40007</t>
+        </is>
+      </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -3145,7 +3214,11 @@
           <t>ETF 시간대별 체결 (상세)</t>
         </is>
       </c>
-      <c r="F63" s="11" t="inlineStr"/>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>ka40009</t>
+        </is>
+      </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -3183,7 +3256,11 @@
           <t>ETF 시간대별 추이</t>
         </is>
       </c>
-      <c r="F64" s="11" t="inlineStr"/>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>ka40006</t>
+        </is>
+      </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -3221,7 +3298,11 @@
           <t>ETF 시간대별 추이 (상세)</t>
         </is>
       </c>
-      <c r="F65" s="11" t="inlineStr"/>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>ka40010</t>
+        </is>
+      </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -3259,7 +3340,11 @@
           <t>금현물 일봉 차트</t>
         </is>
       </c>
-      <c r="F66" s="11" t="inlineStr"/>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>ka50081</t>
+        </is>
+      </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3299,7 +3384,11 @@
           <t>금현물 분봉 차트</t>
         </is>
       </c>
-      <c r="F67" s="11" t="inlineStr"/>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>ka50080</t>
+        </is>
+      </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3339,7 +3428,11 @@
           <t>금현물 월봉 차트</t>
         </is>
       </c>
-      <c r="F68" s="11" t="inlineStr"/>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>ka50083</t>
+        </is>
+      </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3379,7 +3472,11 @@
           <t>금현물 틱차트</t>
         </is>
       </c>
-      <c r="F69" s="11" t="inlineStr"/>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>ka50079</t>
+        </is>
+      </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3419,7 +3516,11 @@
           <t>금현물 주봉 차트</t>
         </is>
       </c>
-      <c r="F70" s="11" t="inlineStr"/>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>ka50082</t>
+        </is>
+      </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3459,7 +3560,11 @@
           <t>금현물 일별 추이</t>
         </is>
       </c>
-      <c r="F71" s="11" t="inlineStr"/>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>ka50012</t>
+        </is>
+      </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3498,7 +3603,11 @@
           <t>금현물 체결 추이</t>
         </is>
       </c>
-      <c r="F72" s="11" t="inlineStr"/>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>ka50010</t>
+        </is>
+      </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3536,7 +3645,11 @@
           <t>금현물 예상 체결</t>
         </is>
       </c>
-      <c r="F73" s="11" t="inlineStr"/>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>ka50087</t>
+        </is>
+      </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3574,7 +3687,11 @@
           <t>금현물 투자자 현황</t>
         </is>
       </c>
-      <c r="F74" s="11" t="inlineStr"/>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>ka52301</t>
+        </is>
+      </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3612,7 +3729,11 @@
           <t>금현물 호가</t>
         </is>
       </c>
-      <c r="F75" s="11" t="inlineStr"/>
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>ka50101</t>
+        </is>
+      </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3651,7 +3772,11 @@
           <t>금현물 시세정보</t>
         </is>
       </c>
-      <c r="F76" s="11" t="inlineStr"/>
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>ka50100</t>
+        </is>
+      </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3689,7 +3814,11 @@
           <t>금현물 당일 분봉 차트</t>
         </is>
       </c>
-      <c r="F77" s="11" t="inlineStr"/>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>ka50092</t>
+        </is>
+      </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3728,7 +3857,11 @@
           <t>금현물 당일 틱차트</t>
         </is>
       </c>
-      <c r="F78" s="11" t="inlineStr"/>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>ka50091</t>
+        </is>
+      </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3767,7 +3900,11 @@
           <t>프로그램매매 차익잔고 추이</t>
         </is>
       </c>
-      <c r="F79" s="11" t="inlineStr"/>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>ka90006</t>
+        </is>
+      </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3806,7 +3943,11 @@
           <t>프로그램매매 누적 추이</t>
         </is>
       </c>
-      <c r="F80" s="11" t="inlineStr"/>
+      <c r="F80" s="11" t="inlineStr">
+        <is>
+          <t>ka90007</t>
+        </is>
+      </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3847,7 +3988,11 @@
           <t>프로그램매매 추이 (일자별)</t>
         </is>
       </c>
-      <c r="F81" s="11" t="inlineStr"/>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>ka90010</t>
+        </is>
+      </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3889,7 +4034,11 @@
           <t>종목 일별 프로그램매매 추이</t>
         </is>
       </c>
-      <c r="F82" s="11" t="inlineStr"/>
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>ka90013</t>
+        </is>
+      </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -3928,7 +4077,11 @@
           <t>종목 시간별 프로그램매매 추이</t>
         </is>
       </c>
-      <c r="F83" s="11" t="inlineStr"/>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>ka90008</t>
+        </is>
+      </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -3967,7 +4120,11 @@
           <t>프로그램매매 추이 (시간대별)</t>
         </is>
       </c>
-      <c r="F84" s="11" t="inlineStr"/>
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>ka90005</t>
+        </is>
+      </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4009,7 +4166,11 @@
           <t>시간외 단일가 등락율 순위</t>
         </is>
       </c>
-      <c r="F85" s="11" t="inlineStr"/>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>ka10098</t>
+        </is>
+      </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4052,7 +4213,11 @@
           <t>거래대금 상위</t>
         </is>
       </c>
-      <c r="F86" s="11" t="inlineStr"/>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>ka10032</t>
+        </is>
+      </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4092,7 +4257,11 @@
           <t>잔량율 급증</t>
         </is>
       </c>
-      <c r="F87" s="11" t="inlineStr"/>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>ka10022</t>
+        </is>
+      </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4135,7 +4304,11 @@
           <t>종목별 증권사 순위</t>
         </is>
       </c>
-      <c r="F88" s="11" t="inlineStr"/>
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>ka10038</t>
+        </is>
+      </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -4176,7 +4349,11 @@
           <t>증권사별 매매 상위</t>
         </is>
       </c>
-      <c r="F89" s="11" t="inlineStr"/>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>ka10039</t>
+        </is>
+      </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
           <t>BROKER_CODE (필수)</t>
@@ -4217,7 +4394,11 @@
           <t>전일대비 등락률 상위</t>
         </is>
       </c>
-      <c r="F90" s="11" t="inlineStr"/>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>ka10027</t>
+        </is>
+      </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4263,7 +4444,11 @@
           <t>신용비율 상위</t>
         </is>
       </c>
-      <c r="F91" s="11" t="inlineStr"/>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>ka10033</t>
+        </is>
+      </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4306,7 +4491,11 @@
           <t>예상체결 등락률 상위</t>
         </is>
       </c>
-      <c r="F92" s="11" t="inlineStr"/>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>ka10029</t>
+        </is>
+      </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4350,7 +4539,11 @@
           <t>외국계 창구 매매 상위</t>
         </is>
       </c>
-      <c r="F93" s="11" t="inlineStr"/>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>ka10037</t>
+        </is>
+      </c>
       <c r="G93" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4392,7 +4585,11 @@
           <t>외인 연속 순매매 상위</t>
         </is>
       </c>
-      <c r="F94" s="11" t="inlineStr"/>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>ka10035</t>
+        </is>
+      </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4433,7 +4630,11 @@
           <t>외인 한도소진율 증가 상위</t>
         </is>
       </c>
-      <c r="F95" s="11" t="inlineStr"/>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>ka10036</t>
+        </is>
+      </c>
       <c r="G95" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4473,7 +4674,11 @@
           <t>외국인/기관 매매 상위</t>
         </is>
       </c>
-      <c r="F96" s="11" t="inlineStr"/>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>ka90009</t>
+        </is>
+      </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4515,7 +4720,11 @@
           <t>외인 기간별 매매 상위</t>
         </is>
       </c>
-      <c r="F97" s="11" t="inlineStr"/>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>ka10034</t>
+        </is>
+      </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4556,7 +4765,11 @@
           <t>실시간 종목 조회 순위</t>
         </is>
       </c>
-      <c r="F98" s="11" t="inlineStr"/>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>ka00198</t>
+        </is>
+      </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4594,7 +4807,11 @@
           <t>장중 투자자별 매매 상위</t>
         </is>
       </c>
-      <c r="F99" s="11" t="inlineStr"/>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>ka10065</t>
+        </is>
+      </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4635,7 +4852,11 @@
           <t>상하한가 순위</t>
         </is>
       </c>
-      <c r="F100" s="11" t="inlineStr"/>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>ka10017</t>
+        </is>
+      </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4680,7 +4901,11 @@
           <t>당일 주요 거래원</t>
         </is>
       </c>
-      <c r="F101" s="11" t="inlineStr"/>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>ka10040</t>
+        </is>
+      </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -4718,7 +4943,11 @@
           <t>고저가근접 순위</t>
         </is>
       </c>
-      <c r="F102" s="11" t="inlineStr"/>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>ka10018</t>
+        </is>
+      </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4762,7 +4991,11 @@
           <t>순매수 거래원 순위</t>
         </is>
       </c>
-      <c r="F103" s="11" t="inlineStr"/>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>ka10042</t>
+        </is>
+      </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -4805,7 +5038,11 @@
           <t>신고저가 순위</t>
         </is>
       </c>
-      <c r="F104" s="11" t="inlineStr"/>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>ka10016</t>
+        </is>
+      </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4851,7 +5088,11 @@
           <t>호가잔량 급증</t>
         </is>
       </c>
-      <c r="F105" s="11" t="inlineStr"/>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>ka10021</t>
+        </is>
+      </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4895,7 +5136,11 @@
           <t>호가잔량 상위</t>
         </is>
       </c>
-      <c r="F106" s="11" t="inlineStr"/>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>ka10020</t>
+        </is>
+      </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4938,7 +5183,11 @@
           <t>전일 거래량 상위</t>
         </is>
       </c>
-      <c r="F107" s="11" t="inlineStr"/>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>ka10031</t>
+        </is>
+      </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4980,7 +5229,11 @@
           <t>동일 순매매 순위</t>
         </is>
       </c>
-      <c r="F108" s="11" t="inlineStr"/>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>ka10062</t>
+        </is>
+      </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5024,7 +5277,11 @@
           <t>가격급등락 순위</t>
         </is>
       </c>
-      <c r="F109" s="11" t="inlineStr"/>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>ka10019</t>
+        </is>
+      </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5071,7 +5328,11 @@
           <t>당일 상위 이탈원</t>
         </is>
       </c>
-      <c r="F110" s="11" t="inlineStr"/>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>ka10053</t>
+        </is>
+      </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -5109,7 +5370,11 @@
           <t>당일 거래량 상위</t>
         </is>
       </c>
-      <c r="F111" s="11" t="inlineStr"/>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>ka10030</t>
+        </is>
+      </c>
       <c r="G111" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5155,7 +5420,11 @@
           <t>거래량 급증</t>
         </is>
       </c>
-      <c r="F112" s="11" t="inlineStr"/>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>ka10023</t>
+        </is>
+      </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5200,7 +5469,11 @@
           <t>업종 일봉 차트</t>
         </is>
       </c>
-      <c r="F113" s="11" t="inlineStr"/>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>ka20006</t>
+        </is>
+      </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
           <t>INDS_CD (필수)</t>
@@ -5238,7 +5511,11 @@
           <t>업종 분봉 차트</t>
         </is>
       </c>
-      <c r="F114" s="11" t="inlineStr"/>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>ka20005</t>
+        </is>
+      </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
           <t>INDS_CD (필수)</t>
@@ -5277,7 +5554,11 @@
           <t>업종 월봉 차트</t>
         </is>
       </c>
-      <c r="F115" s="11" t="inlineStr"/>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>ka20008</t>
+        </is>
+      </c>
       <c r="G115" s="10" t="inlineStr">
         <is>
           <t>INDS_CD (필수)</t>
@@ -5315,7 +5596,11 @@
           <t>업종 틱차트</t>
         </is>
       </c>
-      <c r="F116" s="11" t="inlineStr"/>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>ka20004</t>
+        </is>
+      </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
           <t>INDS_CD (필수)</t>
@@ -5353,7 +5638,11 @@
           <t>업종 주봉 차트</t>
         </is>
       </c>
-      <c r="F117" s="11" t="inlineStr"/>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>ka20007</t>
+        </is>
+      </c>
       <c r="G117" s="10" t="inlineStr">
         <is>
           <t>INDS_CD (필수)</t>
@@ -5391,7 +5680,11 @@
           <t>업종 년봉 차트</t>
         </is>
       </c>
-      <c r="F118" s="11" t="inlineStr"/>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>ka20019</t>
+        </is>
+      </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
           <t>INDS_CD (필수)</t>
@@ -5429,7 +5722,11 @@
           <t>업종코드 리스트</t>
         </is>
       </c>
-      <c r="F119" s="11" t="inlineStr"/>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>ka10101</t>
+        </is>
+      </c>
       <c r="G119" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5467,7 +5764,11 @@
           <t>업종 현재가 조회</t>
         </is>
       </c>
-      <c r="F120" s="11" t="inlineStr"/>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>ka20001</t>
+        </is>
+      </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
           <t>INDS_CD (필수)</t>
@@ -5505,7 +5806,11 @@
           <t>업종 현재가 일별</t>
         </is>
       </c>
-      <c r="F121" s="11" t="inlineStr"/>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>ka20009</t>
+        </is>
+      </c>
       <c r="G121" s="10" t="inlineStr">
         <is>
           <t>INDS_CD (필수)</t>
@@ -5543,7 +5848,11 @@
           <t>전업종 지수</t>
         </is>
       </c>
-      <c r="F122" s="11" t="inlineStr"/>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>ka20003</t>
+        </is>
+      </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5581,7 +5890,11 @@
           <t>업종별 투자자 순매수</t>
         </is>
       </c>
-      <c r="F123" s="11" t="inlineStr"/>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>ka10051</t>
+        </is>
+      </c>
       <c r="G123" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5622,7 +5935,11 @@
           <t>업종 프로그램매매</t>
         </is>
       </c>
-      <c r="F124" s="11" t="inlineStr"/>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>ka10010</t>
+        </is>
+      </c>
       <c r="G124" s="10" t="inlineStr">
         <is>
           <t>CODE (필수)</t>
@@ -5660,7 +5977,11 @@
           <t>업종별 주가</t>
         </is>
       </c>
-      <c r="F125" s="11" t="inlineStr"/>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>ka20002</t>
+        </is>
+      </c>
       <c r="G125" s="10" t="inlineStr">
         <is>
           <t>INDS_CD (필수)</t>
@@ -5699,7 +6020,11 @@
           <t>테마 그룹별 조회</t>
         </is>
       </c>
-      <c r="F126" s="11" t="inlineStr"/>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>ka90001</t>
+        </is>
+      </c>
       <c r="G126" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5742,7 +6067,11 @@
           <t>테마 구성종목 조회</t>
         </is>
       </c>
-      <c r="F127" s="11" t="inlineStr"/>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>ka90002</t>
+        </is>
+      </c>
       <c r="G127" s="10" t="inlineStr">
         <is>
           <t>THEME_CODE (필수)</t>
@@ -6777,7 +7106,7 @@
       <c r="H150" s="12" t="inlineStr">
         <is>
           <t>--price (주문가격 (생략 시 현재가로 예상비용 계산))
---type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] 기본:market (주문유형)
+--type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] (주문유형 (기본: --price 지정 시 limit, 미지정 시 market))
 --exchange [KRX, NXT] 기본:KRX (거래소)</t>
         </is>
       </c>

--- a/kiwoom_cli_commands.xlsx
+++ b/kiwoom_cli_commands.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="전체 명령어" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 명령어" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체 명령어'!$A$1:$H$232</definedName>
@@ -1930,7 +1930,8 @@
       <c r="H32" s="4" t="inlineStr">
         <is>
           <t>--raw (JSON 원본 출력)
---next-key (연속조회 커서 (이전 응답의 meta.cont.next_key))</t>
+--next-key (연속조회 커서 (이전 응답의 meta.cont.next_key))
+--confirm (주문성 API(매수/매도/정정/취소/환전) 확인 생략 (자동화용))</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6292,7 @@
       <c r="H132" s="12" t="inlineStr">
         <is>
           <t>--exchange [K] 기본:K (거래소 (K=KRX))
---confirm (확인 프롬프트 없이 주문 실행)</t>
+--confirm (확인 프롬프트 없이 조건검색 실시간 등록 실행)</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6337,7 @@
           <t>--exchange [K] 기본:K (거래소 (K=KRX))
 --cont-yn (연속조회여부)
 --next-key (연속조회키)
---confirm (확인 프롬프트 없이 주문 실행)</t>
+--confirm (확인 프롬프트 없이 조건검색 조회 실행)</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6379,7 @@
       </c>
       <c r="H134" s="12" t="inlineStr">
         <is>
-          <t>--confirm (확인 프롬프트 없이 주문 실행)</t>
+          <t>--confirm (확인 프롬프트 없이 조건검색 실시간 해제 실행)</t>
         </is>
       </c>
     </row>

--- a/kiwoom_cli_commands.xlsx
+++ b/kiwoom_cli_commands.xlsx
@@ -2565,11 +2565,11 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>--issuer 기본:000000000000 (발행사코드)
---vol-type (거래량구분)
---type 기본:1 (매매구분 (1=순매수, 2=순매도))
---period 기본:1 (기간 (1=전일,5,10,40,60))
---exclude-expired 기본:1 (거래종료ELW제외 (0=포함, 1=제외))</t>
+          <t>--issuer *필수 (발행사코드 3자리 (교보:001, 신한금융투자:002, 한국투자증권:003))
+--vol-type [all, 5k, 10k, 50k, 100k, 500k, 1000k] 기본:all (거래량구분 (all,5k,10k,50k,100k,500k,1000k))
+--type [net-buy, net-sell] 기본:net-buy (매매구분 (net-buy=순매수, net-sell=순매도))
+--period [previous, 5d, 10d, 40d, 60d] 기본:previous (기간 (previous=전일,5d,10d,40d,60d))
+--exclude-expired [include, exclude] 기본:exclude (거래종료ELW제외 (include=포함, exclude=제외))</t>
         </is>
       </c>
     </row>
@@ -4040,10 +4040,10 @@
       <c r="H82" s="10" t="inlineStr">
         <is>
           <t>--date *필수 (날짜 (YYYYMMDD))
---unit 기본:1 (금액/수량)
---market (시장구분)
---tick-type 기본:1 (분틱구분 (0=틱, 1=분))
---exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
+--unit [amount, quantity] 기본:amount (금액/수량)
+--market [kospi, kosdaq] 기본:kospi (시장구분)
+--tick-type [tick, minute] 기본:minute (분틱구분)
+--exchange [KRX, NXT, all] 기본:KRX (거래소 (KRX/NXT/all))</t>
         </is>
       </c>
     </row>
@@ -4172,10 +4172,10 @@
       <c r="H85" s="10" t="inlineStr">
         <is>
           <t>--date *필수 (날짜 (YYYYMMDD))
---unit 기본:1 (금액/수량 (1=금액백만원, 2=수량천주))
---market (시장구분)
---tick-type 기본:1 (분틱구분 (0=틱, 1=분))
---exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
+--unit [amount, quantity] 기본:amount (금액/수량)
+--market [kospi, kosdaq] 기본:kospi (시장구분)
+--tick-type [tick, minute] 기본:minute (분틱구분)
+--exchange [KRX, NXT, all] 기본:KRX (거래소 (KRX/NXT/all))</t>
         </is>
       </c>
     </row>
@@ -4265,8 +4265,8 @@
       <c r="H87" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---include-managed (관리종목포함 (0=미포함, 1=포함))
---exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
+--include-managed [no, yes] 기본:no (관리종목포함 (no=미포함, yes=포함))
+--exchange [KRX, NXT, all] 기본:KRX (거래소 (KRX/NXT/all))</t>
         </is>
       </c>
     </row>
@@ -4355,10 +4355,10 @@
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>--type 기본:1 (조회구분 (1=순매도순위, 2=순매수순위))
+          <t>--type [net-sell, net-buy] 기본:net-sell (조회구분 (net-sell=순매도순위, net-buy=순매수순위))
 --from (시작일자 (YYYYMMDD))
 --to (종료일자 (YYYYMMDD))
---period 기본:1 (기간 (1=전일,4=5일,9=10일,19=20일,39=40일,59=60일,119=120일))</t>
+--period [previous, 5d, 10d, 20d, 40d, 60d, 120d] (기간 (previous=전일,5d,10d,20d,40d,60d,120d — --from/--to와 동시 사용 불가))</t>
         </is>
       </c>
     </row>
@@ -5422,13 +5422,13 @@
       <c r="H112" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---sort 기본:1 (정렬 (1=거래량,2=거래회전율,3=거래대금))
---include-managed (관리종목포함 (0=미포함, 1=포함))
---credit-type (신용구분)
---vol-type (거래량구분)
---price-type (가격구분)
---amount-type (거래대금구분)
---session (장운영구분 (0=전체,1=장중,2=장전시간외,3=장후시간외))
+--sort [volume, turnover, amount] 기본:volume (정렬 (volume=거래량,turnover=거래회전율,amount=거래대금))
+--stock-condition [include-managed, exclude-managed, exclude-preferred, exclude-liquidation, exclude-managed-preferred, exclude-margin-100, only-margin-100, only-margin-60, only-margin-50, only-margin-40, only-margin-30, only-margin-20, exclude-etf, exclude-spac, exclude-etf-etn] 기본:include-managed (종목조건 (include-managed=관리종목포함, exclude-managed=관리종목미포함, exclude-preferred/exclude-liquidation/exclude-managed-preferred/exclude-margin-100/only-margin-100/only-margin-60/only-margin-50/only-margin-40/only-margin-30/only-margin-20/exclude-etf/exclude-spac/exclude-etf-etn))
+--credit-type [all, all-financing, a, b, c, d, short] 기본:all (신용구분 (all,all-financing,a,b,c,d,short))
+--vol-type [all, 5k, 10k, 50k, 100k, 200k, 300k, 500k, 1000k] 기본:all (거래량구분 (all,5k,10k,50k,100k,200k,300k,500k,1000k = 이상))
+--price-type [all, under-1k, over-1k, 1k-2k, 2k-5k, over-5k, 5k-10k, under-10k, over-10k, over-50k, over-100k] 기본:all (가격구분 (all,under-1k,over-1k,1k-2k,2k-5k,over-5k,5k-10k,under-10k,over-10k,over-50k,over-100k))
+--amount-type [all, 10m, 30m, 50m, 100m, 300m, 500m, 1b, 3b, 5b, 10b, 30b, 50b] 기본:all (거래대금구분 (all,10m,30m,50m,100m,300m,500m,1b,3b,5b,10b,30b,50b = 이상))
+--session [all, regular, pre-open, after-hours] 기본:all (장운영구분 (all=전체,regular=장중,pre-open=장전시간외,after-hours=장후시간외))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -6658,8 +6658,8 @@
       </c>
       <c r="H140" s="12" t="inlineStr">
         <is>
-          <t>--price (주문가격 (시장가 주문시 생략))
---type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] (주문유형 (기본: --price 지정 시 limit, 미지정 시 market))
+          <t>--price (주문가격 (금현물은 전체 유형이 지정가 계열이라 필수))
+--type [limit, ioc, fok] (주문유형 (limit=보통, ioc=보통(IOC), fok=보통(FOK); 시장가 없음, 기본 limit))
 --confirm (확인 프롬프트 없이 주문 실행)
 --dry-run (전송될 내용만 출력하고 주문을 전송하지 않음)
 --client-order-id (멱등성 키 (같은 키 재실행 시 재전송 없이 이전 응답 반환))</t>
@@ -7008,8 +7008,8 @@
       </c>
       <c r="H148" s="12" t="inlineStr">
         <is>
-          <t>--price (주문가격 (시장가 주문시 생략))
---type [limit, market, conditional, after-hours, pre-market, single, best, first, ioc, market-ioc, best-ioc, fok, market-fok, best-fok, stop, mid, mid-ioc, mid-fok] (주문유형 (기본: --price 지정 시 limit, 미지정 시 market))
+          <t>--price (주문가격 (금현물은 전체 유형이 지정가 계열이라 필수))
+--type [limit, ioc, fok] (주문유형 (limit=보통, ioc=보통(IOC), fok=보통(FOK); 시장가 없음, 기본 limit))
 --confirm (확인 프롬프트 없이 주문 실행)
 --dry-run (전송될 내용만 출력하고 주문을 전송하지 않음)
 --client-order-id (멱등성 키 (같은 키 재실행 시 재전송 없이 이전 응답 반환))</t>
@@ -7506,11 +7506,11 @@
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
---date-type [0, 1] (조회구분 (0=기간, 1=일자))
---pot [0, 1] (당일/전일 (0=당일, 1=전일))
---days [5, 10, 20, 40, 60, 120] 기본:20 (기간 (5/10/20/40/60/120일))
---sort [1, 2] 기본:2 (정렬기준 (1=종가순, 2=날짜순))
---broker (회원사코드)
+--date-type [period, start-end] 기본:start-end (조회기간구분 (period=기간으로 조회, start-end=시작일자·종료일자로 조회))
+--pot [today, previous] 기본:today (시점구분 (today=당일, previous=전일))
+--days [5d, 10d, 20d, 40d, 60d, 120d] 기본:20d (기간 (5d/10d/20d/40d/60d/120d))
+--sort [close, date] 기본:date (정렬기준 (close=종가순, date=날짜순))
+--broker *필수 (회원사코드 (조회: kiwoom stock brokers))
 --exchange [KRX, NXT, all] 기본:all (거래소구분 (KRX/NXT/all))</t>
         </is>
       </c>
@@ -8114,7 +8114,9 @@
       </c>
       <c r="H173" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>--market [all, kospi, kosdaq] 기본:all (시장거래구분 (all=전체, kospi=코스피, kosdaq=코스닥))
+--grade [all, a, b, c, d, e] 기본:all (신용종목등급구분 (all=전체, a~e=A~E군))
+--code (종목코드 (미지정 시 전체))</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8153,7 @@
       </c>
       <c r="G174" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CODE (필수)</t>
         </is>
       </c>
       <c r="H174" s="14" t="inlineStr">
@@ -8226,7 +8228,7 @@
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>일/주/월별 시세 조회</t>
+          <t>일별 시세 조회</t>
         </is>
       </c>
       <c r="F176" s="15" t="inlineStr">
@@ -8241,7 +8243,7 @@
       </c>
       <c r="H176" s="14" t="inlineStr">
         <is>
-          <t>--type [day, week, month] 기본:day (조회 구분 (day/week/month))</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8574,9 +8576,9 @@
       </c>
       <c r="H184" s="14" t="inlineStr">
         <is>
-          <t>--market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
---amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
---trade [1, 2] 기본:2 (매매구분 (1=순매도, 2=순매수))
+          <t>--market [all, kospi, kosdaq] 기본:kospi (시장구분 (all=전체, kospi=코스피, kosdaq=코스닥))
+--amount-qty [amount, quantity] 기본:amount (금액수량구분 (amount=금액, quantity=수량))
+--trade [net-buy, buy, sell] 기본:net-buy (매매구분 (net-buy=순매수, buy=매수, sell=매도))
 --exchange [KRX, NXT, all] 기본:all (거래소구분 (KRX/NXT/all))</t>
         </is>
       </c>
@@ -8710,13 +8712,13 @@
       </c>
       <c r="H187" s="14" t="inlineStr">
         <is>
-          <t>--period 기본:5 (기간 (일수))
---from (시작일자 (YYYYMMDD, 선택))
---to (종료일자 (YYYYMMDD, 선택))
+          <t>--period [recent, 3d, 5d, 10d, 20d, 120d, range] 기본:5d (기간 (recent=최근일, 3d/5d/10d/20d/120d, range=시작/종료일자로 조회))
+--from (시작일자 (YYYYMMDD, --period range일 때 사용))
+--to (종료일자 (YYYYMMDD, --period range일 때 사용))
 --market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
---net-type 기본:2 (순매수구분 (2=순매수))
---stock-sector [0, 1] (종목/업종 (0=종목, 1=업종))
---amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
+--net-type [net-buy] 기본:net-buy (순매수구분 (net-buy=순매수, 스펙상 고정값))
+--stock-sector [stock, sector] 기본:stock (종목/업종구분 (stock=종목, sector=업종))
+--amount-qty [amount, quantity] 기본:amount (금액수량구분 (amount=금액, quantity=수량))
 --exchange [KRX, NXT, all] 기본:all (거래소구분 (KRX/NXT/all))</t>
         </is>
       </c>
@@ -8852,11 +8854,11 @@
       </c>
       <c r="H190" s="14" t="inlineStr">
         <is>
-          <t>--market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
---amount-qty 기본:1 (금액수량구분 (1=금액&amp;수량))
---investor-type 기본:1000 (투자자별)
---foreign-all [0, 1] (외국계전체 (0/1))
---simultaneous [0, 1] (동시순매수구분 (0/1))
+          <t>--market [all, kospi, kosdaq] 기본:kospi (시장구분 (all=전체, kospi=코스피, kosdaq=코스닥))
+--amount-qty [combined] 기본:combined (금액수량구분 (combined=금액&amp;수량, 스펙상 고정값))
+--investor-type [foreign, institution, investment-trust, insurance, bank, pension, state, other-corporate] 기본:foreign (투자자별 (foreign=외국인, institution=기관계, investment-trust=투신, insurance=보험, bank=은행, pension=연기금, state=국가, other-corporate=기타법인))
+--foreign-all [yes, no] 기본:no (외국계전체 (yes=체크, no=미체크))
+--simultaneous [yes, no] 기본:no (동시순매수구분 (yes=체크, no=미체크))
 --exchange [KRX, NXT, all] 기본:all (거래소구분 (KRX/NXT/all))</t>
         </is>
       </c>

--- a/kiwoom_cli_commands.xlsx
+++ b/kiwoom_cli_commands.xlsx
@@ -937,7 +937,7 @@
 --currency (통화코드 (국내 전용))
 --product [all, stock] 기본:all (상품구분 (all=전체, stock=국내주식; 국내 전용))
 --foreign-exchange (해외거래소코드 (국내 전용))
---exchange [%, KRX, NXT] 기본:% (국내 거래소구분 (%=전체))</t>
+--exchange [all, KRX, NXT] 기본:all (국내 거래소구분 (all=전체, SOR 없음))</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
 --side [all, sell, buy] 기본:all (매도수구분 (all=전체, sell=매도, buy=매수))
 --code (종목코드)
 --from-order (시작주문번호)
---exchange [%, KRX, NXT, SOR] 기본:% (거래소구분 (%=전체))</t>
+--exchange [all, KRX, NXT, SOR] 기본:all (거래소구분 (all=전체))</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
 --qry-type [all, filled] 기본:all (조회구분 (all=전체, filled=체결))
 --code (종목코드)
 --from-order (시작주문번호)
---exchange [%, KRX, NXT, SOR] 기본:% (거래소구분 (%=전체))</t>
+--exchange [all, KRX, NXT, SOR] 기본:all (거래소구분 (all=전체))</t>
         </is>
       </c>
     </row>
@@ -2521,9 +2521,9 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>--sort 기본:1 (정렬 (1=순매수잔량상위, 2=순매도잔량상위))
---right-type 기본:000 (권리구분 (000=전체))
---exclude-expired 기본:1 (거래종료제외 (0=포함, 1=제외))</t>
+          <t>--sort [buy-balance, sell-balance] 기본:buy-balance (정렬 (buy-balance=순매수잔량상위, sell-balance=순매도잔량상위))
+--right-type [all, call, put, dc, dp, early-call, early-put] 기본:all (권리구분 (all,call,put,dc,dp,early-call,early-put))
+--exclude-expired [include, exclude] 기본:exclude (거래종료제외 (include=포함, exclude=제외))</t>
         </is>
       </c>
     </row>
@@ -2611,9 +2611,9 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>--sort 기본:1 (정렬 (1=상승률,2=상승폭,3=하락률,4=하락폭))
---right-type 기본:000 (권리구분 (000=전체))
---exclude-expired 기본:1 (거래종료제외 (0=포함, 1=제외))</t>
+          <t>--sort [rise-rate, rise-price, fall-rate, fall-price] 기본:rise-rate (정렬 (rise-rate=상승률,rise-price=상승폭,fall-rate=하락률,fall-price=하락폭))
+--right-type [all, call, put, dc, dp, early-call, early-put] 기본:all (권리구분 (all,call,put,dc,dp,early-call,early-put))
+--exclude-expired [include, exclude] 기본:exclude (거래종료제외 (include=포함, exclude=제외))</t>
         </is>
       </c>
     </row>
@@ -2699,9 +2699,9 @@
         <is>
           <t>--issuer 기본:000000000000 (발행사코드)
 --underlying 기본:000000000000 (기초자산코드)
---right-type 기본:000 (권리구분)
+--right-type [all, call, put, dc, dp, ex, early-call, early-put] 기본:all (권리구분 (all,call,put,dc,dp,ex,early-call,early-put))
 --lp 기본:000000000000 (LP코드)
---exclude-expired 기본:1 (거래종료ELW제외 (0=포함, 1=제외))</t>
+--exclude-expired [include, exclude] 기본:exclude (거래종료ELW제외 (include=포함, exclude=제외))</t>
         </is>
       </c>
     </row>
@@ -2829,9 +2829,9 @@
         <is>
           <t>--issuer 기본:000000000000 (발행사코드)
 --underlying 기본:000000000000 (기초자산코드)
---right-type (권리구분 (0~7))
+--right-type [all, call, put, dc, dp, ex, early-call, early-put] 기본:all (권리구분 (all,call,put,dc,dp,ex,early-call,early-put))
 --lp 기본:000000000000 (LP코드)
---sort (정렬 (0~7))</t>
+--sort [none, rise-rate, rise-price, fall-rate, fall-price, volume, amount, days-left] 기본:none (정렬 (none,rise-rate,rise-price,fall-rate,fall-price,volume,amount,days-left))</t>
         </is>
       </c>
     </row>
@@ -2957,15 +2957,15 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>--type 기본:1 (등락구분 (1=급등, 2=급락))
---time-type 기본:1 (시간구분 (1=분전, 2=일전))
+          <t>--type [rise, fall] 기본:rise (등락구분 (rise=급등, fall=급락))
+--time-type [minute, day] 기본:minute (시간구분 (minute=분전, day=일전))
 --time 기본:5 (시간)
---vol-type (거래량구분 (0=전체))
+--vol-type [all, 10k, 50k, 100k, 300k, 500k, 1000k] 기본:all (거래량구분 (all,10k,50k,100k,300k,500k,1000k = 이상))
 --issuer 기본:000000000000 (발행사코드 (000000000000=전체))
 --underlying 기본:000000000000 (기초자산코드 (000000000000=전체))
---right-type 기본:000 (권리구분 (000=전체))
+--right-type [all, call, put, dc, dp, ex, early-call, early-put] 기본:all (권리구분 (all,call,put,dc,dp,ex,early-call,early-put))
 --lp 기본:000000000000 (LP코드 (000000000000=전체))
---exclude-expired 기본:1 (거래종료ELW제외 (0=포함, 1=제외))</t>
+--exclude-expired [include, exclude] 기본:exclude (거래종료ELW제외 (include=포함, exclude=제외))</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>--tax-type (과세유형 (0=전체))
---nav (NAV대비 (0=전체))
+          <t>--tax-type [all, tax-free, holding-tax, company, foreign, foreign-tax-free] 기본:all (과세유형 (all,tax-free,holding-tax,company,foreign,foreign-tax-free))
+--nav [all, nav-gt-close, nav-lt-close] 기본:all (NAV대비 (all,nav-gt-close=NAV&gt;전일종가,nav-lt-close=NAV&lt;전일종가))
 --company 기본:0000 (운용사 (0000=전체))
---taxable (과세여부 (0=전체))
+--taxable [all, taxable, tax-free] 기본:all (과세여부 (all,taxable,tax-free))
 --index (추적지수 (0=전체))
---exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
+--exchange [KRX, NXT, all] 기본:KRX (거래소 (KRX/NXT/all))</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       <c r="H62" s="10" t="inlineStr">
         <is>
           <t>--index (ETF대상지수코드)
---period (기간 (0=1주,1=1달,2=6개월,3=1년))</t>
+--period [week, month, six-months, year] 기본:week (기간 (week=1주,month=1달,six-months=6개월,year=1년))</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
         <is>
           <t>--code 기본:M04020000 (종목코드)
 --date *필수 (기준일자 (YYYYMMDD))
---price-type (수정주가구분)</t>
+--price-type [raw, adjusted] 기본:raw (수정주가구분 (raw=원본, adjusted=수정주가))</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
         <is>
           <t>--code 기본:M04020000 (종목코드)
 --date *필수 (기준일자 (YYYYMMDD))
---price-type (수정주가구분)</t>
+--price-type [raw, adjusted] 기본:raw (수정주가구분 (raw=원본, adjusted=수정주가))</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
         <is>
           <t>--code 기본:M04020000 (종목코드)
 --scope 기본:1 (틱범위 (1,3,5,10,30))
---price-type (수정주가구분)</t>
+--price-type [raw, adjusted] 기본:raw (수정주가구분 (raw=원본, adjusted=수정주가))</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
         <is>
           <t>--code 기본:M04020000 (종목코드)
 --date *필수 (기준일자 (YYYYMMDD))
---price-type (수정주가구분)</t>
+--price-type [raw, adjusted] 기본:raw (수정주가구분 (raw=원본, adjusted=수정주가))</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3952,7 @@
       <c r="H80" s="10" t="inlineStr">
         <is>
           <t>--date *필수 (날짜 (YYYYMMDD))
---exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
+--exchange [KRX, NXT, all] 기본:KRX (거래소 (KRX/NXT/all))</t>
         </is>
       </c>
     </row>
@@ -3995,9 +3995,9 @@
       <c r="H81" s="10" t="inlineStr">
         <is>
           <t>--date *필수 (날짜 (YYYYMMDD))
---unit 기본:1 (금액/수량)
+--unit [amount, quantity] 기본:amount (금액/수량)
 --market [kospi, kosdaq] 기본:kospi (시장구분)
---exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
+--exchange [KRX, NXT, all] 기본:KRX (거래소 (KRX/NXT/all))</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>--unit 기본:1 (금액/수량)
+          <t>--unit [amount, quantity] 기본:amount (금액/수량)
 --date (날짜 (YYYYMMDD))</t>
         </is>
       </c>
@@ -4218,11 +4218,11 @@
       <c r="H86" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---sort 기본:1 (정렬 (1=상승률,2=상승폭,3=하락률,4=하락폭,5=보합))
---stk-cnd (종목조건)
---vol-cnd (거래량조건)
---credit (신용조건)
---amount (거래대금)</t>
+--sort [rise-rate, rise-price, fall-rate, fall-price, flat] 기본:rise-rate (정렬 (rise-rate=상승률, rise-price=상승폭, fall-rate=하락률, fall-price=하락폭, flat=보합))
+--stock-cond [all, exclude-managed, exclude-liquidation, exclude-preferred, exclude-managed-preferred, exclude-margin-100, only-margin-100, only-margin-50, only-margin-60, only-margin-40, only-margin-30, only-margin-20, exclude-etf, exclude-spac, exclude-etf-etn, exclude-etn] 기본:all (종목조건 (all,exclude-managed,exclude-liquidation,exclude-preferred,exclude-managed-preferred,exclude-margin-100,only-margin-100,only-margin-50,only-margin-60,only-margin-40,only-margin-30,only-margin-20,exclude-etf,exclude-spac,exclude-etf-etn,exclude-etn))
+--volume-cond [all, 100+, 500+, 1k+, 5k+, 10k+, 50k+, 100k+] 기본:all (거래량조건 (all,100+,500+,1k+,5k+,10k+,50k+,100k+))
+--credit [all, a, b, c, d, exclude-overlimit, e, short, all-financing] 기본:all (신용조건 (all,a,b,c,d,exclude-overlimit,e,short,all-financing))
+--amount [all, 5m, 10m, 30m, 50m, 100m, 300m, 500m, 1b, 3b, 5b, 10b] 기본:all (거래대금 (all,5m,10m,30m,50m,100m,300m,500m,1b,3b,5b,10b))</t>
         </is>
       </c>
     </row>
@@ -4309,10 +4309,10 @@
       <c r="H88" s="10" t="inlineStr">
         <is>
           <t>--market [kospi, kosdaq] 기본:kospi (시장구분)
---type 기본:1 (비율구분 (1=매수/매도비율, 2=매도/매수비율))
+--type [buy-to-sell, sell-to-buy] 기본:buy-to-sell (비율구분 (buy-to-sell=매수/매도비율, sell-to-buy=매도/매수비율))
 --minutes 기본:5 (분 입력)
---vol-type (거래량구분)
---stk-cnd (종목조건)
+--vol-type [5k, 10k, 50k, 100k] 기본:5k (거래량구분 (5k,10k,50k,100k — 전체 없음))
+--stock-cond [all, exclude-managed, exclude-margin-100, only-margin-100, only-margin-40, only-margin-30, only-margin-20] 기본:all (종목조건 (all,exclude-managed,exclude-margin-100,only-margin-100,only-margin-40,only-margin-30,only-margin-20))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -4400,9 +4400,9 @@
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>--vol-type (거래량구분)
---type 기본:1 (매매구분 (1=순매수, 2=순매도))
---period 기본:1 (기간 (1=전일,5,10,60))
+          <t>--vol-type [all, 5k, 10k, 50k, 100k, 500k, 1000k] 기본:all (거래량구분 (all,5k,10k,50k,100k,500k,1000k))
+--type [net-buy, net-sell] 기본:net-buy (매매구분 (net-buy=순매수, net-sell=순매도))
+--period [today, previous, 5d, 10d, 60d] 기본:previous (기간 (today,previous,5d,10d,60d))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -4446,13 +4446,13 @@
       <c r="H91" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---sort 기본:1 (정렬 (1=상승률,2=상승폭,3=하락률,4=하락폭,5=보합))
---vol-cnd (거래량조건)
---stk-cnd (종목조건)
---credit (신용조건)
---include-limit (상하한포함 (0=미포함, 1=포함))
---price-cnd (가격조건)
---amount-cnd (거래대금조건)
+--sort [rise-rate, rise-price, fall-rate, fall-price, flat] 기본:rise-rate (정렬 (rise-rate,rise-price,fall-rate,fall-price,flat))
+--volume-cond [all, 10k, 50k, 100k, 150k, 200k, 300k, 500k, 1000k] 기본:all (거래량조건 (all,10k,50k,100k,150k,200k,300k,500k,1000k))
+--stock-cond [all, exclude-managed, exclude-preferred, exclude-managed-preferred, exclude-margin-100, only-margin-100, only-margin-40, only-margin-30, only-margin-20, exclude-liquidation, only-margin-50, only-margin-60, exclude-etf, exclude-spac, exclude-etf-etn] 기본:all (종목조건 (all,exclude-managed,exclude-preferred,exclude-managed-preferred,exclude-margin-100,only-margin-100,only-margin-40,only-margin-30,only-margin-20,exclude-liquidation,only-margin-50,only-margin-60,exclude-etf,exclude-spac,exclude-etf-etn))
+--credit [all, a, b, c, d, e, all-financing] 기본:all (신용조건 (all,a,b,c,d,e,all-financing))
+--include-limit [yes, no] 기본:no (상하한포함 (yes,no))
+--price-cond [all, under-1k, 1k-2k, 2k-5k, 5k-10k, over-10k, over-1k, under-10k] 기본:all (가격조건 (all,under-1k,1k-2k,2k-5k,5k-10k,over-10k,over-1k,under-10k))
+--amount-cond [all, 30m, 50m, 100m, 300m, 500m, 1b, 3b, 5b, 10b, 30b, 50b] 기본:all (거래대금조건 (all,30m,50m,100m,300m,500m,1b,3b,5b,10b,30b,50b = 이상))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -4496,10 +4496,10 @@
       <c r="H92" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---vol-type (거래량구분)
---stk-cnd (종목조건)
---include-limit (상하한포함)
---credit (신용조건)
+--vol-type [all, 10k, 50k, 100k, 200k, 300k, 500k, 1000k] 기본:all (거래량구분 (all,10k,50k,100k,200k,300k,500k,1000k))
+--stock-cond [all, exclude-managed, exclude-margin-100, only-margin-100, only-margin-40, only-margin-30, only-margin-20] 기본:all (종목조건 (all,exclude-managed,exclude-margin-100,only-margin-100,only-margin-40,only-margin-30,only-margin-20))
+--include-limit [yes, no] 기본:no (상하한포함 (yes,no))
+--credit [all, a, b, c, d, e, all-financing] 기본:all (신용조건 (all,a,b,c,d,e,all-financing))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -4543,11 +4543,11 @@
       <c r="H93" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---sort 기본:1 (정렬 (1=상승률,2=상승폭,3=보합,4=하락률,5=하락폭,6=체결량,7=상한,8=하한))
---vol-cnd (거래량조건)
---stk-cnd (종목조건)
---credit (신용조건)
---price-cnd (가격조건)
+--sort [rise-rate, rise-price, flat, fall-rate, fall-price, volume, upper-limit, lower-limit] 기본:rise-rate (정렬 (rise-rate,rise-price,flat,fall-rate,fall-price,volume,upper-limit,lower-limit))
+--volume-cond [all, 1k, 3k, 5k, 10k, 50k, 100k] 기본:all (거래량조건 (all,1k,3k,5k,10k,50k,100k))
+--stock-cond [all, exclude-managed, exclude-preferred, exclude-managed-preferred, exclude-margin-100, only-margin-100, only-margin-40, only-margin-30, only-margin-20, exclude-liquidation, only-margin-50, only-margin-60, exclude-etf, exclude-spac, exclude-etf-etn] 기본:all (종목조건 (all,exclude-managed,exclude-preferred,exclude-managed-preferred,exclude-margin-100,only-margin-100,only-margin-40,only-margin-30,only-margin-20,exclude-liquidation,only-margin-50,only-margin-60,exclude-etf,exclude-spac,exclude-etf-etn))
+--credit [all, a, b, c, d, exclude-overlimit, e, short, all-financing] 기본:all (신용조건 (all,a,b,c,d,exclude-overlimit,e,short,all-financing))
+--price-cond [all, under-1k, 1k-2k, 2k-5k, 5k-10k, over-10k, over-1k, under-10k] 기본:all (가격조건 (all,under-1k,1k-2k,2k-5k,5k-10k,over-10k,over-1k,under-10k))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -4591,9 +4591,9 @@
       <c r="H94" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---period (기간)
---type 기본:1 (매매구분 (1=순매수,2=순매도,3=매수,4=매도))
---sort 기본:1 (정렬 (1=금액, 2=수량))
+--period [today, previous, 5d, 10d, 20d, 60d] 기본:today (기간 (today,previous,5d,10d,20d,60d))
+--type [net-buy, net-sell, buy, sell] 기본:net-buy (매매구분 (net-buy=순매수,net-sell=순매도,buy=매수,sell=매도))
+--sort [amount, quantity] 기본:amount (정렬 (amount=금액, quantity=수량))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -4637,8 +4637,8 @@
       <c r="H95" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---type 기본:2 (구분 (1=연속순매도, 2=연속순매수))
---base-date (기준일구분 (0=당일, 1=전일))
+--type [net-sell, net-buy] 기본:net-buy (구분 (net-sell=연속순매도, net-buy=연속순매수))
+--base-date [today, previous] 기본:today (기준일구분 (today=당일, previous=전일))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -4682,7 +4682,7 @@
       <c r="H96" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---period (기간 (0=당일,1=전일,5=5일,10,20,60))
+--period [today, previous, 5d, 10d, 20d, 60d] 기본:today (기간 (today,previous,5d,10d,20d,60d))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -4726,8 +4726,8 @@
       <c r="H97" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---unit 기본:1 (금액/수량 (1=금액, 2=수량))
---date-type (날짜포함구분 (0=미포함, 1=포함))
+--unit [amount, quantity] 기본:amount (금액/수량 (amount=금액, quantity=수량))
+--date-type [yes, no] 기본:no (날짜포함구분 (no=미포함, yes=포함))
 --date (날짜 (YYYYMMDD))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
@@ -4772,8 +4772,8 @@
       <c r="H98" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---type 기본:2 (매매구분 (1=순매도, 2=순매수, 3=순매매))
---period (기간 (0=당일,1=전일,5=5일,10,20,60))
+--type [net-sell, net-buy, net-trade] 기본:net-buy (매매구분 (net-sell=순매도, net-buy=순매수, net-trade=순매매))
+--period [today, previous, 5d, 10d, 20d, 60d] 기본:today (기간 (today,previous,5d,10d,20d,60d))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -4858,10 +4858,10 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>--type 기본:1 (매매구분 (1=순매수, 2=순매도))
+          <t>--type [net-buy, net-sell] 기본:net-buy (매매구분 (net-buy=순매수, net-sell=순매도))
 --market [all, kospi, kosdaq] 기본:all (시장구분)
---investor 기본:9000 (기관구분 (9000=외국인, 9999=기관계 등))
---unit 기본:1 (구분 (1=금액, 2=수량))</t>
+--investor [foreign, foreign-broker, financial-investment, investment-trust, other-financial, bank, insurance, pension, state, other-corporate, institution] 기본:foreign (기관구분 (foreign=외국인, foreign-broker=외국계, financial-investment=금융투자, investment-trust=투신, other-financial=기타금융, bank=은행, insurance=보험, pension=연기금, state=국가, other-corporate=기타법인, institution=기관계))
+--unit [amount, quantity] 기본:amount (구분 (amount=금액, quantity=수량))</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       <c r="H101" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---type 기본:1 (상하한구분 (1=상한,2=상승,3=보합,4=하한,5=하락,6=전일상한,7=전일하한))
---sort 기본:2 (정렬 (1=종목코드순,2=연속횟수순,3=등락률순))
---stk-cnd (종목조건)
---vol-type (거래량구분)
---credit (신용조건)
---trade-gold (매매금구분)
+--type [upper, rise, flat, lower, fall, prev-upper, prev-lower] 기본:upper (상하한구분 (upper,rise,flat,lower,fall,prev-upper,prev-lower))
+--sort [code, count, change-rate] 기본:count (정렬 (code=종목코드순,count=연속횟수순,change-rate=등락률순))
+--stock-cond [all, exclude-managed, exclude-preferred, exclude-managed-preferred, exclude-margin-100, only-margin-100, only-margin-40, only-margin-30, only-margin-20, exclude-managed-preferred-alert] 기본:all (종목조건 (all,exclude-managed,exclude-preferred,exclude-managed-preferred,exclude-margin-100,only-margin-100,only-margin-40,only-margin-30,only-margin-20,exclude-managed-preferred-alert))
+--vol-type [all, 10k, 50k, 100k, 150k, 200k, 300k, 500k, 1000k] 기본:all (거래량구분 (all,10k,50k,100k,150k,200k,300k,500k,1000k))
+--credit [all, a, b, c, d, e, all-financing] 기본:all (신용조건 (all,a,b,c,d,e,all-financing))
+--trade-gold [all, under-1k, 1k-2k, 2k-3k, 5k-10k, over-10k, over-1k] 기본:all (매매금구분 (all,under-1k,1k-2k,2k-3k,5k-10k,over-10k,over-1k))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -4994,12 +4994,12 @@
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>--type 기본:1 (구분 (1=고가, 2=저가))
+          <t>--type [high, low] 기본:high (구분 (high=고가, low=저가))
 --rate 기본:05 (근접율 (05,10,15,20,25,30))
 --market [all, kospi, kosdaq] 기본:all (시장구분)
---vol-type (거래량구분)
---stk-cnd (종목조건)
---credit (신용조건)
+--vol-type [all, 10k, 50k, 100k, 150k, 200k, 300k, 500k, 1000k] 기본:all (거래량구분 (all,10k,50k,100k,150k,200k,300k,500k,1000k))
+--stock-cond [all, exclude-managed, exclude-preferred, exclude-margin-100, only-margin-100, only-margin-40, only-margin-30] 기본:all (종목조건 (all,exclude-managed,exclude-preferred,exclude-margin-100,only-margin-100,only-margin-40,only-margin-30))
+--credit [all, a, b, c, d, e, all-financing] 기본:all (신용조건 (all,a,b,c,d,e,all-financing))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -5044,10 +5044,10 @@
         <is>
           <t>--from (시작일자 (YYYYMMDD))
 --to (종료일자 (YYYYMMDD))
---date-type (조회일자구분 (0=기간, 1=일자))
---pot-type (구분 (0=당일, 1=전일))
---period 기본:5 (기간 (5,10,20,40,60,120))
---sort 기본:1 (정렬기준 (1=종가순, 2=날짜순))</t>
+--date-type [period, start-end] 기본:period (조회기간구분 (period=기간으로 조회, start-end=시작일자·종료일자로 조회))
+--pot-type [today, previous] 기본:today (시점구분 (today=당일, previous=전일))
+--period [5d, 10d, 20d, 40d, 60d, 120d] 기본:5d (기간 (5d/10d/20d/40d/60d/120d))
+--sort [close, date] 기본:close (정렬기준 (close=종가순, date=날짜순))</t>
         </is>
       </c>
     </row>
@@ -5090,13 +5090,13 @@
       <c r="H105" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---type 기본:1 (신고저구분 (1=신고가, 2=신저가))
---basis 기본:1 (기준 (1=고저기준, 2=종가기준))
+--type [new-high, new-low] 기본:new-high (신고저구분 (new-high=신고가, new-low=신저가))
+--basis [high-low, close] 기본:high-low (기준 (high-low=고저기준, close=종가기준))
 --period 기본:5 (기간 (5,10,20,60,250))
---stk-cnd (종목조건 (0=전체))
---vol-type (거래량구분)
---credit (신용조건)
---include-limit (상하한포함 (0=미포함, 1=포함))
+--stock-cond [all, exclude-managed, exclude-preferred, exclude-margin-100, only-margin-100, only-margin-40, only-margin-30] 기본:all (종목조건 (all,exclude-managed,exclude-preferred,exclude-margin-100,only-margin-100,only-margin-40,only-margin-30))
+--vol-type [all, 10k, 50k, 100k, 150k, 200k, 300k, 500k, 1000k] 기본:all (거래량구분 (all,10k,50k,100k,150k,200k,300k,500k,1000k))
+--credit [all, a, b, c, d, e, all-financing] 기본:all (신용조건 (all,a,b,c,d,e,all-financing))
+--include-limit [yes, no] 기본:no (상하한포함 (yes,no))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -5140,11 +5140,11 @@
       <c r="H106" s="10" t="inlineStr">
         <is>
           <t>--market [kospi, kosdaq] 기본:kospi (시장구분)
---type 기본:1 (매매구분 (1=매수잔량, 2=매도잔량))
---sort 기본:1 (정렬 (1=급증량, 2=급증률))
+--type [buy-balance, sell-balance] 기본:buy-balance (매매구분 (buy-balance=매수잔량, sell-balance=매도잔량))
+--sort [spike-quantity, spike-rate] 기본:spike-quantity (정렬 (spike-quantity=급증량, spike-rate=급증률))
 --minutes 기본:5 (분 입력)
---vol-type (거래량구분)
---stk-cnd (종목조건)
+--vol-type [1k, 5k, 10k, 50k, 100k] 기본:1k (거래량구분 (1k,5k,10k,50k,100k — 전체 없음))
+--stock-cond [all, exclude-managed, exclude-margin-100, only-margin-100, only-margin-40, only-margin-30, only-margin-20] 기본:all (종목조건 (all,exclude-managed,exclude-margin-100,only-margin-100,only-margin-40,only-margin-30,only-margin-20))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -5188,10 +5188,10 @@
       <c r="H107" s="10" t="inlineStr">
         <is>
           <t>--market [kospi, kosdaq] 기본:kospi (시장구분)
---sort 기본:1 (정렬 (1=순매수잔량순,2=순매도잔량순,3=매수비율순,4=매도비율순))
---vol-type (거래량구분)
---stk-cnd (종목조건)
---credit (신용조건)
+--sort [net-buy-balance, net-sell-balance, buy-ratio, sell-ratio] 기본:net-buy-balance (정렬 (net-buy-balance,net-sell-balance,buy-ratio,sell-ratio))
+--vol-type [preopen, 10k, 50k, 100k] 기본:preopen (거래량구분 (preopen=장시작전(0주이상),10k,50k,100k))
+--stock-cond [all, exclude-managed, exclude-margin-100, only-margin-100, only-margin-40, only-margin-30, only-margin-20] 기본:all (종목조건 (all,exclude-managed,exclude-margin-100,only-margin-100,only-margin-40,only-margin-30,only-margin-20))
+--credit [all, a, b, c, d, e, all-financing] 기본:all (신용조건 (all,a,b,c,d,e,all-financing))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -5235,7 +5235,7 @@
       <c r="H108" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---type 기본:1 (조회구분 (1=전일거래량, 2=전일거래대금))
+--type [volume, amount] 기본:volume (조회구분 (volume=전일거래량, amount=전일거래대금))
 --rank-start 기본:1 (순위시작)
 --rank-end 기본:50 (순위끝)
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
@@ -5283,9 +5283,9 @@
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to (종료일자 (YYYYMMDD))
 --market [all, kospi, kosdaq] 기본:all (시장구분)
---type 기본:1 (매매구분 (1=순매수, 2=순매도))
---sort 기본:1 (정렬조건 (1=수량, 2=금액))
---unit 기본:1 (단위 (1=단주, 1000=천주))
+--type [net-buy, net-sell] 기본:net-buy (매매구분 (net-buy=순매수, net-sell=순매도))
+--sort [quantity, amount] 기본:quantity (정렬조건 (quantity=수량, amount=금액))
+--unit [share, thousand] 기본:share (단위 (share=단주, thousand=천주))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -5329,14 +5329,14 @@
       <c r="H110" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---type 기본:1 (등락구분 (1=급등, 2=급락))
---time-type 기본:1 (시간구분 (1=분전, 2=일전))
+--type [rise, fall] 기본:rise (등락구분 (rise=급등, fall=급락))
+--time-type [minute, day] 기본:minute (시간구분 (minute=분전, day=일전))
 --time 기본:5 (시간)
---vol-type (거래량구분)
---stk-cnd (종목조건)
---credit (신용조건)
---price-cnd (가격조건)
---include-limit (상하한포함 (0=미포함, 1=포함))
+--vol-type [all, 10k, 50k, 100k, 150k, 200k, 300k, 500k, 1000k] 기본:all (거래량구분 (all,10k,50k,100k,150k,200k,300k,500k,1000k))
+--stock-cond [all, exclude-managed, exclude-preferred, exclude-margin-100, only-margin-100, only-margin-40, only-margin-30] 기본:all (종목조건 (all,exclude-managed,exclude-preferred,exclude-margin-100,only-margin-100,only-margin-40,only-margin-30))
+--credit [all, a, b, c, d, e, all-financing] 기본:all (신용조건 (all,a,b,c,d,e,all-financing))
+--price-cond [all, under-1k, 1k-2k, 2k-3k, 5k-10k, over-10k, over-1k] 기본:all (가격조건 (all,under-1k,1k-2k,2k-3k,5k-10k,over-10k,over-1k))
+--include-limit [yes, no] 기본:no (상하한포함 (yes,no))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -5429,7 +5429,7 @@
 --price-type [all, under-1k, over-1k, 1k-2k, 2k-5k, over-5k, 5k-10k, under-10k, over-10k, over-50k, over-100k] 기본:all (가격구분 (all,under-1k,over-1k,1k-2k,2k-5k,over-5k,5k-10k,under-10k,over-10k,over-50k,over-100k))
 --amount-type [all, 10m, 30m, 50m, 100m, 300m, 500m, 1b, 3b, 5b, 10b, 30b, 50b] 기본:all (거래대금구분 (all,10m,30m,50m,100m,300m,500m,1b,3b,5b,10b,30b,50b = 이상))
 --session [all, regular, pre-open, after-hours] 기본:all (장운영구분 (all=전체,regular=장중,pre-open=장전시간외,after-hours=장후시간외))
---exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
+--exchange [KRX, NXT, all] 기본:KRX (거래소 (KRX/NXT/all))</t>
         </is>
       </c>
     </row>
@@ -5472,12 +5472,12 @@
       <c r="H113" s="10" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분)
---sort 기본:1 (정렬 (1=급증량,2=급증률,3=급감량,4=급감률))
---time-type 기본:1 (구분 (1=분, 2=전일))
---vol-type (거래량구분)
+--sort [spike-quantity, spike-rate, drop-quantity, drop-rate] 기본:spike-quantity (정렬 (spike-quantity,spike-rate,drop-quantity,drop-rate))
+--time-type [minute, previous-day] 기본:minute (구분 (minute=분, previous-day=전일))
+--vol-type [5k, 10k, 50k, 100k, 200k, 300k, 500k, 1000k] 기본:5k (거래량구분 (5k,10k,50k,100k,200k,300k,500k,1000k — 전체 없음))
 --time (시간 (선택))
---stk-cnd (종목조건)
---price-type (가격구분)
+--stock-cond [all, exclude-managed, exclude-preferred, exclude-liquidation, exclude-managed-preferred, exclude-margin-100, only-margin-100, only-margin-60, only-margin-50, only-margin-40, only-margin-30, only-margin-20, exclude-etn, exclude-etf, exclude-etf-etn, exclude-spac, exclude-etf-etn-spac] 기본:all (종목조건 (all,exclude-managed,exclude-preferred,exclude-liquidation,exclude-managed-preferred,exclude-margin-100,only-margin-100,only-margin-60,only-margin-50,only-margin-40,only-margin-30,only-margin-20,exclude-etn,exclude-etf,exclude-etf-etn,exclude-spac,exclude-etf-etn-spac))
+--price-type [all, over-50k, over-10k, over-5k, over-1k, over-100k] 기본:all (가격구분 (all,over-50k,over-10k,over-5k,over-1k,over-100k))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>--market (시장구분 (0=코스피,1=코스닥,2=KOSPI200,4=KOSPI100,7=KRX100))</t>
+          <t>--market [kospi, kosdaq, kospi200, kospi100, krx100] 기본:kospi (시장구분)</t>
         </is>
       </c>
     </row>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>--market (시장구분 (0=코스피, 1=코스닥, 2=코스피200))</t>
+          <t>--market [kospi, kosdaq, kospi200] 기본:kospi (시장구분)</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>--market (시장구분)</t>
+          <t>--market [kospi, kosdaq, kospi200] 기본:kospi (시장구분)</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>--inds-cd 기본:001 (업종코드 (001=KOSPI종합, 101=KOSDAQ종합))</t>
+          <t>--sector-code 기본:001 (업종코드 (001=KOSPI종합, 101=KOSDAQ종합))</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       <c r="H124" s="10" t="inlineStr">
         <is>
           <t>--market [kospi, kosdaq] 기본:kospi (시장구분)
---unit (금액/수량 (0=금액, 1=수량))
+--unit [amount, quantity] 기본:amount (금액/수량 구분)
 --date (기준일자 (YYYYMMDD))
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>--market (시장구분)
+          <t>--market [kospi, kosdaq, kospi200] 기본:kospi (시장구분)
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -6071,11 +6071,11 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>--type (검색구분 (0=전체, 1=테마검색, 2=종목검색))
+          <t>--type [all, theme, stock] 기본:all (검색구분)
 --code (종목코드 (종목검색시))
 --date-type 기본:1 (날짜구분 (n일전))
 --theme-name (테마명 (테마검색시))
---sort 기본:1 (정렬 (1=상위기간수익률,2=하위기간수익률,3=상위등락률,4=하위등락률))
+--sort [profit-top, profit-bottom, change-top, change-bottom] 기본:profit-top (정렬 기준)
 --exchange [KRX, NXT] 기본:KRX (거래소 (KRX/NXT))</t>
         </is>
       </c>
@@ -7319,9 +7319,9 @@
         <is>
           <t>--broker *필수 (회원사코드)
 --code (종목코드 (선택))
---market [0, 1, 2, 3] (시장구분 (0=전체, 1=코스피, 2=코스닥, 3=종목))
+--market [all, kospi, kosdaq, stock] 기본:all (시장구분 (all=전체, kospi=코스피, kosdaq=코스닥, stock=종목))
 --volume-type (수량구분)
---price-type (가격구분)
+--price-type [all, under-1k, over-1k, 1k-2k, 2k-5k, 5k-10k, over-10k] 기본:all (가격구분 (all, under-1k, over-1k, 1k-2k, 2k-5k, 5k-10k, over-10k))
 --exchange [KRX, NXT, all] 기본:all (거래소구분 (KRX/NXT/all))</t>
         </is>
       </c>
@@ -7364,14 +7364,14 @@
       </c>
       <c r="H156" s="14" t="inlineStr">
         <is>
-          <t>--sort [1, 2, 3, 4] 기본:1 (정렬구분 (1=시가, 2=고가, 3=저가, 4=기준가))
---volume-cond (거래량조건)
+          <t>--sort [open, high, low, base] 기본:open (정렬구분 (open=시가, high=고가, low=저가, base=기준가))
+--volume-cond [all, 10k, 50k, 100k, 500k, 1000k] 기본:all (거래량조건 (all=전체조회, 10k=만주이상, ..., 1000k=백만주이상))
 --market [all, kospi, kosdaq] 기본:all (시장구분 (all/kospi/kosdaq))
---include-limit [0, 1] (상하한포함 (0=미포함, 1=포함))
---stock-cond (종목조건)
---credit-cond (신용조건)
---amount-cond (거래대금조건)
---direction [1, 2] 기본:1 (등락조건 (1=상위, 2=하위))
+--include-limit [yes, no] 기본:no (상하한포함 (yes=포함, no=미포함))
+--stock-cond [all, exclude-managed, exclude-preferred, exclude-managed-preferred, exclude-margin-100, only-margin-100, only-margin-40, only-margin-30, only-margin-20] 기본:all (종목조건 (all, exclude-managed, exclude-preferred, ...))
+--credit-cond [all, a, b, c, d, e, all-financing] 기본:all (신용조건 (all, a, b, c, d, e, all-financing))
+--amount-cond [all, 30m, 50m, 100m, 300m, 500m, 1b, 3b, 5b, 10b, 30b, 50b] 기본:all (거래대금조건 (all, 30m, 50m, ..., 50b))
+--direction [top, bottom] 기본:top (등락조건 (top=상위, bottom=하위))
 --exchange [KRX, NXT, all] 기본:all (거래소구분 (KRX/NXT/all))</t>
         </is>
       </c>
@@ -7459,7 +7459,7 @@
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분 (all/kospi/kosdaq))
 --ratio 기본:50 (매물집중비율 (0~100))
---include-current [0, 1] (현재가진입 (0=미포함, 1=포함))
+--include-current [yes, no] 기본:no (현재가진입 (yes=포함, no=미포함))
 --count 기본:5 (매물대수)
 --cycle [50, 100, 150, 200, 250, 300] 기본:100 (주기구분)
 --exchange [KRX, NXT, all] 기본:all (거래소구분 (KRX/NXT/all))</t>
@@ -7554,17 +7554,17 @@
       <c r="H160" s="14" t="inlineStr">
         <is>
           <t>--market [all, kospi, kosdaq] 기본:all (시장구분 (all/kospi/kosdaq))
---session [0, 1, 2] (장전구분 (0=전체, 1=정규시장, 2=시간외단일가))
+--session [all, regular, after-hours] 기본:all (장전구분 (all=전체, regular=정규시장, after-hours=시간외단일가))
 --code (종목코드 (선택))
---trigger-type [0, 1, 2, 3] (발동구분 (0=전체, 1=정적VI, 2=동적VI, 3=동적+정적))
+--trigger-type [all, static, dynamic, both] 기본:all (발동구분 (all=전체, static=정적VI, dynamic=동적VI, both=동적+정적))
 --skip-stock (제외종목)
---volume-type (거래량구분)
+--volume-type [yes, no] 기본:no (거래량구분 (yes=사용, no=사용안함))
 --min-volume (최소거래량)
 --max-volume (최대거래량)
---amount-type (거래대금구분)
+--amount-type [yes, no] 기본:no (거래대금구분 (yes=사용, no=사용안함))
 --min-amount (최소거래대금)
 --max-amount (최대거래대금)
---direction [0, 1, 2] (발동방향 (0=전체, 1=상승, 2=하락))
+--direction [all, rise, fall] 기본:all (발동방향 (all=전체, rise=상승, fall=하락))
 --exchange [KRX, NXT, all] 기본:all (거래소구분 (KRX/NXT/all))</t>
         </is>
       </c>
@@ -7652,7 +7652,7 @@
       </c>
       <c r="H162" s="14" t="inlineStr">
         <is>
-          <t>--type [00, 05, 07] 기본:00 (신주인수권구분 (00=전체, 05=신주인수권증권, 07=신주인수권증서))</t>
+          <t>--type [all, warrant-security, warrant-certificate] 기본:all (신주인수권구분 (all=전체, warrant-security=신주인수권증권, warrant-certificate=신주인수권증서))</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
       <c r="H164" s="14" t="inlineStr">
         <is>
           <t>--base-date *필수 (기준일자 (YYYYMMDD))
---adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))
+--adjusted [raw, adjusted] 기본:raw (수정주가구분 (raw=미적용, adjusted=적용))
 --exchange [nasdaq, nyse, amex] (미국 거래소)
 --krw (원화 환산 (미국 전용))</t>
         </is>
@@ -7777,9 +7777,9 @@
       </c>
       <c r="H165" s="14" t="inlineStr">
         <is>
-          <t>--market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
---amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
---trade [0, 1, 2] (매매구분 (0=순매수, 1=매수, 2=매도))</t>
+          <t>--market [all, kospi, kosdaq] 기본:kospi (시장구분 (all=전체, kospi=코스피, kosdaq=코스닥))
+--amount-qty [amount, quantity] 기본:amount (금액수량구분 (amount=금액, quantity=수량))
+--trade [net-buy, buy, sell] 기본:net-buy (매매구분 (net-buy=순매수, buy=매수, sell=매도))</t>
         </is>
       </c>
     </row>
@@ -7822,9 +7822,9 @@
       <c r="H166" s="14" t="inlineStr">
         <is>
           <t>--date *필수 (일자 (YYYYMMDD))
---amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
---trade [0, 1, 2] (매매구분 (0=순매수, 1=매수, 2=매도))
---unit [1000, 1] 기본:1 (단위구분 (1000=천주, 1=단주))</t>
+--amount-qty [amount, quantity] 기본:amount (금액수량구분 (amount=금액, quantity=수량))
+--trade [net-buy, buy, sell] 기본:net-buy (매매구분 (net-buy=순매수, buy=매수, sell=매도))
+--unit [thousand, share] 기본:share (단위구분 (thousand=천주, share=단주))</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       <c r="H167" s="14" t="inlineStr">
         <is>
           <t>--interval [1, 3, 5, 10, 15, 30, 45, 60] 기본:5 (분봉 간격 (1/3/5/10/15/30/45/60))
---adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))
+--adjusted [raw, adjusted] 기본:raw (수정주가구분 (raw=미적용, adjusted=적용))
 --base-date (기준일자 (YYYYMMDD, 선택))
 --exchange [nasdaq, nyse, amex] (미국 거래소)
 --krw (원화 환산 (미국 전용))</t>
@@ -7905,7 +7905,7 @@
       <c r="H168" s="14" t="inlineStr">
         <is>
           <t>--base-date *필수 (기준일자 (YYYYMMDD))
---adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))
+--adjusted [raw, adjusted] 기본:raw (수정주가구분 (raw=미적용, adjusted=적용))
 --exchange [nasdaq, nyse, amex] (미국 거래소)
 --krw (원화 환산 (미국 전용))</t>
         </is>
@@ -7946,7 +7946,7 @@
       <c r="H169" s="14" t="inlineStr">
         <is>
           <t>--range [1, 3, 5, 10, 30] 기본:1 (틱범위 (1/3/5/10/30))
---adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))
+--adjusted [raw, adjusted] 기본:raw (수정주가구분 (raw=미적용, adjusted=적용))
 --exchange [nasdaq, nyse, amex] (미국 거래소)
 --krw (원화 환산 (미국 전용))</t>
         </is>
@@ -7987,7 +7987,7 @@
       <c r="H170" s="14" t="inlineStr">
         <is>
           <t>--base-date *필수 (기준일자 (YYYYMMDD))
---adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))
+--adjusted [raw, adjusted] 기본:raw (수정주가구분 (raw=미적용, adjusted=적용))
 --exchange [nasdaq, nyse, amex] (미국 거래소)
 --krw (원화 환산 (미국 전용))</t>
         </is>
@@ -8028,7 +8028,7 @@
       <c r="H171" s="14" t="inlineStr">
         <is>
           <t>--base-date *필수 (기준일자 (YYYYMMDD))
---adjusted [0, 1] (수정주가구분 (0=미적용, 1=적용))
+--adjusted [raw, adjusted] 기본:raw (수정주가구분 (raw=미적용, adjusted=적용))
 --exchange [nasdaq, nyse, amex] (미국 거래소)
 --krw (원화 환산 (미국 전용))</t>
         </is>
@@ -8286,7 +8286,7 @@
       <c r="H177" s="14" t="inlineStr">
         <is>
           <t>--date *필수 (조회일자 (YYYYMMDD))
---display [0, 1] (표시구분 (0=수량, 1=금액백만원))</t>
+--display [quantity, amount] 기본:quantity (표시구분 (quantity=수량, amount=금액백만원))</t>
         </is>
       </c>
     </row>
@@ -8622,9 +8622,9 @@
       <c r="H185" s="14" t="inlineStr">
         <is>
           <t>--date *필수 (일자 (YYYYMMDD))
---amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
---trade [0, 1, 2] (매매구분 (0=순매수, 1=매수, 2=매도))
---unit [1000, 1] 기본:1 (단위구분 (1000=천주, 1=단주))</t>
+--amount-qty [amount, quantity] 기본:amount (금액수량구분 (amount=금액, quantity=수량))
+--trade [net-buy, buy, sell] 기본:net-buy (매매구분 (net-buy=순매수, buy=매수, sell=매도))
+--unit [thousand, share] 기본:share (단위구분 (thousand=천주, share=단주))</t>
         </is>
       </c>
     </row>
@@ -8668,9 +8668,9 @@
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
---amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
---trade [0, 1, 2] (매매구분 (0=순매수, 1=매수, 2=매도))
---unit [1000, 1] 기본:1 (단위구분 (1000=천주, 1=단주))</t>
+--amount-qty [amount, quantity] 기본:amount (금액수량구분 (amount=금액, quantity=수량))
+--trade [net-buy] 기본:net-buy (매매구분 (net-buy=순매수, 스펙상 고정값))
+--unit [thousand, share] 기본:share (단위구분 (thousand=천주, share=단주))</t>
         </is>
       </c>
     </row>
@@ -8763,9 +8763,9 @@
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
---trade [1, 2] 기본:2 (매매구분 (1=순매도, 2=순매수))
+--trade [net-sell, net-buy] 기본:net-buy (매매구분 (net-sell=순매도, net-buy=순매수))
 --market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
---investor-type 기본:9000 (투자자구분 (8000=개인, 9000=외국인 등))
+--investor-type [individual, foreign, financial-investment, investment-trust, private-fund, other-financial, bank, insurance, pension, state, other-corporate, institution] 기본:foreign (투자자구분 (individual=개인, foreign=외국인, institution=기관계 등))
 --exchange [KRX, NXT, all] 기본:all (거래소구분 (KRX/NXT/all))</t>
         </is>
       </c>
@@ -8810,7 +8810,7 @@
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
---trade [1, 2] 기본:2 (매매구분 (1=순매도, 2=순매수))
+--trade [net-sell, net-buy] 기본:net-buy (매매구분 (net-sell=순매도, net-buy=순매수))
 --market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
 --exchange [KRX, NXT, all] 기본:all (거래소구분 (KRX/NXT/all))</t>
         </is>
@@ -8945,8 +8945,8 @@
       </c>
       <c r="H192" s="14" t="inlineStr">
         <is>
-          <t>--trade [1, 2] 기본:2 (매매구분 (1=순매도, 2=순매수))
---amount-qty [1, 2] 기본:1 (금액수량구분 (1=금액, 2=수량))
+          <t>--trade [net-sell, net-buy] 기본:net-buy (매매구분 (net-sell=순매도, net-buy=순매수))
+--amount-qty [amount, quantity] 기본:amount (금액수량구분 (amount=금액, quantity=수량))
 --market [kospi, kosdaq] 기본:kospi (시장구분 (kospi/kosdaq))
 --exchange [KRX, NXT, all] 기본:all (거래소구분 (KRX/NXT/all))</t>
         </is>
@@ -8992,8 +8992,8 @@
         <is>
           <t>--from *필수 (시작일자 (YYYYMMDD))
 --to *필수 (종료일자 (YYYYMMDD))
---inst-price [1, 2] 기본:1 (기관추정단가구분 (1=매수단가, 2=매도단가))
---foreign-price [1, 2] 기본:1 (외인추정단가구분 (1=매수단가, 2=매도단가))</t>
+--inst-price [buy, sell] 기본:buy (기관추정단가구분 (buy=매수단가, sell=매도단가))
+--foreign-price [buy, sell] 기본:buy (외인추정단가구분 (buy=매수단가, sell=매도단가))</t>
         </is>
       </c>
     </row>
@@ -9536,8 +9536,8 @@
       </c>
       <c r="H206" s="14" t="inlineStr">
         <is>
-          <t>--when [1, 2] 기본:1 (당일전일 (1=당일, 2=전일))
---mode [0, 1] (틱/분 (0=틱, 1=분))
+          <t>--when [today, previous] 기본:today (당일전일 (today=당일, previous=전일))
+--mode [tick, minute] 기본:tick (틱/분 (tick=틱, minute=분))
 --time (시간 (4자리, 예: 1030))</t>
         </is>
       </c>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="H207" s="14" t="inlineStr">
         <is>
-          <t>--when [1, 2] 기본:1 (당일전일 (1=당일, 2=전일))</t>
+          <t>--when [today, previous] 기본:today (당일전일 (today=당일, previous=전일))</t>
         </is>
       </c>
     </row>

--- a/kiwoom_cli_commands.xlsx
+++ b/kiwoom_cli_commands.xlsx
@@ -2007,7 +2007,7 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>--force (서버 폐기에 실패해도 로컬 토큰을 지웁니다 (서버 도달 불가 시 탈출구).)</t>
         </is>
       </c>
     </row>
